--- a/SuppXLS/Scen_usingStepMining_n_mute_original_Min2.xlsx
+++ b/SuppXLS/Scen_usingStepMining_n_mute_original_Min2.xlsx
@@ -4,17 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="18350" windowHeight="8710"/>
   </bookViews>
   <sheets>
     <sheet name="Scen_usingStepMining_n_mute_ori" sheetId="1" r:id="rId1"/>
-    <sheet name="attache--data--from" sheetId="2" r:id="rId2"/>
+    <sheet name="NOUSEattache--data--from" sheetId="2" r:id="rId2"/>
     <sheet name="Codex_sources" sheetId="3" r:id="rId3"/>
     <sheet name="Codex_USGS_raw" sheetId="4" r:id="rId4"/>
     <sheet name="Codex_Li_Busch" sheetId="5" r:id="rId5"/>
     <sheet name="Codex_calc" sheetId="6" r:id="rId6"/>
     <sheet name="Codex_update_notes" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Scen_usingStepMining_n_mute_ori!$C$39:$AO$109</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -4289,10 +4292,7 @@
         <f>Codex_calc!D41</f>
         <v>BNDACT</v>
       </c>
-      <c r="E41" s="30">
-        <f>Codex_calc!E41</f>
-        <v>0</v>
-      </c>
+      <c r="E41" s="30"/>
       <c r="F41" s="30">
         <f>Codex_calc!F41</f>
         <v>0</v>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="I41" s="30">
         <f>Codex_calc!I41</f>
-        <v>0.426746821967562</v>
+        <v>0.426746821967561</v>
       </c>
       <c r="J41" s="30">
         <f>Codex_calc!J41</f>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="L41" s="30">
         <f>Codex_calc!L41</f>
-        <v>7.17848331141587</v>
+        <v>7.17848331141586</v>
       </c>
       <c r="M41" s="30">
         <f>Codex_calc!M41</f>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="O41" s="30">
         <f>Codex_calc!O41</f>
-        <v>1.4250610557956</v>
+        <v>1.42506105579561</v>
       </c>
       <c r="P41" s="30">
         <f>Codex_calc!P41</f>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="AI41" s="30">
         <f>Codex_calc!AI41</f>
-        <v>0.727409355626526</v>
+        <v>0.727409355626527</v>
       </c>
       <c r="AJ41" s="30">
         <f>Codex_calc!AJ41</f>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AL41" s="30">
         <f>Codex_calc!AL41</f>
-        <v>0.363704677813263</v>
+        <v>0.363704677813262</v>
       </c>
       <c r="AM41" s="30">
         <f>Codex_calc!AM41</f>
@@ -4447,10 +4447,7 @@
         <f>Codex_calc!D42</f>
         <v>CUM</v>
       </c>
-      <c r="E42" s="30">
-        <f>Codex_calc!E42</f>
-        <v>0</v>
-      </c>
+      <c r="E42" s="30"/>
       <c r="F42" s="30">
         <f>Codex_calc!F42</f>
         <v>0</v>
@@ -4497,7 +4494,7 @@
       </c>
       <c r="Q42" s="30">
         <f>Codex_calc!Q42</f>
-        <v>94.0713806172171</v>
+        <v>94.0713806172166</v>
       </c>
       <c r="R42" s="30">
         <f>Codex_calc!R42</f>
@@ -4565,7 +4562,7 @@
       </c>
       <c r="AH42" s="30">
         <f>Codex_calc!AH42</f>
-        <v>124.694798393574</v>
+        <v>124.694798393575</v>
       </c>
       <c r="AI42" s="30">
         <f>Codex_calc!AI42</f>
@@ -4763,10 +4760,7 @@
         <f>Codex_calc!D44</f>
         <v>BNDACT</v>
       </c>
-      <c r="E44" s="30">
-        <f>Codex_calc!E44</f>
-        <v>0</v>
-      </c>
+      <c r="E44" s="30"/>
       <c r="F44" s="30">
         <f>Codex_calc!F44</f>
         <v>0</v>
@@ -4781,7 +4775,7 @@
       </c>
       <c r="I44" s="30">
         <f>Codex_calc!I44</f>
-        <v>0.853493643935125</v>
+        <v>0.853493643935123</v>
       </c>
       <c r="J44" s="30">
         <f>Codex_calc!J44</f>
@@ -4897,7 +4891,7 @@
       </c>
       <c r="AL44" s="30">
         <f>Codex_calc!AL44</f>
-        <v>0.727409355626526</v>
+        <v>0.727409355626524</v>
       </c>
       <c r="AM44" s="30">
         <f>Codex_calc!AM44</f>
@@ -4905,7 +4899,7 @@
       </c>
       <c r="AN44" s="30">
         <f>Codex_calc!AN44</f>
-        <v>5.75314672177344</v>
+        <v>5.75314672177343</v>
       </c>
       <c r="AO44" t="str">
         <f>Codex_calc!AO44</f>
@@ -4921,10 +4915,7 @@
         <f>Codex_calc!D45</f>
         <v>CUM</v>
       </c>
-      <c r="E45" s="30">
-        <f>Codex_calc!E45</f>
-        <v>0</v>
-      </c>
+      <c r="E45" s="30"/>
       <c r="F45" s="30">
         <f>Codex_calc!F45</f>
         <v>0</v>
@@ -4935,7 +4926,7 @@
       </c>
       <c r="H45" s="30">
         <f>Codex_calc!H45</f>
-        <v>2609.34575023317</v>
+        <v>2609.34575023318</v>
       </c>
       <c r="I45" s="30">
         <f>Codex_calc!I45</f>
@@ -5237,150 +5228,42 @@
         <f>Codex_calc!D47</f>
         <v>BNDACT</v>
       </c>
-      <c r="E47" s="30">
-        <f>Codex_calc!E47</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="30">
-        <f>Codex_calc!F47</f>
-        <v>0</v>
-      </c>
-      <c r="G47" s="30">
-        <f>Codex_calc!G47</f>
-        <v>0</v>
-      </c>
-      <c r="H47" s="30">
-        <f>Codex_calc!H47</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="30">
-        <f>Codex_calc!I47</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="30">
-        <f>Codex_calc!J47</f>
-        <v>0</v>
-      </c>
-      <c r="K47" s="30">
-        <f>Codex_calc!K47</f>
-        <v>0</v>
-      </c>
-      <c r="L47" s="30">
-        <f>Codex_calc!L47</f>
-        <v>0</v>
-      </c>
-      <c r="M47" s="30">
-        <f>Codex_calc!M47</f>
-        <v>0</v>
-      </c>
-      <c r="N47" s="30">
-        <f>Codex_calc!N47</f>
-        <v>0</v>
-      </c>
-      <c r="O47" s="30">
-        <f>Codex_calc!O47</f>
-        <v>0</v>
-      </c>
-      <c r="P47" s="30">
-        <f>Codex_calc!P47</f>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="30">
-        <f>Codex_calc!Q47</f>
-        <v>0</v>
-      </c>
-      <c r="R47" s="30">
-        <f>Codex_calc!R47</f>
-        <v>0</v>
-      </c>
-      <c r="S47" s="30">
-        <f>Codex_calc!S47</f>
-        <v>0</v>
-      </c>
-      <c r="T47" s="30">
-        <f>Codex_calc!T47</f>
-        <v>0</v>
-      </c>
-      <c r="U47" s="30">
-        <f>Codex_calc!U47</f>
-        <v>0</v>
-      </c>
-      <c r="V47" s="30">
-        <f>Codex_calc!V47</f>
-        <v>0</v>
-      </c>
-      <c r="W47" s="30">
-        <f>Codex_calc!W47</f>
-        <v>0</v>
-      </c>
-      <c r="X47" s="30">
-        <f>Codex_calc!X47</f>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="30">
-        <f>Codex_calc!Y47</f>
-        <v>0</v>
-      </c>
-      <c r="Z47" s="30">
-        <f>Codex_calc!Z47</f>
-        <v>0</v>
-      </c>
-      <c r="AA47" s="30">
-        <f>Codex_calc!AA47</f>
-        <v>0</v>
-      </c>
-      <c r="AB47" s="30">
-        <f>Codex_calc!AB47</f>
-        <v>0</v>
-      </c>
-      <c r="AC47" s="30">
-        <f>Codex_calc!AC47</f>
-        <v>0</v>
-      </c>
-      <c r="AD47" s="30">
-        <f>Codex_calc!AD47</f>
-        <v>0</v>
-      </c>
-      <c r="AE47" s="30">
-        <f>Codex_calc!AE47</f>
-        <v>0</v>
-      </c>
-      <c r="AF47" s="30">
-        <f>Codex_calc!AF47</f>
-        <v>0</v>
-      </c>
-      <c r="AG47" s="30">
-        <f>Codex_calc!AG47</f>
-        <v>0</v>
-      </c>
-      <c r="AH47" s="30">
-        <f>Codex_calc!AH47</f>
-        <v>0</v>
-      </c>
-      <c r="AI47" s="30">
-        <f>Codex_calc!AI47</f>
-        <v>0</v>
-      </c>
-      <c r="AJ47" s="30">
-        <f>Codex_calc!AJ47</f>
-        <v>0</v>
-      </c>
-      <c r="AK47" s="30">
-        <f>Codex_calc!AK47</f>
-        <v>0</v>
-      </c>
-      <c r="AL47" s="30">
-        <f>Codex_calc!AL47</f>
-        <v>0</v>
-      </c>
-      <c r="AM47" s="30">
-        <f>Codex_calc!AM47</f>
-        <v>0</v>
-      </c>
-      <c r="AN47" s="30">
-        <f>Codex_calc!AN47</f>
-        <v>0</v>
-      </c>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
+      <c r="R47" s="30"/>
+      <c r="S47" s="30"/>
+      <c r="T47" s="30"/>
+      <c r="U47" s="30"/>
+      <c r="V47" s="30"/>
+      <c r="W47" s="30"/>
+      <c r="X47" s="30"/>
+      <c r="Y47" s="30"/>
+      <c r="Z47" s="30"/>
+      <c r="AA47" s="30"/>
+      <c r="AB47" s="30"/>
+      <c r="AC47" s="30"/>
+      <c r="AD47" s="30"/>
+      <c r="AE47" s="30"/>
+      <c r="AF47" s="30"/>
+      <c r="AG47" s="30"/>
+      <c r="AH47" s="30"/>
+      <c r="AI47" s="30"/>
+      <c r="AJ47" s="30"/>
+      <c r="AK47" s="30"/>
+      <c r="AL47" s="30"/>
+      <c r="AM47" s="30"/>
+      <c r="AN47" s="30"/>
       <c r="AO47" t="str">
         <f>Codex_calc!AO47</f>
         <v>2019, 2130</v>
@@ -5395,10 +5278,7 @@
         <f>Codex_calc!D48</f>
         <v>CUM</v>
       </c>
-      <c r="E48" s="30">
-        <f>Codex_calc!E48</f>
-        <v>0</v>
-      </c>
+      <c r="E48" s="30"/>
       <c r="F48" s="30">
         <f>Codex_calc!F48</f>
         <v>0</v>
@@ -5441,11 +5321,11 @@
       </c>
       <c r="P48" s="30">
         <f>Codex_calc!P48</f>
-        <v>449.659973226238</v>
+        <v>449.659973226239</v>
       </c>
       <c r="Q48" s="30">
         <f>Codex_calc!Q48</f>
-        <v>2787.73946940985</v>
+        <v>2787.73946940986</v>
       </c>
       <c r="R48" s="30">
         <f>Codex_calc!R48</f>
@@ -5517,7 +5397,7 @@
       </c>
       <c r="AI48" s="30">
         <f>Codex_calc!AI48</f>
-        <v>9.4402035733622</v>
+        <v>9.44020357336223</v>
       </c>
       <c r="AJ48" s="30">
         <f>Codex_calc!AJ48</f>
@@ -5868,150 +5748,42 @@
         <f>Codex_calc!D51</f>
         <v>BNDACT</v>
       </c>
-      <c r="E51" s="30">
-        <f>Codex_calc!E51</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="30">
-        <f>Codex_calc!F51</f>
-        <v>0</v>
-      </c>
-      <c r="G51" s="30">
-        <f>Codex_calc!G51</f>
-        <v>0</v>
-      </c>
-      <c r="H51" s="30">
-        <f>Codex_calc!H51</f>
-        <v>6.40384615384615</v>
-      </c>
-      <c r="I51" s="30">
-        <f>Codex_calc!I51</f>
-        <v>0</v>
-      </c>
-      <c r="J51" s="30">
-        <f>Codex_calc!J51</f>
-        <v>0</v>
-      </c>
-      <c r="K51" s="30">
-        <f>Codex_calc!K51</f>
-        <v>0</v>
-      </c>
-      <c r="L51" s="30">
-        <f>Codex_calc!L51</f>
-        <v>9.96153846153846</v>
-      </c>
-      <c r="M51" s="30">
-        <f>Codex_calc!M51</f>
-        <v>17.0769230769231</v>
-      </c>
-      <c r="N51" s="30">
-        <f>Codex_calc!N51</f>
-        <v>0</v>
-      </c>
-      <c r="O51" s="30">
-        <f>Codex_calc!O51</f>
-        <v>0</v>
-      </c>
-      <c r="P51" s="30">
-        <f>Codex_calc!P51</f>
-        <v>0</v>
-      </c>
-      <c r="Q51" s="30">
-        <f>Codex_calc!Q51</f>
-        <v>0</v>
-      </c>
-      <c r="R51" s="30">
-        <f>Codex_calc!R51</f>
-        <v>0</v>
-      </c>
-      <c r="S51" s="30">
-        <f>Codex_calc!S51</f>
-        <v>0</v>
-      </c>
-      <c r="T51" s="30">
-        <f>Codex_calc!T51</f>
-        <v>0</v>
-      </c>
-      <c r="U51" s="30">
-        <f>Codex_calc!U51</f>
-        <v>0</v>
-      </c>
-      <c r="V51" s="30">
-        <f>Codex_calc!V51</f>
-        <v>0</v>
-      </c>
-      <c r="W51" s="30">
-        <f>Codex_calc!W51</f>
-        <v>0</v>
-      </c>
-      <c r="X51" s="30">
-        <f>Codex_calc!X51</f>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="30">
-        <f>Codex_calc!Y51</f>
-        <v>0</v>
-      </c>
-      <c r="Z51" s="30">
-        <f>Codex_calc!Z51</f>
-        <v>0</v>
-      </c>
-      <c r="AA51" s="30">
-        <f>Codex_calc!AA51</f>
-        <v>21.3461538461538</v>
-      </c>
-      <c r="AB51" s="30">
-        <f>Codex_calc!AB51</f>
-        <v>0</v>
-      </c>
-      <c r="AC51" s="30">
-        <f>Codex_calc!AC51</f>
-        <v>0</v>
-      </c>
-      <c r="AD51" s="30">
-        <f>Codex_calc!AD51</f>
-        <v>469.615384615385</v>
-      </c>
-      <c r="AE51" s="30">
-        <f>Codex_calc!AE51</f>
-        <v>28.4615384615385</v>
-      </c>
-      <c r="AF51" s="30">
-        <f>Codex_calc!AF51</f>
-        <v>0</v>
-      </c>
-      <c r="AG51" s="30">
-        <f>Codex_calc!AG51</f>
-        <v>0</v>
-      </c>
-      <c r="AH51" s="30">
-        <f>Codex_calc!AH51</f>
-        <v>0</v>
-      </c>
-      <c r="AI51" s="30">
-        <f>Codex_calc!AI51</f>
-        <v>0</v>
-      </c>
-      <c r="AJ51" s="30">
-        <f>Codex_calc!AJ51</f>
-        <v>0</v>
-      </c>
-      <c r="AK51" s="30">
-        <f>Codex_calc!AK51</f>
-        <v>0</v>
-      </c>
-      <c r="AL51" s="30">
-        <f>Codex_calc!AL51</f>
-        <v>0</v>
-      </c>
-      <c r="AM51" s="30">
-        <f>Codex_calc!AM51</f>
-        <v>0</v>
-      </c>
-      <c r="AN51" s="30">
-        <f>Codex_calc!AN51</f>
-        <v>0</v>
-      </c>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="30"/>
+      <c r="S51" s="30"/>
+      <c r="T51" s="30"/>
+      <c r="U51" s="30"/>
+      <c r="V51" s="30"/>
+      <c r="W51" s="30"/>
+      <c r="X51" s="30"/>
+      <c r="Y51" s="30"/>
+      <c r="Z51" s="30"/>
+      <c r="AA51" s="30"/>
+      <c r="AB51" s="30"/>
+      <c r="AC51" s="30"/>
+      <c r="AD51" s="30"/>
+      <c r="AE51" s="30"/>
+      <c r="AF51" s="30"/>
+      <c r="AG51" s="30"/>
+      <c r="AH51" s="30"/>
+      <c r="AI51" s="30"/>
+      <c r="AJ51" s="30"/>
+      <c r="AK51" s="30"/>
+      <c r="AL51" s="30"/>
+      <c r="AM51" s="30"/>
+      <c r="AN51" s="30"/>
       <c r="AO51" t="str">
         <f>Codex_calc!AO51</f>
         <v>2019, 2130</v>
@@ -6026,10 +5798,7 @@
         <f>Codex_calc!D52</f>
         <v>CUM</v>
       </c>
-      <c r="E52" s="30">
-        <f>Codex_calc!E52</f>
-        <v>0</v>
-      </c>
+      <c r="E52" s="30"/>
       <c r="F52" s="30">
         <f>Codex_calc!F52</f>
         <v>0</v>
@@ -6342,150 +6111,42 @@
         <f>Codex_calc!D54</f>
         <v>BNDACT</v>
       </c>
-      <c r="E54" s="30">
-        <f>Codex_calc!E54</f>
-        <v>0</v>
-      </c>
-      <c r="F54" s="30">
-        <f>Codex_calc!F54</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="30">
-        <f>Codex_calc!G54</f>
-        <v>0</v>
-      </c>
-      <c r="H54" s="30">
-        <f>Codex_calc!H54</f>
-        <v>12.8076923076923</v>
-      </c>
-      <c r="I54" s="30">
-        <f>Codex_calc!I54</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="30">
-        <f>Codex_calc!J54</f>
-        <v>0</v>
-      </c>
-      <c r="K54" s="30">
-        <f>Codex_calc!K54</f>
-        <v>0</v>
-      </c>
-      <c r="L54" s="30">
-        <f>Codex_calc!L54</f>
-        <v>19.9230769230769</v>
-      </c>
-      <c r="M54" s="30">
-        <f>Codex_calc!M54</f>
-        <v>34.1538461538462</v>
-      </c>
-      <c r="N54" s="30">
-        <f>Codex_calc!N54</f>
-        <v>0</v>
-      </c>
-      <c r="O54" s="30">
-        <f>Codex_calc!O54</f>
-        <v>0</v>
-      </c>
-      <c r="P54" s="30">
-        <f>Codex_calc!P54</f>
-        <v>0</v>
-      </c>
-      <c r="Q54" s="30">
-        <f>Codex_calc!Q54</f>
-        <v>0</v>
-      </c>
-      <c r="R54" s="30">
-        <f>Codex_calc!R54</f>
-        <v>0</v>
-      </c>
-      <c r="S54" s="30">
-        <f>Codex_calc!S54</f>
-        <v>0</v>
-      </c>
-      <c r="T54" s="30">
-        <f>Codex_calc!T54</f>
-        <v>0</v>
-      </c>
-      <c r="U54" s="30">
-        <f>Codex_calc!U54</f>
-        <v>0</v>
-      </c>
-      <c r="V54" s="30">
-        <f>Codex_calc!V54</f>
-        <v>0</v>
-      </c>
-      <c r="W54" s="30">
-        <f>Codex_calc!W54</f>
-        <v>0</v>
-      </c>
-      <c r="X54" s="30">
-        <f>Codex_calc!X54</f>
-        <v>0</v>
-      </c>
-      <c r="Y54" s="30">
-        <f>Codex_calc!Y54</f>
-        <v>0</v>
-      </c>
-      <c r="Z54" s="30">
-        <f>Codex_calc!Z54</f>
-        <v>0</v>
-      </c>
-      <c r="AA54" s="30">
-        <f>Codex_calc!AA54</f>
-        <v>42.6923076923077</v>
-      </c>
-      <c r="AB54" s="30">
-        <f>Codex_calc!AB54</f>
-        <v>0</v>
-      </c>
-      <c r="AC54" s="30">
-        <f>Codex_calc!AC54</f>
-        <v>0</v>
-      </c>
-      <c r="AD54" s="30">
-        <f>Codex_calc!AD54</f>
-        <v>939.230769230769</v>
-      </c>
-      <c r="AE54" s="30">
-        <f>Codex_calc!AE54</f>
-        <v>56.9230769230769</v>
-      </c>
-      <c r="AF54" s="30">
-        <f>Codex_calc!AF54</f>
-        <v>0</v>
-      </c>
-      <c r="AG54" s="30">
-        <f>Codex_calc!AG54</f>
-        <v>0</v>
-      </c>
-      <c r="AH54" s="30">
-        <f>Codex_calc!AH54</f>
-        <v>0</v>
-      </c>
-      <c r="AI54" s="30">
-        <f>Codex_calc!AI54</f>
-        <v>0</v>
-      </c>
-      <c r="AJ54" s="30">
-        <f>Codex_calc!AJ54</f>
-        <v>0</v>
-      </c>
-      <c r="AK54" s="30">
-        <f>Codex_calc!AK54</f>
-        <v>0</v>
-      </c>
-      <c r="AL54" s="30">
-        <f>Codex_calc!AL54</f>
-        <v>0</v>
-      </c>
-      <c r="AM54" s="30">
-        <f>Codex_calc!AM54</f>
-        <v>0</v>
-      </c>
-      <c r="AN54" s="30">
-        <f>Codex_calc!AN54</f>
-        <v>0</v>
-      </c>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+      <c r="Q54" s="30"/>
+      <c r="R54" s="30"/>
+      <c r="S54" s="30"/>
+      <c r="T54" s="30"/>
+      <c r="U54" s="30"/>
+      <c r="V54" s="30"/>
+      <c r="W54" s="30"/>
+      <c r="X54" s="30"/>
+      <c r="Y54" s="30"/>
+      <c r="Z54" s="30"/>
+      <c r="AA54" s="30"/>
+      <c r="AB54" s="30"/>
+      <c r="AC54" s="30"/>
+      <c r="AD54" s="30"/>
+      <c r="AE54" s="30"/>
+      <c r="AF54" s="30"/>
+      <c r="AG54" s="30"/>
+      <c r="AH54" s="30"/>
+      <c r="AI54" s="30"/>
+      <c r="AJ54" s="30"/>
+      <c r="AK54" s="30"/>
+      <c r="AL54" s="30"/>
+      <c r="AM54" s="30"/>
+      <c r="AN54" s="30"/>
       <c r="AO54" t="str">
         <f>Codex_calc!AO54</f>
         <v>2019, 2130</v>
@@ -6500,10 +6161,7 @@
         <f>Codex_calc!D55</f>
         <v>CUM</v>
       </c>
-      <c r="E55" s="30">
-        <f>Codex_calc!E55</f>
-        <v>0</v>
-      </c>
+      <c r="E55" s="30"/>
       <c r="F55" s="30">
         <f>Codex_calc!F55</f>
         <v>0</v>
@@ -6816,150 +6474,42 @@
         <f>Codex_calc!D57</f>
         <v>BNDACT</v>
       </c>
-      <c r="E57">
-        <f>Codex_calc!E57</f>
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <f>Codex_calc!F57</f>
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <f>Codex_calc!G57</f>
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <f>Codex_calc!H57</f>
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <f>Codex_calc!I57</f>
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <f>Codex_calc!J57</f>
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <f>Codex_calc!K57</f>
-        <v>0</v>
-      </c>
-      <c r="L57">
-        <f>Codex_calc!L57</f>
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <f>Codex_calc!M57</f>
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <f>Codex_calc!N57</f>
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <f>Codex_calc!O57</f>
-        <v>0</v>
-      </c>
-      <c r="P57">
-        <f>Codex_calc!P57</f>
-        <v>0</v>
-      </c>
-      <c r="Q57">
-        <f>Codex_calc!Q57</f>
-        <v>0</v>
-      </c>
-      <c r="R57">
-        <f>Codex_calc!R57</f>
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <f>Codex_calc!S57</f>
-        <v>0</v>
-      </c>
-      <c r="T57">
-        <f>Codex_calc!T57</f>
-        <v>0</v>
-      </c>
-      <c r="U57">
-        <f>Codex_calc!U57</f>
-        <v>0</v>
-      </c>
-      <c r="V57">
-        <f>Codex_calc!V57</f>
-        <v>0</v>
-      </c>
-      <c r="W57">
-        <f>Codex_calc!W57</f>
-        <v>0</v>
-      </c>
-      <c r="X57">
-        <f>Codex_calc!X57</f>
-        <v>0</v>
-      </c>
-      <c r="Y57">
-        <f>Codex_calc!Y57</f>
-        <v>0</v>
-      </c>
-      <c r="Z57">
-        <f>Codex_calc!Z57</f>
-        <v>0</v>
-      </c>
-      <c r="AA57">
-        <f>Codex_calc!AA57</f>
-        <v>0</v>
-      </c>
-      <c r="AB57">
-        <f>Codex_calc!AB57</f>
-        <v>0</v>
-      </c>
-      <c r="AC57">
-        <f>Codex_calc!AC57</f>
-        <v>0</v>
-      </c>
-      <c r="AD57">
-        <f>Codex_calc!AD57</f>
-        <v>0</v>
-      </c>
-      <c r="AE57">
-        <f>Codex_calc!AE57</f>
-        <v>0</v>
-      </c>
-      <c r="AF57">
-        <f>Codex_calc!AF57</f>
-        <v>0</v>
-      </c>
-      <c r="AG57">
-        <f>Codex_calc!AG57</f>
-        <v>0</v>
-      </c>
-      <c r="AH57">
-        <f>Codex_calc!AH57</f>
-        <v>0</v>
-      </c>
-      <c r="AI57">
-        <f>Codex_calc!AI57</f>
-        <v>0</v>
-      </c>
-      <c r="AJ57">
-        <f>Codex_calc!AJ57</f>
-        <v>0</v>
-      </c>
-      <c r="AK57">
-        <f>Codex_calc!AK57</f>
-        <v>0</v>
-      </c>
-      <c r="AL57">
-        <f>Codex_calc!AL57</f>
-        <v>0</v>
-      </c>
-      <c r="AM57">
-        <f>Codex_calc!AM57</f>
-        <v>0</v>
-      </c>
-      <c r="AN57">
-        <f>Codex_calc!AN57</f>
-        <v>0</v>
-      </c>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="O57"/>
+      <c r="P57"/>
+      <c r="Q57"/>
+      <c r="R57"/>
+      <c r="S57"/>
+      <c r="T57"/>
+      <c r="U57"/>
+      <c r="V57"/>
+      <c r="W57"/>
+      <c r="X57"/>
+      <c r="Y57"/>
+      <c r="Z57"/>
+      <c r="AA57"/>
+      <c r="AB57"/>
+      <c r="AC57"/>
+      <c r="AD57"/>
+      <c r="AE57"/>
+      <c r="AF57"/>
+      <c r="AG57"/>
+      <c r="AH57"/>
+      <c r="AI57"/>
+      <c r="AJ57"/>
+      <c r="AK57"/>
+      <c r="AL57"/>
+      <c r="AM57"/>
+      <c r="AN57"/>
       <c r="AO57" t="str">
         <f>Codex_calc!AO57</f>
         <v>2019, 2130</v>
@@ -6974,10 +6524,7 @@
         <f>Codex_calc!D58</f>
         <v>CUM</v>
       </c>
-      <c r="E58">
-        <f>Codex_calc!E58</f>
-        <v>0</v>
-      </c>
+      <c r="E58"/>
       <c r="F58">
         <f>Codex_calc!F58</f>
         <v>0</v>
@@ -7447,150 +6994,42 @@
         <f>Codex_calc!D61</f>
         <v>BNDACT</v>
       </c>
-      <c r="E61">
-        <f>Codex_calc!E61</f>
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <f>Codex_calc!F61</f>
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <f>Codex_calc!G61</f>
-        <v>166.12332516129</v>
-      </c>
-      <c r="H61">
-        <f>Codex_calc!H61</f>
-        <v>2.62785935483871</v>
-      </c>
-      <c r="I61">
-        <f>Codex_calc!I61</f>
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <f>Codex_calc!J61</f>
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <f>Codex_calc!K61</f>
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <f>Codex_calc!L61</f>
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <f>Codex_calc!M61</f>
-        <v>1.42046451612903</v>
-      </c>
-      <c r="N61">
-        <f>Codex_calc!N61</f>
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <f>Codex_calc!O61</f>
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <f>Codex_calc!P61</f>
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <f>Codex_calc!Q61</f>
-        <v>0</v>
-      </c>
-      <c r="R61">
-        <f>Codex_calc!R61</f>
-        <v>0</v>
-      </c>
-      <c r="S61">
-        <f>Codex_calc!S61</f>
-        <v>0</v>
-      </c>
-      <c r="T61">
-        <f>Codex_calc!T61</f>
-        <v>0</v>
-      </c>
-      <c r="U61">
-        <f>Codex_calc!U61</f>
-        <v>0</v>
-      </c>
-      <c r="V61">
-        <f>Codex_calc!V61</f>
-        <v>0</v>
-      </c>
-      <c r="W61">
-        <f>Codex_calc!W61</f>
-        <v>0</v>
-      </c>
-      <c r="X61">
-        <f>Codex_calc!X61</f>
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <f>Codex_calc!Y61</f>
-        <v>1.42046451612903</v>
-      </c>
-      <c r="Z61">
-        <f>Codex_calc!Z61</f>
-        <v>0</v>
-      </c>
-      <c r="AA61">
-        <f>Codex_calc!AA61</f>
-        <v>2.69888258064516</v>
-      </c>
-      <c r="AB61">
-        <f>Codex_calc!AB61</f>
-        <v>0</v>
-      </c>
-      <c r="AC61">
-        <f>Codex_calc!AC61</f>
-        <v>0</v>
-      </c>
-      <c r="AD61">
-        <f>Codex_calc!AD61</f>
-        <v>42.3298425806452</v>
-      </c>
-      <c r="AE61">
-        <f>Codex_calc!AE61</f>
-        <v>5.46878838709677</v>
-      </c>
-      <c r="AF61">
-        <f>Codex_calc!AF61</f>
-        <v>0</v>
-      </c>
-      <c r="AG61">
-        <f>Codex_calc!AG61</f>
-        <v>0</v>
-      </c>
-      <c r="AH61">
-        <f>Codex_calc!AH61</f>
-        <v>0</v>
-      </c>
-      <c r="AI61">
-        <f>Codex_calc!AI61</f>
-        <v>0</v>
-      </c>
-      <c r="AJ61">
-        <f>Codex_calc!AJ61</f>
-        <v>0</v>
-      </c>
-      <c r="AK61">
-        <f>Codex_calc!AK61</f>
-        <v>1.34944129032258</v>
-      </c>
-      <c r="AL61">
-        <f>Codex_calc!AL61</f>
-        <v>0</v>
-      </c>
-      <c r="AM61">
-        <f>Codex_calc!AM61</f>
-        <v>0</v>
-      </c>
-      <c r="AN61">
-        <f>Codex_calc!AN61</f>
-        <v>0</v>
-      </c>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
+      <c r="N61"/>
+      <c r="O61"/>
+      <c r="P61"/>
+      <c r="Q61"/>
+      <c r="R61"/>
+      <c r="S61"/>
+      <c r="T61"/>
+      <c r="U61"/>
+      <c r="V61"/>
+      <c r="W61"/>
+      <c r="X61"/>
+      <c r="Y61"/>
+      <c r="Z61"/>
+      <c r="AA61"/>
+      <c r="AB61"/>
+      <c r="AC61"/>
+      <c r="AD61"/>
+      <c r="AE61"/>
+      <c r="AF61"/>
+      <c r="AG61"/>
+      <c r="AH61"/>
+      <c r="AI61"/>
+      <c r="AJ61"/>
+      <c r="AK61"/>
+      <c r="AL61"/>
+      <c r="AM61"/>
+      <c r="AN61"/>
       <c r="AO61" t="str">
         <f>Codex_calc!AO61</f>
         <v>2019, 2130</v>
@@ -7605,10 +7044,7 @@
         <f>Codex_calc!D62</f>
         <v>CUM</v>
       </c>
-      <c r="E62">
-        <f>Codex_calc!E62</f>
-        <v>0</v>
-      </c>
+      <c r="E62"/>
       <c r="F62">
         <f>Codex_calc!F62</f>
         <v>0</v>
@@ -7921,150 +7357,42 @@
         <f>Codex_calc!D64</f>
         <v>BNDACT</v>
       </c>
-      <c r="E64">
-        <f>Codex_calc!E64</f>
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <f>Codex_calc!F64</f>
-        <v>0</v>
-      </c>
-      <c r="G64">
-        <f>Codex_calc!G64</f>
-        <v>332.246650322581</v>
-      </c>
-      <c r="H64">
-        <f>Codex_calc!H64</f>
-        <v>5.25571870967742</v>
-      </c>
-      <c r="I64">
-        <f>Codex_calc!I64</f>
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <f>Codex_calc!J64</f>
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <f>Codex_calc!K64</f>
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <f>Codex_calc!L64</f>
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <f>Codex_calc!M64</f>
-        <v>2.84092903225806</v>
-      </c>
-      <c r="N64">
-        <f>Codex_calc!N64</f>
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <f>Codex_calc!O64</f>
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <f>Codex_calc!P64</f>
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <f>Codex_calc!Q64</f>
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <f>Codex_calc!R64</f>
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <f>Codex_calc!S64</f>
-        <v>0</v>
-      </c>
-      <c r="T64">
-        <f>Codex_calc!T64</f>
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <f>Codex_calc!U64</f>
-        <v>0</v>
-      </c>
-      <c r="V64">
-        <f>Codex_calc!V64</f>
-        <v>0</v>
-      </c>
-      <c r="W64">
-        <f>Codex_calc!W64</f>
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <f>Codex_calc!X64</f>
-        <v>0</v>
-      </c>
-      <c r="Y64">
-        <f>Codex_calc!Y64</f>
-        <v>2.84092903225806</v>
-      </c>
-      <c r="Z64">
-        <f>Codex_calc!Z64</f>
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <f>Codex_calc!AA64</f>
-        <v>5.39776516129032</v>
-      </c>
-      <c r="AB64">
-        <f>Codex_calc!AB64</f>
-        <v>0</v>
-      </c>
-      <c r="AC64">
-        <f>Codex_calc!AC64</f>
-        <v>0</v>
-      </c>
-      <c r="AD64">
-        <f>Codex_calc!AD64</f>
-        <v>84.6596851612903</v>
-      </c>
-      <c r="AE64">
-        <f>Codex_calc!AE64</f>
-        <v>10.9375767741935</v>
-      </c>
-      <c r="AF64">
-        <f>Codex_calc!AF64</f>
-        <v>0</v>
-      </c>
-      <c r="AG64">
-        <f>Codex_calc!AG64</f>
-        <v>0</v>
-      </c>
-      <c r="AH64">
-        <f>Codex_calc!AH64</f>
-        <v>0</v>
-      </c>
-      <c r="AI64">
-        <f>Codex_calc!AI64</f>
-        <v>0</v>
-      </c>
-      <c r="AJ64">
-        <f>Codex_calc!AJ64</f>
-        <v>0</v>
-      </c>
-      <c r="AK64">
-        <f>Codex_calc!AK64</f>
-        <v>2.69888258064516</v>
-      </c>
-      <c r="AL64">
-        <f>Codex_calc!AL64</f>
-        <v>0</v>
-      </c>
-      <c r="AM64">
-        <f>Codex_calc!AM64</f>
-        <v>0</v>
-      </c>
-      <c r="AN64">
-        <f>Codex_calc!AN64</f>
-        <v>0</v>
-      </c>
+      <c r="E64"/>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64"/>
+      <c r="I64"/>
+      <c r="J64"/>
+      <c r="K64"/>
+      <c r="L64"/>
+      <c r="M64"/>
+      <c r="N64"/>
+      <c r="O64"/>
+      <c r="P64"/>
+      <c r="Q64"/>
+      <c r="R64"/>
+      <c r="S64"/>
+      <c r="T64"/>
+      <c r="U64"/>
+      <c r="V64"/>
+      <c r="W64"/>
+      <c r="X64"/>
+      <c r="Y64"/>
+      <c r="Z64"/>
+      <c r="AA64"/>
+      <c r="AB64"/>
+      <c r="AC64"/>
+      <c r="AD64"/>
+      <c r="AE64"/>
+      <c r="AF64"/>
+      <c r="AG64"/>
+      <c r="AH64"/>
+      <c r="AI64"/>
+      <c r="AJ64"/>
+      <c r="AK64"/>
+      <c r="AL64"/>
+      <c r="AM64"/>
+      <c r="AN64"/>
       <c r="AO64" t="str">
         <f>Codex_calc!AO64</f>
         <v>2019, 2130</v>
@@ -8079,10 +7407,7 @@
         <f>Codex_calc!D65</f>
         <v>CUM</v>
       </c>
-      <c r="E65">
-        <f>Codex_calc!E65</f>
-        <v>0</v>
-      </c>
+      <c r="E65"/>
       <c r="F65">
         <f>Codex_calc!F65</f>
         <v>0</v>
@@ -8093,7 +7418,7 @@
       </c>
       <c r="H65">
         <f>Codex_calc!H65</f>
-        <v>654.005537634408</v>
+        <v>654.005537634409</v>
       </c>
       <c r="I65">
         <f>Codex_calc!I65</f>
@@ -8395,150 +7720,42 @@
         <f>Codex_calc!D67</f>
         <v>BNDACT</v>
       </c>
-      <c r="E67">
-        <f>Codex_calc!E67</f>
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <f>Codex_calc!F67</f>
-        <v>0</v>
-      </c>
-      <c r="G67">
-        <f>Codex_calc!G67</f>
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <f>Codex_calc!H67</f>
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <f>Codex_calc!I67</f>
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <f>Codex_calc!J67</f>
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <f>Codex_calc!K67</f>
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <f>Codex_calc!L67</f>
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <f>Codex_calc!M67</f>
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <f>Codex_calc!N67</f>
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <f>Codex_calc!O67</f>
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <f>Codex_calc!P67</f>
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <f>Codex_calc!Q67</f>
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <f>Codex_calc!R67</f>
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <f>Codex_calc!S67</f>
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <f>Codex_calc!T67</f>
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <f>Codex_calc!U67</f>
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <f>Codex_calc!V67</f>
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <f>Codex_calc!W67</f>
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <f>Codex_calc!X67</f>
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <f>Codex_calc!Y67</f>
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <f>Codex_calc!Z67</f>
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <f>Codex_calc!AA67</f>
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <f>Codex_calc!AB67</f>
-        <v>0</v>
-      </c>
-      <c r="AC67">
-        <f>Codex_calc!AC67</f>
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <f>Codex_calc!AD67</f>
-        <v>0</v>
-      </c>
-      <c r="AE67">
-        <f>Codex_calc!AE67</f>
-        <v>0</v>
-      </c>
-      <c r="AF67">
-        <f>Codex_calc!AF67</f>
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <f>Codex_calc!AG67</f>
-        <v>0</v>
-      </c>
-      <c r="AH67">
-        <f>Codex_calc!AH67</f>
-        <v>0</v>
-      </c>
-      <c r="AI67">
-        <f>Codex_calc!AI67</f>
-        <v>0</v>
-      </c>
-      <c r="AJ67">
-        <f>Codex_calc!AJ67</f>
-        <v>0</v>
-      </c>
-      <c r="AK67">
-        <f>Codex_calc!AK67</f>
-        <v>0</v>
-      </c>
-      <c r="AL67">
-        <f>Codex_calc!AL67</f>
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <f>Codex_calc!AM67</f>
-        <v>0</v>
-      </c>
-      <c r="AN67">
-        <f>Codex_calc!AN67</f>
-        <v>0</v>
-      </c>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="M67"/>
+      <c r="N67"/>
+      <c r="O67"/>
+      <c r="P67"/>
+      <c r="Q67"/>
+      <c r="R67"/>
+      <c r="S67"/>
+      <c r="T67"/>
+      <c r="U67"/>
+      <c r="V67"/>
+      <c r="W67"/>
+      <c r="X67"/>
+      <c r="Y67"/>
+      <c r="Z67"/>
+      <c r="AA67"/>
+      <c r="AB67"/>
+      <c r="AC67"/>
+      <c r="AD67"/>
+      <c r="AE67"/>
+      <c r="AF67"/>
+      <c r="AG67"/>
+      <c r="AH67"/>
+      <c r="AI67"/>
+      <c r="AJ67"/>
+      <c r="AK67"/>
+      <c r="AL67"/>
+      <c r="AM67"/>
+      <c r="AN67"/>
       <c r="AO67" t="str">
         <f>Codex_calc!AO67</f>
         <v>2019, 2130</v>
@@ -8553,10 +7770,7 @@
         <f>Codex_calc!D68</f>
         <v>CUM</v>
       </c>
-      <c r="E68">
-        <f>Codex_calc!E68</f>
-        <v>0</v>
-      </c>
+      <c r="E68"/>
       <c r="F68">
         <f>Codex_calc!F68</f>
         <v>0</v>
@@ -8567,7 +7781,7 @@
       </c>
       <c r="H68">
         <f>Codex_calc!H68</f>
-        <v>654.005537634408</v>
+        <v>654.005537634409</v>
       </c>
       <c r="I68">
         <f>Codex_calc!I68</f>
@@ -9026,150 +8240,42 @@
         <f>Codex_calc!D71</f>
         <v>BNDACT</v>
       </c>
-      <c r="E71">
-        <f>Codex_calc!E71</f>
-        <v>0</v>
-      </c>
-      <c r="F71">
-        <f>Codex_calc!F71</f>
-        <v>0</v>
-      </c>
-      <c r="G71">
-        <f>Codex_calc!G71</f>
-        <v>74.235</v>
-      </c>
-      <c r="H71">
-        <f>Codex_calc!H71</f>
-        <v>16.16</v>
-      </c>
-      <c r="I71">
-        <f>Codex_calc!I71</f>
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <f>Codex_calc!J71</f>
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <f>Codex_calc!K71</f>
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <f>Codex_calc!L71</f>
-        <v>8.08</v>
-      </c>
-      <c r="M71">
-        <f>Codex_calc!M71</f>
-        <v>7.07</v>
-      </c>
-      <c r="N71">
-        <f>Codex_calc!N71</f>
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <f>Codex_calc!O71</f>
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <f>Codex_calc!P71</f>
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <f>Codex_calc!Q71</f>
-        <v>0</v>
-      </c>
-      <c r="R71">
-        <f>Codex_calc!R71</f>
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <f>Codex_calc!S71</f>
-        <v>0</v>
-      </c>
-      <c r="T71">
-        <f>Codex_calc!T71</f>
-        <v>0</v>
-      </c>
-      <c r="U71">
-        <f>Codex_calc!U71</f>
-        <v>7.979</v>
-      </c>
-      <c r="V71">
-        <f>Codex_calc!V71</f>
-        <v>0</v>
-      </c>
-      <c r="W71">
-        <f>Codex_calc!W71</f>
-        <v>0</v>
-      </c>
-      <c r="X71">
-        <f>Codex_calc!X71</f>
-        <v>0</v>
-      </c>
-      <c r="Y71">
-        <f>Codex_calc!Y71</f>
-        <v>0</v>
-      </c>
-      <c r="Z71">
-        <f>Codex_calc!Z71</f>
-        <v>0</v>
-      </c>
-      <c r="AA71">
-        <f>Codex_calc!AA71</f>
-        <v>0</v>
-      </c>
-      <c r="AB71">
-        <f>Codex_calc!AB71</f>
-        <v>0</v>
-      </c>
-      <c r="AC71">
-        <f>Codex_calc!AC71</f>
-        <v>0</v>
-      </c>
-      <c r="AD71">
-        <f>Codex_calc!AD71</f>
-        <v>13.13</v>
-      </c>
-      <c r="AE71">
-        <f>Codex_calc!AE71</f>
-        <v>0</v>
-      </c>
-      <c r="AF71">
-        <f>Codex_calc!AF71</f>
-        <v>0</v>
-      </c>
-      <c r="AG71">
-        <f>Codex_calc!AG71</f>
-        <v>76.76</v>
-      </c>
-      <c r="AH71">
-        <f>Codex_calc!AH71</f>
-        <v>0</v>
-      </c>
-      <c r="AI71">
-        <f>Codex_calc!AI71</f>
-        <v>0</v>
-      </c>
-      <c r="AJ71">
-        <f>Codex_calc!AJ71</f>
-        <v>0</v>
-      </c>
-      <c r="AK71">
-        <f>Codex_calc!AK71</f>
-        <v>0</v>
-      </c>
-      <c r="AL71">
-        <f>Codex_calc!AL71</f>
-        <v>0</v>
-      </c>
-      <c r="AM71">
-        <f>Codex_calc!AM71</f>
-        <v>0</v>
-      </c>
-      <c r="AN71">
-        <f>Codex_calc!AN71</f>
-        <v>0</v>
-      </c>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
+      <c r="N71"/>
+      <c r="O71"/>
+      <c r="P71"/>
+      <c r="Q71"/>
+      <c r="R71"/>
+      <c r="S71"/>
+      <c r="T71"/>
+      <c r="U71"/>
+      <c r="V71"/>
+      <c r="W71"/>
+      <c r="X71"/>
+      <c r="Y71"/>
+      <c r="Z71"/>
+      <c r="AA71"/>
+      <c r="AB71"/>
+      <c r="AC71"/>
+      <c r="AD71"/>
+      <c r="AE71"/>
+      <c r="AF71"/>
+      <c r="AG71"/>
+      <c r="AH71"/>
+      <c r="AI71"/>
+      <c r="AJ71"/>
+      <c r="AK71"/>
+      <c r="AL71"/>
+      <c r="AM71"/>
+      <c r="AN71"/>
       <c r="AO71" t="str">
         <f>Codex_calc!AO71</f>
         <v>2019, 2130</v>
@@ -9184,10 +8290,7 @@
         <f>Codex_calc!D72</f>
         <v>CUM</v>
       </c>
-      <c r="E72">
-        <f>Codex_calc!E72</f>
-        <v>0</v>
-      </c>
+      <c r="E72"/>
       <c r="F72">
         <f>Codex_calc!F72</f>
         <v>0</v>
@@ -9500,150 +8603,42 @@
         <f>Codex_calc!D74</f>
         <v>BNDACT</v>
       </c>
-      <c r="E74">
-        <f>Codex_calc!E74</f>
-        <v>0</v>
-      </c>
-      <c r="F74">
-        <f>Codex_calc!F74</f>
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <f>Codex_calc!G74</f>
-        <v>148.47</v>
-      </c>
-      <c r="H74">
-        <f>Codex_calc!H74</f>
-        <v>32.32</v>
-      </c>
-      <c r="I74">
-        <f>Codex_calc!I74</f>
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <f>Codex_calc!J74</f>
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <f>Codex_calc!K74</f>
-        <v>0</v>
-      </c>
-      <c r="L74">
-        <f>Codex_calc!L74</f>
-        <v>16.16</v>
-      </c>
-      <c r="M74">
-        <f>Codex_calc!M74</f>
-        <v>14.14</v>
-      </c>
-      <c r="N74">
-        <f>Codex_calc!N74</f>
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <f>Codex_calc!O74</f>
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <f>Codex_calc!P74</f>
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <f>Codex_calc!Q74</f>
-        <v>0</v>
-      </c>
-      <c r="R74">
-        <f>Codex_calc!R74</f>
-        <v>0</v>
-      </c>
-      <c r="S74">
-        <f>Codex_calc!S74</f>
-        <v>0</v>
-      </c>
-      <c r="T74">
-        <f>Codex_calc!T74</f>
-        <v>0</v>
-      </c>
-      <c r="U74">
-        <f>Codex_calc!U74</f>
-        <v>15.958</v>
-      </c>
-      <c r="V74">
-        <f>Codex_calc!V74</f>
-        <v>0</v>
-      </c>
-      <c r="W74">
-        <f>Codex_calc!W74</f>
-        <v>0</v>
-      </c>
-      <c r="X74">
-        <f>Codex_calc!X74</f>
-        <v>0</v>
-      </c>
-      <c r="Y74">
-        <f>Codex_calc!Y74</f>
-        <v>0</v>
-      </c>
-      <c r="Z74">
-        <f>Codex_calc!Z74</f>
-        <v>0</v>
-      </c>
-      <c r="AA74">
-        <f>Codex_calc!AA74</f>
-        <v>0</v>
-      </c>
-      <c r="AB74">
-        <f>Codex_calc!AB74</f>
-        <v>0</v>
-      </c>
-      <c r="AC74">
-        <f>Codex_calc!AC74</f>
-        <v>0</v>
-      </c>
-      <c r="AD74">
-        <f>Codex_calc!AD74</f>
-        <v>26.26</v>
-      </c>
-      <c r="AE74">
-        <f>Codex_calc!AE74</f>
-        <v>0</v>
-      </c>
-      <c r="AF74">
-        <f>Codex_calc!AF74</f>
-        <v>0</v>
-      </c>
-      <c r="AG74">
-        <f>Codex_calc!AG74</f>
-        <v>153.52</v>
-      </c>
-      <c r="AH74">
-        <f>Codex_calc!AH74</f>
-        <v>0</v>
-      </c>
-      <c r="AI74">
-        <f>Codex_calc!AI74</f>
-        <v>0</v>
-      </c>
-      <c r="AJ74">
-        <f>Codex_calc!AJ74</f>
-        <v>0</v>
-      </c>
-      <c r="AK74">
-        <f>Codex_calc!AK74</f>
-        <v>0</v>
-      </c>
-      <c r="AL74">
-        <f>Codex_calc!AL74</f>
-        <v>0</v>
-      </c>
-      <c r="AM74">
-        <f>Codex_calc!AM74</f>
-        <v>0</v>
-      </c>
-      <c r="AN74">
-        <f>Codex_calc!AN74</f>
-        <v>0</v>
-      </c>
+      <c r="E74"/>
+      <c r="F74"/>
+      <c r="G74"/>
+      <c r="H74"/>
+      <c r="I74"/>
+      <c r="J74"/>
+      <c r="K74"/>
+      <c r="L74"/>
+      <c r="M74"/>
+      <c r="N74"/>
+      <c r="O74"/>
+      <c r="P74"/>
+      <c r="Q74"/>
+      <c r="R74"/>
+      <c r="S74"/>
+      <c r="T74"/>
+      <c r="U74"/>
+      <c r="V74"/>
+      <c r="W74"/>
+      <c r="X74"/>
+      <c r="Y74"/>
+      <c r="Z74"/>
+      <c r="AA74"/>
+      <c r="AB74"/>
+      <c r="AC74"/>
+      <c r="AD74"/>
+      <c r="AE74"/>
+      <c r="AF74"/>
+      <c r="AG74"/>
+      <c r="AH74"/>
+      <c r="AI74"/>
+      <c r="AJ74"/>
+      <c r="AK74"/>
+      <c r="AL74"/>
+      <c r="AM74"/>
+      <c r="AN74"/>
       <c r="AO74" t="str">
         <f>Codex_calc!AO74</f>
         <v>2019, 2130</v>
@@ -9658,10 +8653,7 @@
         <f>Codex_calc!D75</f>
         <v>CUM</v>
       </c>
-      <c r="E75">
-        <f>Codex_calc!E75</f>
-        <v>0</v>
-      </c>
+      <c r="E75"/>
       <c r="F75">
         <f>Codex_calc!F75</f>
         <v>0</v>
@@ -9692,7 +8684,7 @@
       </c>
       <c r="M75">
         <f>Codex_calc!M75</f>
-        <v>11087.5555555556</v>
+        <v>11087.5555555555</v>
       </c>
       <c r="N75">
         <f>Codex_calc!N75</f>
@@ -9760,7 +8752,7 @@
       </c>
       <c r="AD75">
         <f>Codex_calc!AD75</f>
-        <v>85.2888888888889</v>
+        <v>85.2888888888888</v>
       </c>
       <c r="AE75">
         <f>Codex_calc!AE75</f>
@@ -9974,150 +8966,42 @@
         <f>Codex_calc!D77</f>
         <v>BNDACT</v>
       </c>
-      <c r="E77">
-        <f>Codex_calc!E77</f>
-        <v>0</v>
-      </c>
-      <c r="F77">
-        <f>Codex_calc!F77</f>
-        <v>0</v>
-      </c>
-      <c r="G77">
-        <f>Codex_calc!G77</f>
-        <v>0</v>
-      </c>
-      <c r="H77">
-        <f>Codex_calc!H77</f>
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <f>Codex_calc!I77</f>
-        <v>0</v>
-      </c>
-      <c r="J77">
-        <f>Codex_calc!J77</f>
-        <v>0</v>
-      </c>
-      <c r="K77">
-        <f>Codex_calc!K77</f>
-        <v>0</v>
-      </c>
-      <c r="L77">
-        <f>Codex_calc!L77</f>
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <f>Codex_calc!M77</f>
-        <v>0</v>
-      </c>
-      <c r="N77">
-        <f>Codex_calc!N77</f>
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <f>Codex_calc!O77</f>
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <f>Codex_calc!P77</f>
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <f>Codex_calc!Q77</f>
-        <v>0</v>
-      </c>
-      <c r="R77">
-        <f>Codex_calc!R77</f>
-        <v>0</v>
-      </c>
-      <c r="S77">
-        <f>Codex_calc!S77</f>
-        <v>0</v>
-      </c>
-      <c r="T77">
-        <f>Codex_calc!T77</f>
-        <v>0</v>
-      </c>
-      <c r="U77">
-        <f>Codex_calc!U77</f>
-        <v>0</v>
-      </c>
-      <c r="V77">
-        <f>Codex_calc!V77</f>
-        <v>0</v>
-      </c>
-      <c r="W77">
-        <f>Codex_calc!W77</f>
-        <v>0</v>
-      </c>
-      <c r="X77">
-        <f>Codex_calc!X77</f>
-        <v>0</v>
-      </c>
-      <c r="Y77">
-        <f>Codex_calc!Y77</f>
-        <v>0</v>
-      </c>
-      <c r="Z77">
-        <f>Codex_calc!Z77</f>
-        <v>0</v>
-      </c>
-      <c r="AA77">
-        <f>Codex_calc!AA77</f>
-        <v>0</v>
-      </c>
-      <c r="AB77">
-        <f>Codex_calc!AB77</f>
-        <v>0</v>
-      </c>
-      <c r="AC77">
-        <f>Codex_calc!AC77</f>
-        <v>0</v>
-      </c>
-      <c r="AD77">
-        <f>Codex_calc!AD77</f>
-        <v>0</v>
-      </c>
-      <c r="AE77">
-        <f>Codex_calc!AE77</f>
-        <v>0</v>
-      </c>
-      <c r="AF77">
-        <f>Codex_calc!AF77</f>
-        <v>0</v>
-      </c>
-      <c r="AG77">
-        <f>Codex_calc!AG77</f>
-        <v>0</v>
-      </c>
-      <c r="AH77">
-        <f>Codex_calc!AH77</f>
-        <v>0</v>
-      </c>
-      <c r="AI77">
-        <f>Codex_calc!AI77</f>
-        <v>0</v>
-      </c>
-      <c r="AJ77">
-        <f>Codex_calc!AJ77</f>
-        <v>0</v>
-      </c>
-      <c r="AK77">
-        <f>Codex_calc!AK77</f>
-        <v>0</v>
-      </c>
-      <c r="AL77">
-        <f>Codex_calc!AL77</f>
-        <v>0</v>
-      </c>
-      <c r="AM77">
-        <f>Codex_calc!AM77</f>
-        <v>0</v>
-      </c>
-      <c r="AN77">
-        <f>Codex_calc!AN77</f>
-        <v>0</v>
-      </c>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77"/>
+      <c r="I77"/>
+      <c r="J77"/>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="M77"/>
+      <c r="N77"/>
+      <c r="O77"/>
+      <c r="P77"/>
+      <c r="Q77"/>
+      <c r="R77"/>
+      <c r="S77"/>
+      <c r="T77"/>
+      <c r="U77"/>
+      <c r="V77"/>
+      <c r="W77"/>
+      <c r="X77"/>
+      <c r="Y77"/>
+      <c r="Z77"/>
+      <c r="AA77"/>
+      <c r="AB77"/>
+      <c r="AC77"/>
+      <c r="AD77"/>
+      <c r="AE77"/>
+      <c r="AF77"/>
+      <c r="AG77"/>
+      <c r="AH77"/>
+      <c r="AI77"/>
+      <c r="AJ77"/>
+      <c r="AK77"/>
+      <c r="AL77"/>
+      <c r="AM77"/>
+      <c r="AN77"/>
       <c r="AO77" t="str">
         <f>Codex_calc!AO77</f>
         <v>2019, 2130</v>
@@ -10132,10 +9016,7 @@
         <f>Codex_calc!D78</f>
         <v>CUM</v>
       </c>
-      <c r="E78">
-        <f>Codex_calc!E78</f>
-        <v>0</v>
-      </c>
+      <c r="E78"/>
       <c r="F78">
         <f>Codex_calc!F78</f>
         <v>0</v>
@@ -10166,7 +9047,7 @@
       </c>
       <c r="M78">
         <f>Codex_calc!M78</f>
-        <v>11087.5555555556</v>
+        <v>11087.5555555555</v>
       </c>
       <c r="N78">
         <f>Codex_calc!N78</f>
@@ -10234,7 +9115,7 @@
       </c>
       <c r="AD78">
         <f>Codex_calc!AD78</f>
-        <v>85.2888888888889</v>
+        <v>85.2888888888888</v>
       </c>
       <c r="AE78">
         <f>Codex_calc!AE78</f>
@@ -10605,150 +9486,6 @@
         <f>Codex_calc!D81</f>
         <v>BNDACT</v>
       </c>
-      <c r="E81">
-        <f>Codex_calc!E81</f>
-        <v>0</v>
-      </c>
-      <c r="F81">
-        <f>Codex_calc!F81</f>
-        <v>0</v>
-      </c>
-      <c r="G81">
-        <f>Codex_calc!G81</f>
-        <v>0</v>
-      </c>
-      <c r="H81">
-        <f>Codex_calc!H81</f>
-        <v>30.1272972972973</v>
-      </c>
-      <c r="I81">
-        <f>Codex_calc!I81</f>
-        <v>0</v>
-      </c>
-      <c r="J81">
-        <f>Codex_calc!J81</f>
-        <v>0</v>
-      </c>
-      <c r="K81">
-        <f>Codex_calc!K81</f>
-        <v>0</v>
-      </c>
-      <c r="L81">
-        <f>Codex_calc!L81</f>
-        <v>24.1018378378378</v>
-      </c>
-      <c r="M81">
-        <f>Codex_calc!M81</f>
-        <v>903.818918918919</v>
-      </c>
-      <c r="N81">
-        <f>Codex_calc!N81</f>
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <f>Codex_calc!O81</f>
-        <v>0</v>
-      </c>
-      <c r="P81">
-        <f>Codex_calc!P81</f>
-        <v>0</v>
-      </c>
-      <c r="Q81">
-        <f>Codex_calc!Q81</f>
-        <v>0</v>
-      </c>
-      <c r="R81">
-        <f>Codex_calc!R81</f>
-        <v>0</v>
-      </c>
-      <c r="S81">
-        <f>Codex_calc!S81</f>
-        <v>0</v>
-      </c>
-      <c r="T81">
-        <f>Codex_calc!T81</f>
-        <v>15.0636486486486</v>
-      </c>
-      <c r="U81">
-        <f>Codex_calc!U81</f>
-        <v>84.3564324324324</v>
-      </c>
-      <c r="V81">
-        <f>Codex_calc!V81</f>
-        <v>0</v>
-      </c>
-      <c r="W81">
-        <f>Codex_calc!W81</f>
-        <v>0</v>
-      </c>
-      <c r="X81">
-        <f>Codex_calc!X81</f>
-        <v>0</v>
-      </c>
-      <c r="Y81">
-        <f>Codex_calc!Y81</f>
-        <v>0</v>
-      </c>
-      <c r="Z81">
-        <f>Codex_calc!Z81</f>
-        <v>86.3649189189189</v>
-      </c>
-      <c r="AA81">
-        <f>Codex_calc!AA81</f>
-        <v>79.5360648648649</v>
-      </c>
-      <c r="AB81">
-        <f>Codex_calc!AB81</f>
-        <v>26.1103243243243</v>
-      </c>
-      <c r="AC81">
-        <f>Codex_calc!AC81</f>
-        <v>0</v>
-      </c>
-      <c r="AD81">
-        <f>Codex_calc!AD81</f>
-        <v>162.687405405405</v>
-      </c>
-      <c r="AE81">
-        <f>Codex_calc!AE81</f>
-        <v>78.330972972973</v>
-      </c>
-      <c r="AF81">
-        <f>Codex_calc!AF81</f>
-        <v>0</v>
-      </c>
-      <c r="AG81">
-        <f>Codex_calc!AG81</f>
-        <v>0</v>
-      </c>
-      <c r="AH81">
-        <f>Codex_calc!AH81</f>
-        <v>0</v>
-      </c>
-      <c r="AI81">
-        <f>Codex_calc!AI81</f>
-        <v>0</v>
-      </c>
-      <c r="AJ81">
-        <f>Codex_calc!AJ81</f>
-        <v>0</v>
-      </c>
-      <c r="AK81">
-        <f>Codex_calc!AK81</f>
-        <v>0</v>
-      </c>
-      <c r="AL81">
-        <f>Codex_calc!AL81</f>
-        <v>0</v>
-      </c>
-      <c r="AM81">
-        <f>Codex_calc!AM81</f>
-        <v>0</v>
-      </c>
-      <c r="AN81">
-        <f>Codex_calc!AN81</f>
-        <v>0</v>
-      </c>
       <c r="AO81" t="str">
         <f>Codex_calc!AO81</f>
         <v>2019, 2130</v>
@@ -10763,10 +9500,7 @@
         <f>Codex_calc!D82</f>
         <v>CUM</v>
       </c>
-      <c r="E82">
-        <f>Codex_calc!E82</f>
-        <v>0</v>
-      </c>
+      <c r="E82"/>
       <c r="F82">
         <f>Codex_calc!F82</f>
         <v>0</v>
@@ -11079,150 +9813,6 @@
         <f>Codex_calc!D84</f>
         <v>BNDACT</v>
       </c>
-      <c r="E84">
-        <f>Codex_calc!E84</f>
-        <v>0</v>
-      </c>
-      <c r="F84">
-        <f>Codex_calc!F84</f>
-        <v>0</v>
-      </c>
-      <c r="G84">
-        <f>Codex_calc!G84</f>
-        <v>0</v>
-      </c>
-      <c r="H84">
-        <f>Codex_calc!H84</f>
-        <v>60.2545945945946</v>
-      </c>
-      <c r="I84">
-        <f>Codex_calc!I84</f>
-        <v>0</v>
-      </c>
-      <c r="J84">
-        <f>Codex_calc!J84</f>
-        <v>0</v>
-      </c>
-      <c r="K84">
-        <f>Codex_calc!K84</f>
-        <v>0</v>
-      </c>
-      <c r="L84">
-        <f>Codex_calc!L84</f>
-        <v>48.2036756756757</v>
-      </c>
-      <c r="M84">
-        <f>Codex_calc!M84</f>
-        <v>1807.63783783784</v>
-      </c>
-      <c r="N84">
-        <f>Codex_calc!N84</f>
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <f>Codex_calc!O84</f>
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <f>Codex_calc!P84</f>
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <f>Codex_calc!Q84</f>
-        <v>0</v>
-      </c>
-      <c r="R84">
-        <f>Codex_calc!R84</f>
-        <v>0</v>
-      </c>
-      <c r="S84">
-        <f>Codex_calc!S84</f>
-        <v>0</v>
-      </c>
-      <c r="T84">
-        <f>Codex_calc!T84</f>
-        <v>30.1272972972973</v>
-      </c>
-      <c r="U84">
-        <f>Codex_calc!U84</f>
-        <v>168.712864864865</v>
-      </c>
-      <c r="V84">
-        <f>Codex_calc!V84</f>
-        <v>0</v>
-      </c>
-      <c r="W84">
-        <f>Codex_calc!W84</f>
-        <v>0</v>
-      </c>
-      <c r="X84">
-        <f>Codex_calc!X84</f>
-        <v>0</v>
-      </c>
-      <c r="Y84">
-        <f>Codex_calc!Y84</f>
-        <v>0</v>
-      </c>
-      <c r="Z84">
-        <f>Codex_calc!Z84</f>
-        <v>172.729837837838</v>
-      </c>
-      <c r="AA84">
-        <f>Codex_calc!AA84</f>
-        <v>159.07212972973</v>
-      </c>
-      <c r="AB84">
-        <f>Codex_calc!AB84</f>
-        <v>52.2206486486486</v>
-      </c>
-      <c r="AC84">
-        <f>Codex_calc!AC84</f>
-        <v>0</v>
-      </c>
-      <c r="AD84">
-        <f>Codex_calc!AD84</f>
-        <v>325.374810810811</v>
-      </c>
-      <c r="AE84">
-        <f>Codex_calc!AE84</f>
-        <v>156.661945945946</v>
-      </c>
-      <c r="AF84">
-        <f>Codex_calc!AF84</f>
-        <v>0</v>
-      </c>
-      <c r="AG84">
-        <f>Codex_calc!AG84</f>
-        <v>0</v>
-      </c>
-      <c r="AH84">
-        <f>Codex_calc!AH84</f>
-        <v>0</v>
-      </c>
-      <c r="AI84">
-        <f>Codex_calc!AI84</f>
-        <v>0</v>
-      </c>
-      <c r="AJ84">
-        <f>Codex_calc!AJ84</f>
-        <v>0</v>
-      </c>
-      <c r="AK84">
-        <f>Codex_calc!AK84</f>
-        <v>0</v>
-      </c>
-      <c r="AL84">
-        <f>Codex_calc!AL84</f>
-        <v>0</v>
-      </c>
-      <c r="AM84">
-        <f>Codex_calc!AM84</f>
-        <v>0</v>
-      </c>
-      <c r="AN84">
-        <f>Codex_calc!AN84</f>
-        <v>0</v>
-      </c>
       <c r="AO84" t="str">
         <f>Codex_calc!AO84</f>
         <v>2019, 2130</v>
@@ -11237,10 +9827,7 @@
         <f>Codex_calc!D85</f>
         <v>CUM</v>
       </c>
-      <c r="E85">
-        <f>Codex_calc!E85</f>
-        <v>0</v>
-      </c>
+      <c r="E85"/>
       <c r="F85">
         <f>Codex_calc!F85</f>
         <v>0</v>
@@ -11553,150 +10140,42 @@
         <f>Codex_calc!D87</f>
         <v>BNDACT</v>
       </c>
-      <c r="E87">
-        <f>Codex_calc!E87</f>
-        <v>0</v>
-      </c>
-      <c r="F87">
-        <f>Codex_calc!F87</f>
-        <v>0</v>
-      </c>
-      <c r="G87">
-        <f>Codex_calc!G87</f>
-        <v>0</v>
-      </c>
-      <c r="H87">
-        <f>Codex_calc!H87</f>
-        <v>0</v>
-      </c>
-      <c r="I87">
-        <f>Codex_calc!I87</f>
-        <v>0</v>
-      </c>
-      <c r="J87">
-        <f>Codex_calc!J87</f>
-        <v>0</v>
-      </c>
-      <c r="K87">
-        <f>Codex_calc!K87</f>
-        <v>0</v>
-      </c>
-      <c r="L87">
-        <f>Codex_calc!L87</f>
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <f>Codex_calc!M87</f>
-        <v>0</v>
-      </c>
-      <c r="N87">
-        <f>Codex_calc!N87</f>
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <f>Codex_calc!O87</f>
-        <v>0</v>
-      </c>
-      <c r="P87">
-        <f>Codex_calc!P87</f>
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <f>Codex_calc!Q87</f>
-        <v>0</v>
-      </c>
-      <c r="R87">
-        <f>Codex_calc!R87</f>
-        <v>0</v>
-      </c>
-      <c r="S87">
-        <f>Codex_calc!S87</f>
-        <v>0</v>
-      </c>
-      <c r="T87">
-        <f>Codex_calc!T87</f>
-        <v>0</v>
-      </c>
-      <c r="U87">
-        <f>Codex_calc!U87</f>
-        <v>0</v>
-      </c>
-      <c r="V87">
-        <f>Codex_calc!V87</f>
-        <v>0</v>
-      </c>
-      <c r="W87">
-        <f>Codex_calc!W87</f>
-        <v>0</v>
-      </c>
-      <c r="X87">
-        <f>Codex_calc!X87</f>
-        <v>0</v>
-      </c>
-      <c r="Y87">
-        <f>Codex_calc!Y87</f>
-        <v>0</v>
-      </c>
-      <c r="Z87">
-        <f>Codex_calc!Z87</f>
-        <v>0</v>
-      </c>
-      <c r="AA87">
-        <f>Codex_calc!AA87</f>
-        <v>0</v>
-      </c>
-      <c r="AB87">
-        <f>Codex_calc!AB87</f>
-        <v>0</v>
-      </c>
-      <c r="AC87">
-        <f>Codex_calc!AC87</f>
-        <v>0</v>
-      </c>
-      <c r="AD87">
-        <f>Codex_calc!AD87</f>
-        <v>0</v>
-      </c>
-      <c r="AE87">
-        <f>Codex_calc!AE87</f>
-        <v>0</v>
-      </c>
-      <c r="AF87">
-        <f>Codex_calc!AF87</f>
-        <v>0</v>
-      </c>
-      <c r="AG87">
-        <f>Codex_calc!AG87</f>
-        <v>0</v>
-      </c>
-      <c r="AH87">
-        <f>Codex_calc!AH87</f>
-        <v>0</v>
-      </c>
-      <c r="AI87">
-        <f>Codex_calc!AI87</f>
-        <v>0</v>
-      </c>
-      <c r="AJ87">
-        <f>Codex_calc!AJ87</f>
-        <v>0</v>
-      </c>
-      <c r="AK87">
-        <f>Codex_calc!AK87</f>
-        <v>0</v>
-      </c>
-      <c r="AL87">
-        <f>Codex_calc!AL87</f>
-        <v>0</v>
-      </c>
-      <c r="AM87">
-        <f>Codex_calc!AM87</f>
-        <v>0</v>
-      </c>
-      <c r="AN87">
-        <f>Codex_calc!AN87</f>
-        <v>0</v>
-      </c>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="I87"/>
+      <c r="J87"/>
+      <c r="K87"/>
+      <c r="L87"/>
+      <c r="M87"/>
+      <c r="N87"/>
+      <c r="O87"/>
+      <c r="P87"/>
+      <c r="Q87"/>
+      <c r="R87"/>
+      <c r="S87"/>
+      <c r="T87"/>
+      <c r="U87"/>
+      <c r="V87"/>
+      <c r="W87"/>
+      <c r="X87"/>
+      <c r="Y87"/>
+      <c r="Z87"/>
+      <c r="AA87"/>
+      <c r="AB87"/>
+      <c r="AC87"/>
+      <c r="AD87"/>
+      <c r="AE87"/>
+      <c r="AF87"/>
+      <c r="AG87"/>
+      <c r="AH87"/>
+      <c r="AI87"/>
+      <c r="AJ87"/>
+      <c r="AK87"/>
+      <c r="AL87"/>
+      <c r="AM87"/>
+      <c r="AN87"/>
       <c r="AO87" t="str">
         <f>Codex_calc!AO87</f>
         <v>2019, 2130</v>
@@ -11711,150 +10190,42 @@
         <f>Codex_calc!D88</f>
         <v>CUM</v>
       </c>
-      <c r="E88">
-        <f>Codex_calc!E88</f>
-        <v>0</v>
-      </c>
-      <c r="F88">
-        <f>Codex_calc!F88</f>
-        <v>0</v>
-      </c>
-      <c r="G88">
-        <f>Codex_calc!G88</f>
-        <v>12812.7586206897</v>
-      </c>
-      <c r="H88">
-        <f>Codex_calc!H88</f>
-        <v>6406.37931034483</v>
-      </c>
-      <c r="I88">
-        <f>Codex_calc!I88</f>
-        <v>0</v>
-      </c>
-      <c r="J88">
-        <f>Codex_calc!J88</f>
-        <v>0</v>
-      </c>
-      <c r="K88">
-        <f>Codex_calc!K88</f>
-        <v>0</v>
-      </c>
-      <c r="L88">
-        <f>Codex_calc!L88</f>
-        <v>2943.4715750233</v>
-      </c>
-      <c r="M88">
-        <f>Codex_calc!M88</f>
-        <v>1229.33224603914</v>
-      </c>
-      <c r="N88">
-        <f>Codex_calc!N88</f>
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <f>Codex_calc!O88</f>
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <f>Codex_calc!P88</f>
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <f>Codex_calc!Q88</f>
-        <v>0</v>
-      </c>
-      <c r="R88">
-        <f>Codex_calc!R88</f>
-        <v>0</v>
-      </c>
-      <c r="S88">
-        <f>Codex_calc!S88</f>
-        <v>0</v>
-      </c>
-      <c r="T88">
-        <f>Codex_calc!T88</f>
-        <v>0</v>
-      </c>
-      <c r="U88">
-        <f>Codex_calc!U88</f>
-        <v>1125.4450139795</v>
-      </c>
-      <c r="V88">
-        <f>Codex_calc!V88</f>
-        <v>0</v>
-      </c>
-      <c r="W88">
-        <f>Codex_calc!W88</f>
-        <v>0</v>
-      </c>
-      <c r="X88">
-        <f>Codex_calc!X88</f>
-        <v>0</v>
-      </c>
-      <c r="Y88">
-        <f>Codex_calc!Y88</f>
-        <v>3462.90773532153</v>
-      </c>
-      <c r="Z88">
-        <f>Codex_calc!Z88</f>
-        <v>0</v>
-      </c>
-      <c r="AA88">
-        <f>Codex_calc!AA88</f>
-        <v>34.6290773532153</v>
-      </c>
-      <c r="AB88">
-        <f>Codex_calc!AB88</f>
-        <v>0</v>
-      </c>
-      <c r="AC88">
-        <f>Codex_calc!AC88</f>
-        <v>0</v>
-      </c>
-      <c r="AD88">
-        <f>Codex_calc!AD88</f>
-        <v>19842.4613233924</v>
-      </c>
-      <c r="AE88">
-        <f>Codex_calc!AE88</f>
-        <v>1125.4450139795</v>
-      </c>
-      <c r="AF88">
-        <f>Codex_calc!AF88</f>
-        <v>311.661696178938</v>
-      </c>
-      <c r="AG88">
-        <f>Codex_calc!AG88</f>
-        <v>0</v>
-      </c>
-      <c r="AH88">
-        <f>Codex_calc!AH88</f>
-        <v>0</v>
-      </c>
-      <c r="AI88">
-        <f>Codex_calc!AI88</f>
-        <v>0</v>
-      </c>
-      <c r="AJ88">
-        <f>Codex_calc!AJ88</f>
-        <v>0</v>
-      </c>
-      <c r="AK88">
-        <f>Codex_calc!AK88</f>
-        <v>119.470316868593</v>
-      </c>
-      <c r="AL88">
-        <f>Codex_calc!AL88</f>
-        <v>0</v>
-      </c>
-      <c r="AM88">
-        <f>Codex_calc!AM88</f>
-        <v>0</v>
-      </c>
-      <c r="AN88">
-        <f>Codex_calc!AN88</f>
-        <v>0</v>
-      </c>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="I88"/>
+      <c r="J88"/>
+      <c r="K88"/>
+      <c r="L88"/>
+      <c r="M88"/>
+      <c r="N88"/>
+      <c r="O88"/>
+      <c r="P88"/>
+      <c r="Q88"/>
+      <c r="R88"/>
+      <c r="S88"/>
+      <c r="T88"/>
+      <c r="U88"/>
+      <c r="V88"/>
+      <c r="W88"/>
+      <c r="X88"/>
+      <c r="Y88"/>
+      <c r="Z88"/>
+      <c r="AA88"/>
+      <c r="AB88"/>
+      <c r="AC88"/>
+      <c r="AD88"/>
+      <c r="AE88"/>
+      <c r="AF88"/>
+      <c r="AG88"/>
+      <c r="AH88"/>
+      <c r="AI88"/>
+      <c r="AJ88"/>
+      <c r="AK88"/>
+      <c r="AL88"/>
+      <c r="AM88"/>
+      <c r="AN88"/>
       <c r="AO88" t="str">
         <f>Codex_calc!AO88</f>
         <v>2019, 2130</v>
@@ -12184,150 +10555,42 @@
         <f>Codex_calc!D91</f>
         <v>BNDACT</v>
       </c>
-      <c r="E91">
-        <f>Codex_calc!E91</f>
-        <v>0</v>
-      </c>
-      <c r="F91">
-        <f>Codex_calc!F91</f>
-        <v>0</v>
-      </c>
-      <c r="G91">
-        <f>Codex_calc!G91</f>
-        <v>102.6</v>
-      </c>
-      <c r="H91">
-        <f>Codex_calc!H91</f>
-        <v>18.0913043478261</v>
-      </c>
-      <c r="I91">
-        <f>Codex_calc!I91</f>
-        <v>0</v>
-      </c>
-      <c r="J91">
-        <f>Codex_calc!J91</f>
-        <v>0</v>
-      </c>
-      <c r="K91">
-        <f>Codex_calc!K91</f>
-        <v>0</v>
-      </c>
-      <c r="L91">
-        <f>Codex_calc!L91</f>
-        <v>0</v>
-      </c>
-      <c r="M91">
-        <f>Codex_calc!M91</f>
-        <v>44.6086956521739</v>
-      </c>
-      <c r="N91">
-        <f>Codex_calc!N91</f>
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <f>Codex_calc!O91</f>
-        <v>0</v>
-      </c>
-      <c r="P91">
-        <f>Codex_calc!P91</f>
-        <v>0</v>
-      </c>
-      <c r="Q91">
-        <f>Codex_calc!Q91</f>
-        <v>0</v>
-      </c>
-      <c r="R91">
-        <f>Codex_calc!R91</f>
-        <v>0</v>
-      </c>
-      <c r="S91">
-        <f>Codex_calc!S91</f>
-        <v>0</v>
-      </c>
-      <c r="T91">
-        <f>Codex_calc!T91</f>
-        <v>0</v>
-      </c>
-      <c r="U91">
-        <f>Codex_calc!U91</f>
-        <v>0.57</v>
-      </c>
-      <c r="V91">
-        <f>Codex_calc!V91</f>
-        <v>0</v>
-      </c>
-      <c r="W91">
-        <f>Codex_calc!W91</f>
-        <v>0</v>
-      </c>
-      <c r="X91">
-        <f>Codex_calc!X91</f>
-        <v>0</v>
-      </c>
-      <c r="Y91">
-        <f>Codex_calc!Y91</f>
-        <v>198.260869565217</v>
-      </c>
-      <c r="Z91">
-        <f>Codex_calc!Z91</f>
-        <v>0</v>
-      </c>
-      <c r="AA91">
-        <f>Codex_calc!AA91</f>
-        <v>54.2739130434783</v>
-      </c>
-      <c r="AB91">
-        <f>Codex_calc!AB91</f>
-        <v>0</v>
-      </c>
-      <c r="AC91">
-        <f>Codex_calc!AC91</f>
-        <v>10.1608695652174</v>
-      </c>
-      <c r="AD91">
-        <f>Codex_calc!AD91</f>
-        <v>109.539130434783</v>
-      </c>
-      <c r="AE91">
-        <f>Codex_calc!AE91</f>
-        <v>32.2173913043478</v>
-      </c>
-      <c r="AF91">
-        <f>Codex_calc!AF91</f>
-        <v>0</v>
-      </c>
-      <c r="AG91">
-        <f>Codex_calc!AG91</f>
-        <v>0</v>
-      </c>
-      <c r="AH91">
-        <f>Codex_calc!AH91</f>
-        <v>0</v>
-      </c>
-      <c r="AI91">
-        <f>Codex_calc!AI91</f>
-        <v>0</v>
-      </c>
-      <c r="AJ91">
-        <f>Codex_calc!AJ91</f>
-        <v>0</v>
-      </c>
-      <c r="AK91">
-        <f>Codex_calc!AK91</f>
-        <v>0</v>
-      </c>
-      <c r="AL91">
-        <f>Codex_calc!AL91</f>
-        <v>0</v>
-      </c>
-      <c r="AM91">
-        <f>Codex_calc!AM91</f>
-        <v>0</v>
-      </c>
-      <c r="AN91">
-        <f>Codex_calc!AN91</f>
-        <v>0</v>
-      </c>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91"/>
+      <c r="I91"/>
+      <c r="J91"/>
+      <c r="K91"/>
+      <c r="L91"/>
+      <c r="M91"/>
+      <c r="N91"/>
+      <c r="O91"/>
+      <c r="P91"/>
+      <c r="Q91"/>
+      <c r="R91"/>
+      <c r="S91"/>
+      <c r="T91"/>
+      <c r="U91"/>
+      <c r="V91"/>
+      <c r="W91"/>
+      <c r="X91"/>
+      <c r="Y91"/>
+      <c r="Z91"/>
+      <c r="AA91"/>
+      <c r="AB91"/>
+      <c r="AC91"/>
+      <c r="AD91"/>
+      <c r="AE91"/>
+      <c r="AF91"/>
+      <c r="AG91"/>
+      <c r="AH91"/>
+      <c r="AI91"/>
+      <c r="AJ91"/>
+      <c r="AK91"/>
+      <c r="AL91"/>
+      <c r="AM91"/>
+      <c r="AN91"/>
       <c r="AO91" t="str">
         <f>Codex_calc!AO91</f>
         <v>2019, 2130</v>
@@ -12342,10 +10605,7 @@
         <f>Codex_calc!D92</f>
         <v>CUM</v>
       </c>
-      <c r="E92">
-        <f>Codex_calc!E92</f>
-        <v>0</v>
-      </c>
+      <c r="E92"/>
       <c r="F92">
         <f>Codex_calc!F92</f>
         <v>0</v>
@@ -12658,150 +10918,42 @@
         <f>Codex_calc!D94</f>
         <v>BNDACT</v>
       </c>
-      <c r="E94">
-        <f>Codex_calc!E94</f>
-        <v>0</v>
-      </c>
-      <c r="F94">
-        <f>Codex_calc!F94</f>
-        <v>0</v>
-      </c>
-      <c r="G94">
-        <f>Codex_calc!G94</f>
-        <v>205.2</v>
-      </c>
-      <c r="H94">
-        <f>Codex_calc!H94</f>
-        <v>36.1826086956522</v>
-      </c>
-      <c r="I94">
-        <f>Codex_calc!I94</f>
-        <v>0</v>
-      </c>
-      <c r="J94">
-        <f>Codex_calc!J94</f>
-        <v>0</v>
-      </c>
-      <c r="K94">
-        <f>Codex_calc!K94</f>
-        <v>0</v>
-      </c>
-      <c r="L94">
-        <f>Codex_calc!L94</f>
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <f>Codex_calc!M94</f>
-        <v>89.2173913043478</v>
-      </c>
-      <c r="N94">
-        <f>Codex_calc!N94</f>
-        <v>0</v>
-      </c>
-      <c r="O94">
-        <f>Codex_calc!O94</f>
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <f>Codex_calc!P94</f>
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <f>Codex_calc!Q94</f>
-        <v>0</v>
-      </c>
-      <c r="R94">
-        <f>Codex_calc!R94</f>
-        <v>0</v>
-      </c>
-      <c r="S94">
-        <f>Codex_calc!S94</f>
-        <v>0</v>
-      </c>
-      <c r="T94">
-        <f>Codex_calc!T94</f>
-        <v>0</v>
-      </c>
-      <c r="U94">
-        <f>Codex_calc!U94</f>
-        <v>1.14</v>
-      </c>
-      <c r="V94">
-        <f>Codex_calc!V94</f>
-        <v>0</v>
-      </c>
-      <c r="W94">
-        <f>Codex_calc!W94</f>
-        <v>0</v>
-      </c>
-      <c r="X94">
-        <f>Codex_calc!X94</f>
-        <v>0</v>
-      </c>
-      <c r="Y94">
-        <f>Codex_calc!Y94</f>
-        <v>396.521739130435</v>
-      </c>
-      <c r="Z94">
-        <f>Codex_calc!Z94</f>
-        <v>0</v>
-      </c>
-      <c r="AA94">
-        <f>Codex_calc!AA94</f>
-        <v>108.547826086957</v>
-      </c>
-      <c r="AB94">
-        <f>Codex_calc!AB94</f>
-        <v>0</v>
-      </c>
-      <c r="AC94">
-        <f>Codex_calc!AC94</f>
-        <v>20.3217391304348</v>
-      </c>
-      <c r="AD94">
-        <f>Codex_calc!AD94</f>
-        <v>219.078260869565</v>
-      </c>
-      <c r="AE94">
-        <f>Codex_calc!AE94</f>
-        <v>64.4347826086956</v>
-      </c>
-      <c r="AF94">
-        <f>Codex_calc!AF94</f>
-        <v>0</v>
-      </c>
-      <c r="AG94">
-        <f>Codex_calc!AG94</f>
-        <v>0</v>
-      </c>
-      <c r="AH94">
-        <f>Codex_calc!AH94</f>
-        <v>0</v>
-      </c>
-      <c r="AI94">
-        <f>Codex_calc!AI94</f>
-        <v>0</v>
-      </c>
-      <c r="AJ94">
-        <f>Codex_calc!AJ94</f>
-        <v>0</v>
-      </c>
-      <c r="AK94">
-        <f>Codex_calc!AK94</f>
-        <v>0</v>
-      </c>
-      <c r="AL94">
-        <f>Codex_calc!AL94</f>
-        <v>0</v>
-      </c>
-      <c r="AM94">
-        <f>Codex_calc!AM94</f>
-        <v>0</v>
-      </c>
-      <c r="AN94">
-        <f>Codex_calc!AN94</f>
-        <v>0</v>
-      </c>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="H94"/>
+      <c r="I94"/>
+      <c r="J94"/>
+      <c r="K94"/>
+      <c r="L94"/>
+      <c r="M94"/>
+      <c r="N94"/>
+      <c r="O94"/>
+      <c r="P94"/>
+      <c r="Q94"/>
+      <c r="R94"/>
+      <c r="S94"/>
+      <c r="T94"/>
+      <c r="U94"/>
+      <c r="V94"/>
+      <c r="W94"/>
+      <c r="X94"/>
+      <c r="Y94"/>
+      <c r="Z94"/>
+      <c r="AA94"/>
+      <c r="AB94"/>
+      <c r="AC94"/>
+      <c r="AD94"/>
+      <c r="AE94"/>
+      <c r="AF94"/>
+      <c r="AG94"/>
+      <c r="AH94"/>
+      <c r="AI94"/>
+      <c r="AJ94"/>
+      <c r="AK94"/>
+      <c r="AL94"/>
+      <c r="AM94"/>
+      <c r="AN94"/>
       <c r="AO94" t="str">
         <f>Codex_calc!AO94</f>
         <v>2019, 2130</v>
@@ -12816,10 +10968,7 @@
         <f>Codex_calc!D95</f>
         <v>CUM</v>
       </c>
-      <c r="E95">
-        <f>Codex_calc!E95</f>
-        <v>0</v>
-      </c>
+      <c r="E95"/>
       <c r="F95">
         <f>Codex_calc!F95</f>
         <v>0</v>
@@ -13132,150 +11281,42 @@
         <f>Codex_calc!D97</f>
         <v>BNDACT</v>
       </c>
-      <c r="E97">
-        <f>Codex_calc!E97</f>
-        <v>0</v>
-      </c>
-      <c r="F97">
-        <f>Codex_calc!F97</f>
-        <v>0</v>
-      </c>
-      <c r="G97">
-        <f>Codex_calc!G97</f>
-        <v>0</v>
-      </c>
-      <c r="H97">
-        <f>Codex_calc!H97</f>
-        <v>0</v>
-      </c>
-      <c r="I97">
-        <f>Codex_calc!I97</f>
-        <v>0</v>
-      </c>
-      <c r="J97">
-        <f>Codex_calc!J97</f>
-        <v>0</v>
-      </c>
-      <c r="K97">
-        <f>Codex_calc!K97</f>
-        <v>0</v>
-      </c>
-      <c r="L97">
-        <f>Codex_calc!L97</f>
-        <v>0</v>
-      </c>
-      <c r="M97">
-        <f>Codex_calc!M97</f>
-        <v>0</v>
-      </c>
-      <c r="N97">
-        <f>Codex_calc!N97</f>
-        <v>0</v>
-      </c>
-      <c r="O97">
-        <f>Codex_calc!O97</f>
-        <v>0</v>
-      </c>
-      <c r="P97">
-        <f>Codex_calc!P97</f>
-        <v>0</v>
-      </c>
-      <c r="Q97">
-        <f>Codex_calc!Q97</f>
-        <v>0</v>
-      </c>
-      <c r="R97">
-        <f>Codex_calc!R97</f>
-        <v>0</v>
-      </c>
-      <c r="S97">
-        <f>Codex_calc!S97</f>
-        <v>0</v>
-      </c>
-      <c r="T97">
-        <f>Codex_calc!T97</f>
-        <v>0</v>
-      </c>
-      <c r="U97">
-        <f>Codex_calc!U97</f>
-        <v>0</v>
-      </c>
-      <c r="V97">
-        <f>Codex_calc!V97</f>
-        <v>0</v>
-      </c>
-      <c r="W97">
-        <f>Codex_calc!W97</f>
-        <v>0</v>
-      </c>
-      <c r="X97">
-        <f>Codex_calc!X97</f>
-        <v>0</v>
-      </c>
-      <c r="Y97">
-        <f>Codex_calc!Y97</f>
-        <v>0</v>
-      </c>
-      <c r="Z97">
-        <f>Codex_calc!Z97</f>
-        <v>0</v>
-      </c>
-      <c r="AA97">
-        <f>Codex_calc!AA97</f>
-        <v>0</v>
-      </c>
-      <c r="AB97">
-        <f>Codex_calc!AB97</f>
-        <v>0</v>
-      </c>
-      <c r="AC97">
-        <f>Codex_calc!AC97</f>
-        <v>0</v>
-      </c>
-      <c r="AD97">
-        <f>Codex_calc!AD97</f>
-        <v>0</v>
-      </c>
-      <c r="AE97">
-        <f>Codex_calc!AE97</f>
-        <v>0</v>
-      </c>
-      <c r="AF97">
-        <f>Codex_calc!AF97</f>
-        <v>0</v>
-      </c>
-      <c r="AG97">
-        <f>Codex_calc!AG97</f>
-        <v>0</v>
-      </c>
-      <c r="AH97">
-        <f>Codex_calc!AH97</f>
-        <v>0</v>
-      </c>
-      <c r="AI97">
-        <f>Codex_calc!AI97</f>
-        <v>0</v>
-      </c>
-      <c r="AJ97">
-        <f>Codex_calc!AJ97</f>
-        <v>0</v>
-      </c>
-      <c r="AK97">
-        <f>Codex_calc!AK97</f>
-        <v>0</v>
-      </c>
-      <c r="AL97">
-        <f>Codex_calc!AL97</f>
-        <v>0</v>
-      </c>
-      <c r="AM97">
-        <f>Codex_calc!AM97</f>
-        <v>0</v>
-      </c>
-      <c r="AN97">
-        <f>Codex_calc!AN97</f>
-        <v>0</v>
-      </c>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
+      <c r="H97"/>
+      <c r="I97"/>
+      <c r="J97"/>
+      <c r="K97"/>
+      <c r="L97"/>
+      <c r="M97"/>
+      <c r="N97"/>
+      <c r="O97"/>
+      <c r="P97"/>
+      <c r="Q97"/>
+      <c r="R97"/>
+      <c r="S97"/>
+      <c r="T97"/>
+      <c r="U97"/>
+      <c r="V97"/>
+      <c r="W97"/>
+      <c r="X97"/>
+      <c r="Y97"/>
+      <c r="Z97"/>
+      <c r="AA97"/>
+      <c r="AB97"/>
+      <c r="AC97"/>
+      <c r="AD97"/>
+      <c r="AE97"/>
+      <c r="AF97"/>
+      <c r="AG97"/>
+      <c r="AH97"/>
+      <c r="AI97"/>
+      <c r="AJ97"/>
+      <c r="AK97"/>
+      <c r="AL97"/>
+      <c r="AM97"/>
+      <c r="AN97"/>
       <c r="AO97" t="str">
         <f>Codex_calc!AO97</f>
         <v>2019, 2130</v>
@@ -13290,10 +11331,7 @@
         <f>Codex_calc!D98</f>
         <v>CUM</v>
       </c>
-      <c r="E98">
-        <f>Codex_calc!E98</f>
-        <v>0</v>
-      </c>
+      <c r="E98"/>
       <c r="F98">
         <f>Codex_calc!F98</f>
         <v>0</v>
@@ -13763,150 +11801,42 @@
         <f>Codex_calc!D101</f>
         <v>BNDACT</v>
       </c>
-      <c r="E101">
-        <f>Codex_calc!E101</f>
-        <v>0</v>
-      </c>
-      <c r="F101">
-        <f>Codex_calc!F101</f>
-        <v>0</v>
-      </c>
-      <c r="G101">
-        <f>Codex_calc!G101</f>
-        <v>175.30025</v>
-      </c>
-      <c r="H101">
-        <f>Codex_calc!H101</f>
-        <v>0</v>
-      </c>
-      <c r="I101">
-        <f>Codex_calc!I101</f>
-        <v>0.16307</v>
-      </c>
-      <c r="J101">
-        <f>Codex_calc!J101</f>
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <f>Codex_calc!K101</f>
-        <v>0</v>
-      </c>
-      <c r="L101">
-        <f>Codex_calc!L101</f>
-        <v>52.99775</v>
-      </c>
-      <c r="M101">
-        <f>Codex_calc!M101</f>
-        <v>1141.49</v>
-      </c>
-      <c r="N101">
-        <f>Codex_calc!N101</f>
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <f>Codex_calc!O101</f>
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <f>Codex_calc!P101</f>
-        <v>0</v>
-      </c>
-      <c r="Q101">
-        <f>Codex_calc!Q101</f>
-        <v>0.114149</v>
-      </c>
-      <c r="R101">
-        <f>Codex_calc!R101</f>
-        <v>0</v>
-      </c>
-      <c r="S101">
-        <f>Codex_calc!S101</f>
-        <v>0</v>
-      </c>
-      <c r="T101">
-        <f>Codex_calc!T101</f>
-        <v>0</v>
-      </c>
-      <c r="U101">
-        <f>Codex_calc!U101</f>
-        <v>13.86095</v>
-      </c>
-      <c r="V101">
-        <f>Codex_calc!V101</f>
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <f>Codex_calc!W101</f>
-        <v>0</v>
-      </c>
-      <c r="X101">
-        <f>Codex_calc!X101</f>
-        <v>0</v>
-      </c>
-      <c r="Y101">
-        <f>Codex_calc!Y101</f>
-        <v>0</v>
-      </c>
-      <c r="Z101">
-        <f>Codex_calc!Z101</f>
-        <v>0</v>
-      </c>
-      <c r="AA101">
-        <f>Codex_calc!AA101</f>
-        <v>7.126159</v>
-      </c>
-      <c r="AB101">
-        <f>Codex_calc!AB101</f>
-        <v>5.38131</v>
-      </c>
-      <c r="AC101">
-        <f>Codex_calc!AC101</f>
-        <v>0</v>
-      </c>
-      <c r="AD101">
-        <f>Codex_calc!AD101</f>
-        <v>9.94727</v>
-      </c>
-      <c r="AE101">
-        <f>Codex_calc!AE101</f>
-        <v>20.38375</v>
-      </c>
-      <c r="AF101">
-        <f>Codex_calc!AF101</f>
-        <v>0</v>
-      </c>
-      <c r="AG101">
-        <f>Codex_calc!AG101</f>
-        <v>0</v>
-      </c>
-      <c r="AH101">
-        <f>Codex_calc!AH101</f>
-        <v>0</v>
-      </c>
-      <c r="AI101">
-        <f>Codex_calc!AI101</f>
-        <v>0</v>
-      </c>
-      <c r="AJ101">
-        <f>Codex_calc!AJ101</f>
-        <v>0</v>
-      </c>
-      <c r="AK101">
-        <f>Codex_calc!AK101</f>
-        <v>1.79377</v>
-      </c>
-      <c r="AL101">
-        <f>Codex_calc!AL101</f>
-        <v>0</v>
-      </c>
-      <c r="AM101">
-        <f>Codex_calc!AM101</f>
-        <v>0.65228</v>
-      </c>
-      <c r="AN101">
-        <f>Codex_calc!AN101</f>
-        <v>0</v>
-      </c>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
+      <c r="L101"/>
+      <c r="M101"/>
+      <c r="N101"/>
+      <c r="O101"/>
+      <c r="P101"/>
+      <c r="Q101"/>
+      <c r="R101"/>
+      <c r="S101"/>
+      <c r="T101"/>
+      <c r="U101"/>
+      <c r="V101"/>
+      <c r="W101"/>
+      <c r="X101"/>
+      <c r="Y101"/>
+      <c r="Z101"/>
+      <c r="AA101"/>
+      <c r="AB101"/>
+      <c r="AC101"/>
+      <c r="AD101"/>
+      <c r="AE101"/>
+      <c r="AF101"/>
+      <c r="AG101"/>
+      <c r="AH101"/>
+      <c r="AI101"/>
+      <c r="AJ101"/>
+      <c r="AK101"/>
+      <c r="AL101"/>
+      <c r="AM101"/>
+      <c r="AN101"/>
       <c r="AO101" t="str">
         <f>Codex_calc!AO101</f>
         <v>2019, 2130</v>
@@ -13921,10 +11851,7 @@
         <f>Codex_calc!D102</f>
         <v>CUM</v>
       </c>
-      <c r="E102">
-        <f>Codex_calc!E102</f>
-        <v>0</v>
-      </c>
+      <c r="E102"/>
       <c r="F102">
         <f>Codex_calc!F102</f>
         <v>0</v>
@@ -14237,150 +12164,42 @@
         <f>Codex_calc!D104</f>
         <v>BNDACT</v>
       </c>
-      <c r="E104">
-        <f>Codex_calc!E104</f>
-        <v>0</v>
-      </c>
-      <c r="F104">
-        <f>Codex_calc!F104</f>
-        <v>0</v>
-      </c>
-      <c r="G104">
-        <f>Codex_calc!G104</f>
-        <v>350.6005</v>
-      </c>
-      <c r="H104">
-        <f>Codex_calc!H104</f>
-        <v>0</v>
-      </c>
-      <c r="I104">
-        <f>Codex_calc!I104</f>
-        <v>0.32614</v>
-      </c>
-      <c r="J104">
-        <f>Codex_calc!J104</f>
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <f>Codex_calc!K104</f>
-        <v>0</v>
-      </c>
-      <c r="L104">
-        <f>Codex_calc!L104</f>
-        <v>105.9955</v>
-      </c>
-      <c r="M104">
-        <f>Codex_calc!M104</f>
-        <v>2282.98</v>
-      </c>
-      <c r="N104">
-        <f>Codex_calc!N104</f>
-        <v>0</v>
-      </c>
-      <c r="O104">
-        <f>Codex_calc!O104</f>
-        <v>0</v>
-      </c>
-      <c r="P104">
-        <f>Codex_calc!P104</f>
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <f>Codex_calc!Q104</f>
-        <v>0.228298</v>
-      </c>
-      <c r="R104">
-        <f>Codex_calc!R104</f>
-        <v>0</v>
-      </c>
-      <c r="S104">
-        <f>Codex_calc!S104</f>
-        <v>0</v>
-      </c>
-      <c r="T104">
-        <f>Codex_calc!T104</f>
-        <v>0</v>
-      </c>
-      <c r="U104">
-        <f>Codex_calc!U104</f>
-        <v>27.7219</v>
-      </c>
-      <c r="V104">
-        <f>Codex_calc!V104</f>
-        <v>0</v>
-      </c>
-      <c r="W104">
-        <f>Codex_calc!W104</f>
-        <v>0</v>
-      </c>
-      <c r="X104">
-        <f>Codex_calc!X104</f>
-        <v>0</v>
-      </c>
-      <c r="Y104">
-        <f>Codex_calc!Y104</f>
-        <v>0</v>
-      </c>
-      <c r="Z104">
-        <f>Codex_calc!Z104</f>
-        <v>0</v>
-      </c>
-      <c r="AA104">
-        <f>Codex_calc!AA104</f>
-        <v>14.252318</v>
-      </c>
-      <c r="AB104">
-        <f>Codex_calc!AB104</f>
-        <v>10.76262</v>
-      </c>
-      <c r="AC104">
-        <f>Codex_calc!AC104</f>
-        <v>0</v>
-      </c>
-      <c r="AD104">
-        <f>Codex_calc!AD104</f>
-        <v>19.89454</v>
-      </c>
-      <c r="AE104">
-        <f>Codex_calc!AE104</f>
-        <v>40.7675</v>
-      </c>
-      <c r="AF104">
-        <f>Codex_calc!AF104</f>
-        <v>0</v>
-      </c>
-      <c r="AG104">
-        <f>Codex_calc!AG104</f>
-        <v>0</v>
-      </c>
-      <c r="AH104">
-        <f>Codex_calc!AH104</f>
-        <v>0</v>
-      </c>
-      <c r="AI104">
-        <f>Codex_calc!AI104</f>
-        <v>0</v>
-      </c>
-      <c r="AJ104">
-        <f>Codex_calc!AJ104</f>
-        <v>0</v>
-      </c>
-      <c r="AK104">
-        <f>Codex_calc!AK104</f>
-        <v>3.58754</v>
-      </c>
-      <c r="AL104">
-        <f>Codex_calc!AL104</f>
-        <v>0</v>
-      </c>
-      <c r="AM104">
-        <f>Codex_calc!AM104</f>
-        <v>1.30456</v>
-      </c>
-      <c r="AN104">
-        <f>Codex_calc!AN104</f>
-        <v>0</v>
-      </c>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104"/>
+      <c r="J104"/>
+      <c r="K104"/>
+      <c r="L104"/>
+      <c r="M104"/>
+      <c r="N104"/>
+      <c r="O104"/>
+      <c r="P104"/>
+      <c r="Q104"/>
+      <c r="R104"/>
+      <c r="S104"/>
+      <c r="T104"/>
+      <c r="U104"/>
+      <c r="V104"/>
+      <c r="W104"/>
+      <c r="X104"/>
+      <c r="Y104"/>
+      <c r="Z104"/>
+      <c r="AA104"/>
+      <c r="AB104"/>
+      <c r="AC104"/>
+      <c r="AD104"/>
+      <c r="AE104"/>
+      <c r="AF104"/>
+      <c r="AG104"/>
+      <c r="AH104"/>
+      <c r="AI104"/>
+      <c r="AJ104"/>
+      <c r="AK104"/>
+      <c r="AL104"/>
+      <c r="AM104"/>
+      <c r="AN104"/>
       <c r="AO104" t="str">
         <f>Codex_calc!AO104</f>
         <v>2019, 2130</v>
@@ -14395,10 +12214,7 @@
         <f>Codex_calc!D105</f>
         <v>CUM</v>
       </c>
-      <c r="E105">
-        <f>Codex_calc!E105</f>
-        <v>0</v>
-      </c>
+      <c r="E105"/>
       <c r="F105">
         <f>Codex_calc!F105</f>
         <v>0</v>
@@ -14711,150 +12527,42 @@
         <f>Codex_calc!D107</f>
         <v>BNDACT</v>
       </c>
-      <c r="E107">
-        <f>Codex_calc!E107</f>
-        <v>0</v>
-      </c>
-      <c r="F107">
-        <f>Codex_calc!F107</f>
-        <v>0</v>
-      </c>
-      <c r="G107">
-        <f>Codex_calc!G107</f>
-        <v>0</v>
-      </c>
-      <c r="H107">
-        <f>Codex_calc!H107</f>
-        <v>0</v>
-      </c>
-      <c r="I107">
-        <f>Codex_calc!I107</f>
-        <v>0</v>
-      </c>
-      <c r="J107">
-        <f>Codex_calc!J107</f>
-        <v>0</v>
-      </c>
-      <c r="K107">
-        <f>Codex_calc!K107</f>
-        <v>0</v>
-      </c>
-      <c r="L107">
-        <f>Codex_calc!L107</f>
-        <v>0</v>
-      </c>
-      <c r="M107">
-        <f>Codex_calc!M107</f>
-        <v>0</v>
-      </c>
-      <c r="N107">
-        <f>Codex_calc!N107</f>
-        <v>0</v>
-      </c>
-      <c r="O107">
-        <f>Codex_calc!O107</f>
-        <v>0</v>
-      </c>
-      <c r="P107">
-        <f>Codex_calc!P107</f>
-        <v>0</v>
-      </c>
-      <c r="Q107">
-        <f>Codex_calc!Q107</f>
-        <v>0</v>
-      </c>
-      <c r="R107">
-        <f>Codex_calc!R107</f>
-        <v>0</v>
-      </c>
-      <c r="S107">
-        <f>Codex_calc!S107</f>
-        <v>0</v>
-      </c>
-      <c r="T107">
-        <f>Codex_calc!T107</f>
-        <v>0</v>
-      </c>
-      <c r="U107">
-        <f>Codex_calc!U107</f>
-        <v>0</v>
-      </c>
-      <c r="V107">
-        <f>Codex_calc!V107</f>
-        <v>0</v>
-      </c>
-      <c r="W107">
-        <f>Codex_calc!W107</f>
-        <v>0</v>
-      </c>
-      <c r="X107">
-        <f>Codex_calc!X107</f>
-        <v>0</v>
-      </c>
-      <c r="Y107">
-        <f>Codex_calc!Y107</f>
-        <v>0</v>
-      </c>
-      <c r="Z107">
-        <f>Codex_calc!Z107</f>
-        <v>0</v>
-      </c>
-      <c r="AA107">
-        <f>Codex_calc!AA107</f>
-        <v>0</v>
-      </c>
-      <c r="AB107">
-        <f>Codex_calc!AB107</f>
-        <v>0</v>
-      </c>
-      <c r="AC107">
-        <f>Codex_calc!AC107</f>
-        <v>0</v>
-      </c>
-      <c r="AD107">
-        <f>Codex_calc!AD107</f>
-        <v>0</v>
-      </c>
-      <c r="AE107">
-        <f>Codex_calc!AE107</f>
-        <v>0</v>
-      </c>
-      <c r="AF107">
-        <f>Codex_calc!AF107</f>
-        <v>0</v>
-      </c>
-      <c r="AG107">
-        <f>Codex_calc!AG107</f>
-        <v>0</v>
-      </c>
-      <c r="AH107">
-        <f>Codex_calc!AH107</f>
-        <v>0</v>
-      </c>
-      <c r="AI107">
-        <f>Codex_calc!AI107</f>
-        <v>0</v>
-      </c>
-      <c r="AJ107">
-        <f>Codex_calc!AJ107</f>
-        <v>0</v>
-      </c>
-      <c r="AK107">
-        <f>Codex_calc!AK107</f>
-        <v>0</v>
-      </c>
-      <c r="AL107">
-        <f>Codex_calc!AL107</f>
-        <v>0</v>
-      </c>
-      <c r="AM107">
-        <f>Codex_calc!AM107</f>
-        <v>0</v>
-      </c>
-      <c r="AN107">
-        <f>Codex_calc!AN107</f>
-        <v>0</v>
-      </c>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107"/>
+      <c r="J107"/>
+      <c r="K107"/>
+      <c r="L107"/>
+      <c r="M107"/>
+      <c r="N107"/>
+      <c r="O107"/>
+      <c r="P107"/>
+      <c r="Q107"/>
+      <c r="R107"/>
+      <c r="S107"/>
+      <c r="T107"/>
+      <c r="U107"/>
+      <c r="V107"/>
+      <c r="W107"/>
+      <c r="X107"/>
+      <c r="Y107"/>
+      <c r="Z107"/>
+      <c r="AA107"/>
+      <c r="AB107"/>
+      <c r="AC107"/>
+      <c r="AD107"/>
+      <c r="AE107"/>
+      <c r="AF107"/>
+      <c r="AG107"/>
+      <c r="AH107"/>
+      <c r="AI107"/>
+      <c r="AJ107"/>
+      <c r="AK107"/>
+      <c r="AL107"/>
+      <c r="AM107"/>
+      <c r="AN107"/>
       <c r="AO107" t="str">
         <f>Codex_calc!AO107</f>
         <v>2019, 2130</v>
@@ -14869,10 +12577,7 @@
         <f>Codex_calc!D108</f>
         <v>CUM</v>
       </c>
-      <c r="E108">
-        <f>Codex_calc!E108</f>
-        <v>0</v>
-      </c>
+      <c r="E108"/>
       <c r="F108">
         <f>Codex_calc!F108</f>
         <v>0</v>
@@ -15174,6 +12879,576 @@
       <c r="AO109" t="str">
         <f>Codex_calc!AO109</f>
         <v>2019, 2130</v>
+      </c>
+    </row>
+    <row r="113" spans="3:40">
+      <c r="E113"/>
+      <c r="F113">
+        <f>Codex_calc!F81</f>
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <f>Codex_calc!G81</f>
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <f>Codex_calc!H81</f>
+        <v>30.1272972972973</v>
+      </c>
+      <c r="I113">
+        <f>Codex_calc!I81</f>
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <f>Codex_calc!J81</f>
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <f>Codex_calc!K81</f>
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <f>Codex_calc!L81</f>
+        <v>24.1018378378378</v>
+      </c>
+      <c r="M113">
+        <f>Codex_calc!M81</f>
+        <v>903.818918918919</v>
+      </c>
+      <c r="N113">
+        <f>Codex_calc!N81</f>
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <f>Codex_calc!O81</f>
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <f>Codex_calc!P81</f>
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <f>Codex_calc!Q81</f>
+        <v>0</v>
+      </c>
+      <c r="R113">
+        <f>Codex_calc!R81</f>
+        <v>0</v>
+      </c>
+      <c r="S113">
+        <f>Codex_calc!S81</f>
+        <v>0</v>
+      </c>
+      <c r="T113">
+        <f>Codex_calc!T81</f>
+        <v>15.0636486486486</v>
+      </c>
+      <c r="U113">
+        <f>Codex_calc!U81</f>
+        <v>84.3564324324324</v>
+      </c>
+      <c r="V113">
+        <f>Codex_calc!V81</f>
+        <v>0</v>
+      </c>
+      <c r="W113">
+        <f>Codex_calc!W81</f>
+        <v>0</v>
+      </c>
+      <c r="X113">
+        <f>Codex_calc!X81</f>
+        <v>0</v>
+      </c>
+      <c r="Y113">
+        <f>Codex_calc!Y81</f>
+        <v>0</v>
+      </c>
+      <c r="Z113">
+        <f>Codex_calc!Z81</f>
+        <v>86.3649189189189</v>
+      </c>
+      <c r="AA113">
+        <f>Codex_calc!AA81</f>
+        <v>79.5360648648649</v>
+      </c>
+      <c r="AB113">
+        <f>Codex_calc!AB81</f>
+        <v>26.1103243243243</v>
+      </c>
+      <c r="AC113">
+        <f>Codex_calc!AC81</f>
+        <v>0</v>
+      </c>
+      <c r="AD113">
+        <f>Codex_calc!AD81</f>
+        <v>162.687405405405</v>
+      </c>
+      <c r="AE113">
+        <f>Codex_calc!AE81</f>
+        <v>78.330972972973</v>
+      </c>
+      <c r="AF113">
+        <f>Codex_calc!AF81</f>
+        <v>0</v>
+      </c>
+      <c r="AG113">
+        <f>Codex_calc!AG81</f>
+        <v>0</v>
+      </c>
+      <c r="AH113">
+        <f>Codex_calc!AH81</f>
+        <v>0</v>
+      </c>
+      <c r="AI113">
+        <f>Codex_calc!AI81</f>
+        <v>0</v>
+      </c>
+      <c r="AJ113">
+        <f>Codex_calc!AJ81</f>
+        <v>0</v>
+      </c>
+      <c r="AK113">
+        <f>Codex_calc!AK81</f>
+        <v>0</v>
+      </c>
+      <c r="AL113">
+        <f>Codex_calc!AL81</f>
+        <v>0</v>
+      </c>
+      <c r="AM113">
+        <f>Codex_calc!AM81</f>
+        <v>0</v>
+      </c>
+      <c r="AN113">
+        <f>Codex_calc!AN81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="3:40">
+      <c r="E114"/>
+      <c r="F114">
+        <f>Codex_calc!F84</f>
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <f>Codex_calc!G84</f>
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <f>Codex_calc!H84</f>
+        <v>60.2545945945946</v>
+      </c>
+      <c r="I114">
+        <f>Codex_calc!I84</f>
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <f>Codex_calc!J84</f>
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <f>Codex_calc!K84</f>
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <f>Codex_calc!L84</f>
+        <v>48.2036756756757</v>
+      </c>
+      <c r="M114">
+        <f>Codex_calc!M84</f>
+        <v>1807.63783783784</v>
+      </c>
+      <c r="N114">
+        <f>Codex_calc!N84</f>
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <f>Codex_calc!O84</f>
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <f>Codex_calc!P84</f>
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <f>Codex_calc!Q84</f>
+        <v>0</v>
+      </c>
+      <c r="R114">
+        <f>Codex_calc!R84</f>
+        <v>0</v>
+      </c>
+      <c r="S114">
+        <f>Codex_calc!S84</f>
+        <v>0</v>
+      </c>
+      <c r="T114">
+        <f>Codex_calc!T84</f>
+        <v>30.1272972972973</v>
+      </c>
+      <c r="U114">
+        <f>Codex_calc!U84</f>
+        <v>168.712864864865</v>
+      </c>
+      <c r="V114">
+        <f>Codex_calc!V84</f>
+        <v>0</v>
+      </c>
+      <c r="W114">
+        <f>Codex_calc!W84</f>
+        <v>0</v>
+      </c>
+      <c r="X114">
+        <f>Codex_calc!X84</f>
+        <v>0</v>
+      </c>
+      <c r="Y114">
+        <f>Codex_calc!Y84</f>
+        <v>0</v>
+      </c>
+      <c r="Z114">
+        <f>Codex_calc!Z84</f>
+        <v>172.729837837838</v>
+      </c>
+      <c r="AA114">
+        <f>Codex_calc!AA84</f>
+        <v>159.07212972973</v>
+      </c>
+      <c r="AB114">
+        <f>Codex_calc!AB84</f>
+        <v>52.2206486486486</v>
+      </c>
+      <c r="AC114">
+        <f>Codex_calc!AC84</f>
+        <v>0</v>
+      </c>
+      <c r="AD114">
+        <f>Codex_calc!AD84</f>
+        <v>325.374810810811</v>
+      </c>
+      <c r="AE114">
+        <f>Codex_calc!AE84</f>
+        <v>156.661945945946</v>
+      </c>
+      <c r="AF114">
+        <f>Codex_calc!AF84</f>
+        <v>0</v>
+      </c>
+      <c r="AG114">
+        <f>Codex_calc!AG84</f>
+        <v>0</v>
+      </c>
+      <c r="AH114">
+        <f>Codex_calc!AH84</f>
+        <v>0</v>
+      </c>
+      <c r="AI114">
+        <f>Codex_calc!AI84</f>
+        <v>0</v>
+      </c>
+      <c r="AJ114">
+        <f>Codex_calc!AJ84</f>
+        <v>0</v>
+      </c>
+      <c r="AK114">
+        <f>Codex_calc!AK84</f>
+        <v>0</v>
+      </c>
+      <c r="AL114">
+        <f>Codex_calc!AL84</f>
+        <v>0</v>
+      </c>
+      <c r="AM114">
+        <f>Codex_calc!AM84</f>
+        <v>0</v>
+      </c>
+      <c r="AN114">
+        <f>Codex_calc!AN84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="3:40">
+      <c r="F115" s="1" t="e">
+        <f>F82/F113</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G115" s="1" t="e">
+        <f t="shared" ref="G115:AN115" si="3">G82/G113</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H115" s="1">
+        <f t="shared" si="3"/>
+        <v>616.666666666666</v>
+      </c>
+      <c r="I115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L115" s="1">
+        <f t="shared" si="3"/>
+        <v>354.166666666667</v>
+      </c>
+      <c r="M115" s="1">
+        <f t="shared" si="3"/>
+        <v>3.94444444444444</v>
+      </c>
+      <c r="N115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T115" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U115" s="1">
+        <f t="shared" si="3"/>
+        <v>38.6904761904762</v>
+      </c>
+      <c r="V115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z115" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA115" s="1">
+        <f t="shared" si="3"/>
+        <v>1.26262626262626</v>
+      </c>
+      <c r="AB115" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD115" s="1">
+        <f t="shared" si="3"/>
+        <v>353.703703703704</v>
+      </c>
+      <c r="AE115" s="1">
+        <f t="shared" si="3"/>
+        <v>41.6666666666666</v>
+      </c>
+      <c r="AF115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AI115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AJ115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AK115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AM115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AN115" s="1" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="116" spans="3:40">
+      <c r="F116" s="1" t="e">
+        <f>F102/F101</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G116" s="1" t="e">
+        <f t="shared" ref="G116:AN116" si="4">G102/G101</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AI116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AJ116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AK116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AM116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AN116" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="117" spans="3:40">
@@ -32645,7 +30920,7 @@
       </c>
       <c r="I41">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,I$4)*Codex_sources!$D$5/3</f>
-        <v>0.426746821967562</v>
+        <v>0.426746821967561</v>
       </c>
       <c r="J41">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,J$4)*Codex_sources!$D$5/3</f>
@@ -32657,7 +30932,7 @@
       </c>
       <c r="L41">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,L$4)*Codex_sources!$D$5/3</f>
-        <v>7.17848331141587</v>
+        <v>7.17848331141586</v>
       </c>
       <c r="M41">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,M$4)*Codex_sources!$D$5/3</f>
@@ -32669,7 +30944,7 @@
       </c>
       <c r="O41">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,O$4)*Codex_sources!$D$5/3</f>
-        <v>1.4250610557956</v>
+        <v>1.42506105579561</v>
       </c>
       <c r="P41">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,P$4)*Codex_sources!$D$5/3</f>
@@ -32749,7 +31024,7 @@
       </c>
       <c r="AI41">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,AI$4)*Codex_sources!$D$5/3</f>
-        <v>0.727409355626526</v>
+        <v>0.727409355626527</v>
       </c>
       <c r="AJ41">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,AJ$4)*Codex_sources!$D$5/3</f>
@@ -32761,7 +31036,7 @@
       </c>
       <c r="AL41">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,AL$4)*Codex_sources!$D$5/3</f>
-        <v>0.363704677813263</v>
+        <v>0.363704677813262</v>
       </c>
       <c r="AM41">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,AM$4)*Codex_sources!$D$5/3</f>
@@ -32828,7 +31103,7 @@
       </c>
       <c r="Q42">
         <f>SUMIFS(Codex_Li_Busch!$G:$G,Codex_Li_Busch!$D:$D,Q$4)*Codex_sources!$D$5</f>
-        <v>94.0713806172171</v>
+        <v>94.0713806172166</v>
       </c>
       <c r="R42">
         <f>SUMIFS(Codex_Li_Busch!$G:$G,Codex_Li_Busch!$D:$D,R$4)*Codex_sources!$D$5</f>
@@ -32896,7 +31171,7 @@
       </c>
       <c r="AH42">
         <f>SUMIFS(Codex_Li_Busch!$G:$G,Codex_Li_Busch!$D:$D,AH$4)*Codex_sources!$D$5</f>
-        <v>124.694798393574</v>
+        <v>124.694798393575</v>
       </c>
       <c r="AI42">
         <f>SUMIFS(Codex_Li_Busch!$G:$G,Codex_Li_Busch!$D:$D,AI$4)*Codex_sources!$D$5</f>
@@ -33103,7 +31378,7 @@
       </c>
       <c r="I44">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,I$4)*Codex_sources!$D$5*2/3</f>
-        <v>0.853493643935125</v>
+        <v>0.853493643935123</v>
       </c>
       <c r="J44">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,J$4)*Codex_sources!$D$5*2/3</f>
@@ -33219,7 +31494,7 @@
       </c>
       <c r="AL44">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,AL$4)*Codex_sources!$D$5*2/3</f>
-        <v>0.727409355626526</v>
+        <v>0.727409355626524</v>
       </c>
       <c r="AM44">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,AM$4)*Codex_sources!$D$5*2/3</f>
@@ -33227,7 +31502,7 @@
       </c>
       <c r="AN44">
         <f>SUMIFS(Codex_Li_Busch!$J:$J,Codex_Li_Busch!$D:$D,AN$4)*Codex_sources!$D$5*2/3</f>
-        <v>5.75314672177344</v>
+        <v>5.75314672177343</v>
       </c>
       <c r="AO44" t="str">
         <f t="shared" si="0"/>
@@ -33251,7 +31526,7 @@
       </c>
       <c r="H45">
         <f>SUMIFS(Codex_Li_Busch!$H:$H,Codex_Li_Busch!$D:$D,H$4)*Codex_sources!$D$5</f>
-        <v>2609.34575023317</v>
+        <v>2609.34575023318</v>
       </c>
       <c r="I45">
         <f>SUMIFS(Codex_Li_Busch!$H:$H,Codex_Li_Busch!$D:$D,I$4)*Codex_sources!$D$5</f>
@@ -33602,11 +31877,11 @@
       </c>
       <c r="P48">
         <f>SUMIFS(Codex_Li_Busch!$I:$I,Codex_Li_Busch!$D:$D,P$4)*Codex_sources!$D$5</f>
-        <v>449.659973226238</v>
+        <v>449.659973226239</v>
       </c>
       <c r="Q48">
         <f>SUMIFS(Codex_Li_Busch!$I:$I,Codex_Li_Busch!$D:$D,Q$4)*Codex_sources!$D$5</f>
-        <v>2787.73946940985</v>
+        <v>2787.73946940986</v>
       </c>
       <c r="R48">
         <f>SUMIFS(Codex_Li_Busch!$I:$I,Codex_Li_Busch!$D:$D,R$4)*Codex_sources!$D$5</f>
@@ -33678,7 +31953,7 @@
       </c>
       <c r="AI48">
         <f>SUMIFS(Codex_Li_Busch!$I:$I,Codex_Li_Busch!$D:$D,AI$4)*Codex_sources!$D$5</f>
-        <v>9.4402035733622</v>
+        <v>9.44020357336223</v>
       </c>
       <c r="AJ48">
         <f>SUMIFS(Codex_Li_Busch!$I:$I,Codex_Li_Busch!$D:$D,AJ$4)*Codex_sources!$D$5</f>
@@ -35737,7 +34012,7 @@
       </c>
       <c r="H65">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$7,Codex_USGS_raw!$C:$C,H$4)*Codex_sources!$D$7*Codex_sources!$K$7</f>
-        <v>654.005537634408</v>
+        <v>654.005537634409</v>
       </c>
       <c r="I65">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$7,Codex_USGS_raw!$C:$C,I$4)*Codex_sources!$D$7*Codex_sources!$K$7</f>
@@ -36056,7 +34331,7 @@
       </c>
       <c r="H68">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$7,Codex_USGS_raw!$C:$C,H$4)*Codex_sources!$D$7*Codex_sources!$L$7</f>
-        <v>654.005537634408</v>
+        <v>654.005537634409</v>
       </c>
       <c r="I68">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$7,Codex_USGS_raw!$C:$C,I$4)*Codex_sources!$D$7*Codex_sources!$L$7</f>
@@ -37000,7 +35275,7 @@
       </c>
       <c r="M75">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$8,Codex_USGS_raw!$C:$C,M$4)*Codex_sources!$D$8*Codex_sources!$K$8</f>
-        <v>11087.5555555556</v>
+        <v>11087.5555555555</v>
       </c>
       <c r="N75">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$8,Codex_USGS_raw!$C:$C,N$4)*Codex_sources!$D$8*Codex_sources!$K$8</f>
@@ -37068,7 +35343,7 @@
       </c>
       <c r="AD75">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$8,Codex_USGS_raw!$C:$C,AD$4)*Codex_sources!$D$8*Codex_sources!$K$8</f>
-        <v>85.2888888888889</v>
+        <v>85.2888888888888</v>
       </c>
       <c r="AE75">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$8,Codex_USGS_raw!$C:$C,AE$4)*Codex_sources!$D$8*Codex_sources!$K$8</f>
@@ -37319,7 +35594,7 @@
       </c>
       <c r="M78">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$8,Codex_USGS_raw!$C:$C,M$4)*Codex_sources!$D$8*Codex_sources!$L$8</f>
-        <v>11087.5555555556</v>
+        <v>11087.5555555555</v>
       </c>
       <c r="N78">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$8,Codex_USGS_raw!$C:$C,N$4)*Codex_sources!$D$8*Codex_sources!$L$8</f>
@@ -37387,7 +35662,7 @@
       </c>
       <c r="AD78">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$8,Codex_USGS_raw!$C:$C,AD$4)*Codex_sources!$D$8*Codex_sources!$L$8</f>
-        <v>85.2888888888889</v>
+        <v>85.2888888888888</v>
       </c>
       <c r="AE78">
         <f>SUMIFS(Codex_USGS_raw!$E:$E,Codex_USGS_raw!$A:$A,Codex_sources!$A$8,Codex_USGS_raw!$C:$C,AE$4)*Codex_sources!$D$8*Codex_sources!$L$8</f>

--- a/SuppXLS/Scen_usingStepMining_n_mute_original_Min2.xlsx
+++ b/SuppXLS/Scen_usingStepMining_n_mute_original_Min2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710"/>
+    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Scen_usingStepMining_n_mute_ori" sheetId="1" r:id="rId1"/>
@@ -2803,22 +2803,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="C4:AO172"/>
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="30.3636363636364" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.4545454545455" style="1" customWidth="1"/>
     <col min="6" max="8" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.8181818181818"/>
+    <col min="10" max="10" width="10.5454545454545"/>
     <col min="11" max="11" width="33.1818181818182" style="1" customWidth="1"/>
     <col min="12" max="12" width="11.2727272727273" style="1" customWidth="1"/>
     <col min="13" max="13" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5454545454545"/>
+    <col min="15" max="15" width="12.8181818181818"/>
     <col min="16" max="16" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.8181818181818"/>
     <col min="18" max="18" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5454545454545"/>
     <col min="20" max="21" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="22" max="24" width="10.5454545454545"/>
     <col min="25" max="35" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="36" max="36" width="10.5454545454545"/>
     <col min="37" max="37" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="38" max="38" width="12.8181818181818"/>
     <col min="39" max="39" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="40" max="40" width="12.8181818181818"/>
     <col min="41" max="41" width="10.5454545454545" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4438,7 +4448,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="42" spans="3:41">
+    <row r="42" hidden="1" spans="3:41">
       <c r="C42" s="30" t="str">
         <f>Codex_calc!C42</f>
         <v>MINLiRSV1</v>
@@ -4593,7 +4603,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="43" spans="3:41">
+    <row r="43" hidden="1" spans="3:41">
       <c r="C43" s="30" t="str">
         <f>Codex_calc!C43</f>
         <v>MINLiRSV1</v>
@@ -4906,7 +4916,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="45" spans="3:41">
+    <row r="45" hidden="1" spans="3:41">
       <c r="C45" s="30" t="str">
         <f>Codex_calc!C45</f>
         <v>MINLiRSV2</v>
@@ -5061,7 +5071,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="46" spans="3:41">
+    <row r="46" hidden="1" spans="3:41">
       <c r="C46" s="30" t="str">
         <f>Codex_calc!C46</f>
         <v>MINLiRSV2</v>
@@ -5219,7 +5229,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="47" spans="3:41">
+    <row r="47" hidden="1" spans="3:41">
       <c r="C47" s="30" t="str">
         <f>Codex_calc!C47</f>
         <v>MINLiRSV3</v>
@@ -5269,7 +5279,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="48" spans="3:41">
+    <row r="48" hidden="1" spans="3:41">
       <c r="C48" s="30" t="str">
         <f>Codex_calc!C48</f>
         <v>MINLiRSV3</v>
@@ -5424,7 +5434,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="49" spans="3:41">
+    <row r="49" hidden="1" spans="3:41">
       <c r="C49" s="30" t="str">
         <f>Codex_calc!C49</f>
         <v>MINLiRSV3</v>
@@ -5582,7 +5592,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="50" spans="3:41">
+    <row r="50" hidden="1" spans="3:41">
       <c r="C50" s="30" t="s">
         <v>63</v>
       </c>
@@ -5749,47 +5759,152 @@
         <v>BNDACT</v>
       </c>
       <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="30"/>
-      <c r="K51" s="30"/>
-      <c r="L51" s="30"/>
-      <c r="M51" s="30"/>
-      <c r="N51" s="30"/>
-      <c r="O51" s="30"/>
-      <c r="P51" s="30"/>
-      <c r="Q51" s="30"/>
-      <c r="R51" s="30"/>
-      <c r="S51" s="30"/>
-      <c r="T51" s="30"/>
-      <c r="U51" s="30"/>
-      <c r="V51" s="30"/>
-      <c r="W51" s="30"/>
-      <c r="X51" s="30"/>
-      <c r="Y51" s="30"/>
-      <c r="Z51" s="30"/>
-      <c r="AA51" s="30"/>
-      <c r="AB51" s="30"/>
-      <c r="AC51" s="30"/>
-      <c r="AD51" s="30"/>
-      <c r="AE51" s="30"/>
-      <c r="AF51" s="30"/>
-      <c r="AG51" s="30"/>
-      <c r="AH51" s="30"/>
-      <c r="AI51" s="30"/>
-      <c r="AJ51" s="30"/>
-      <c r="AK51" s="30"/>
-      <c r="AL51" s="30"/>
-      <c r="AM51" s="30"/>
-      <c r="AN51" s="30"/>
+      <c r="F51" s="30">
+        <f>Codex_calc!F51</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="30">
+        <f>Codex_calc!G51</f>
+        <v>0</v>
+      </c>
+      <c r="H51" s="30">
+        <f>Codex_calc!H51</f>
+        <v>6.40384615384615</v>
+      </c>
+      <c r="I51" s="30">
+        <f>Codex_calc!I51</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="30">
+        <f>Codex_calc!J51</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="30">
+        <f>Codex_calc!K51</f>
+        <v>0</v>
+      </c>
+      <c r="L51" s="30">
+        <f>Codex_calc!L51</f>
+        <v>9.96153846153846</v>
+      </c>
+      <c r="M51" s="30">
+        <f>Codex_calc!M51</f>
+        <v>17.0769230769231</v>
+      </c>
+      <c r="N51" s="30">
+        <f>Codex_calc!N51</f>
+        <v>0</v>
+      </c>
+      <c r="O51" s="30">
+        <f>Codex_calc!O51</f>
+        <v>0</v>
+      </c>
+      <c r="P51" s="30">
+        <f>Codex_calc!P51</f>
+        <v>0</v>
+      </c>
+      <c r="Q51" s="30">
+        <f>Codex_calc!Q51</f>
+        <v>0</v>
+      </c>
+      <c r="R51" s="30">
+        <f>Codex_calc!R51</f>
+        <v>0</v>
+      </c>
+      <c r="S51" s="30">
+        <f>Codex_calc!S51</f>
+        <v>0</v>
+      </c>
+      <c r="T51" s="30">
+        <f>Codex_calc!T51</f>
+        <v>0</v>
+      </c>
+      <c r="U51" s="30">
+        <f>Codex_calc!U51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="30">
+        <f>Codex_calc!V51</f>
+        <v>0</v>
+      </c>
+      <c r="W51" s="30">
+        <f>Codex_calc!W51</f>
+        <v>0</v>
+      </c>
+      <c r="X51" s="30">
+        <f>Codex_calc!X51</f>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="30">
+        <f>Codex_calc!Y51</f>
+        <v>0</v>
+      </c>
+      <c r="Z51" s="30">
+        <f>Codex_calc!Z51</f>
+        <v>0</v>
+      </c>
+      <c r="AA51" s="30">
+        <f>Codex_calc!AA51</f>
+        <v>21.3461538461538</v>
+      </c>
+      <c r="AB51" s="30">
+        <f>Codex_calc!AB51</f>
+        <v>0</v>
+      </c>
+      <c r="AC51" s="30">
+        <f>Codex_calc!AC51</f>
+        <v>0</v>
+      </c>
+      <c r="AD51" s="30">
+        <f>Codex_calc!AD51</f>
+        <v>469.615384615385</v>
+      </c>
+      <c r="AE51" s="30">
+        <f>Codex_calc!AE51</f>
+        <v>28.4615384615385</v>
+      </c>
+      <c r="AF51" s="30">
+        <f>Codex_calc!AF51</f>
+        <v>0</v>
+      </c>
+      <c r="AG51" s="30">
+        <f>Codex_calc!AG51</f>
+        <v>0</v>
+      </c>
+      <c r="AH51" s="30">
+        <f>Codex_calc!AH51</f>
+        <v>0</v>
+      </c>
+      <c r="AI51" s="30">
+        <f>Codex_calc!AI51</f>
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="30">
+        <f>Codex_calc!AJ51</f>
+        <v>0</v>
+      </c>
+      <c r="AK51" s="30">
+        <f>Codex_calc!AK51</f>
+        <v>0</v>
+      </c>
+      <c r="AL51" s="30">
+        <f>Codex_calc!AL51</f>
+        <v>0</v>
+      </c>
+      <c r="AM51" s="30">
+        <f>Codex_calc!AM51</f>
+        <v>0</v>
+      </c>
+      <c r="AN51" s="30">
+        <f>Codex_calc!AN51</f>
+        <v>0</v>
+      </c>
       <c r="AO51" t="str">
         <f>Codex_calc!AO51</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="52" spans="3:41">
+    <row r="52" hidden="1" spans="3:41">
       <c r="C52" s="30" t="str">
         <f>Codex_calc!C52</f>
         <v>MINNiRSV1</v>
@@ -5944,7 +6059,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="53" spans="3:41">
+    <row r="53" hidden="1" spans="3:41">
       <c r="C53" s="30" t="str">
         <f>Codex_calc!C53</f>
         <v>MINNiRSV1</v>
@@ -6112,47 +6227,152 @@
         <v>BNDACT</v>
       </c>
       <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
-      <c r="L54" s="30"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="30"/>
-      <c r="O54" s="30"/>
-      <c r="P54" s="30"/>
-      <c r="Q54" s="30"/>
-      <c r="R54" s="30"/>
-      <c r="S54" s="30"/>
-      <c r="T54" s="30"/>
-      <c r="U54" s="30"/>
-      <c r="V54" s="30"/>
-      <c r="W54" s="30"/>
-      <c r="X54" s="30"/>
-      <c r="Y54" s="30"/>
-      <c r="Z54" s="30"/>
-      <c r="AA54" s="30"/>
-      <c r="AB54" s="30"/>
-      <c r="AC54" s="30"/>
-      <c r="AD54" s="30"/>
-      <c r="AE54" s="30"/>
-      <c r="AF54" s="30"/>
-      <c r="AG54" s="30"/>
-      <c r="AH54" s="30"/>
-      <c r="AI54" s="30"/>
-      <c r="AJ54" s="30"/>
-      <c r="AK54" s="30"/>
-      <c r="AL54" s="30"/>
-      <c r="AM54" s="30"/>
-      <c r="AN54" s="30"/>
+      <c r="F54" s="30">
+        <f>Codex_calc!F54</f>
+        <v>0</v>
+      </c>
+      <c r="G54" s="30">
+        <f>Codex_calc!G54</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="30">
+        <f>Codex_calc!H54</f>
+        <v>12.8076923076923</v>
+      </c>
+      <c r="I54" s="30">
+        <f>Codex_calc!I54</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="30">
+        <f>Codex_calc!J54</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="30">
+        <f>Codex_calc!K54</f>
+        <v>0</v>
+      </c>
+      <c r="L54" s="30">
+        <f>Codex_calc!L54</f>
+        <v>19.9230769230769</v>
+      </c>
+      <c r="M54" s="30">
+        <f>Codex_calc!M54</f>
+        <v>34.1538461538462</v>
+      </c>
+      <c r="N54" s="30">
+        <f>Codex_calc!N54</f>
+        <v>0</v>
+      </c>
+      <c r="O54" s="30">
+        <f>Codex_calc!O54</f>
+        <v>0</v>
+      </c>
+      <c r="P54" s="30">
+        <f>Codex_calc!P54</f>
+        <v>0</v>
+      </c>
+      <c r="Q54" s="30">
+        <f>Codex_calc!Q54</f>
+        <v>0</v>
+      </c>
+      <c r="R54" s="30">
+        <f>Codex_calc!R54</f>
+        <v>0</v>
+      </c>
+      <c r="S54" s="30">
+        <f>Codex_calc!S54</f>
+        <v>0</v>
+      </c>
+      <c r="T54" s="30">
+        <f>Codex_calc!T54</f>
+        <v>0</v>
+      </c>
+      <c r="U54" s="30">
+        <f>Codex_calc!U54</f>
+        <v>0</v>
+      </c>
+      <c r="V54" s="30">
+        <f>Codex_calc!V54</f>
+        <v>0</v>
+      </c>
+      <c r="W54" s="30">
+        <f>Codex_calc!W54</f>
+        <v>0</v>
+      </c>
+      <c r="X54" s="30">
+        <f>Codex_calc!X54</f>
+        <v>0</v>
+      </c>
+      <c r="Y54" s="30">
+        <f>Codex_calc!Y54</f>
+        <v>0</v>
+      </c>
+      <c r="Z54" s="30">
+        <f>Codex_calc!Z54</f>
+        <v>0</v>
+      </c>
+      <c r="AA54" s="30">
+        <f>Codex_calc!AA54</f>
+        <v>42.6923076923077</v>
+      </c>
+      <c r="AB54" s="30">
+        <f>Codex_calc!AB54</f>
+        <v>0</v>
+      </c>
+      <c r="AC54" s="30">
+        <f>Codex_calc!AC54</f>
+        <v>0</v>
+      </c>
+      <c r="AD54" s="30">
+        <f>Codex_calc!AD54</f>
+        <v>939.230769230769</v>
+      </c>
+      <c r="AE54" s="30">
+        <f>Codex_calc!AE54</f>
+        <v>56.9230769230769</v>
+      </c>
+      <c r="AF54" s="30">
+        <f>Codex_calc!AF54</f>
+        <v>0</v>
+      </c>
+      <c r="AG54" s="30">
+        <f>Codex_calc!AG54</f>
+        <v>0</v>
+      </c>
+      <c r="AH54" s="30">
+        <f>Codex_calc!AH54</f>
+        <v>0</v>
+      </c>
+      <c r="AI54" s="30">
+        <f>Codex_calc!AI54</f>
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="30">
+        <f>Codex_calc!AJ54</f>
+        <v>0</v>
+      </c>
+      <c r="AK54" s="30">
+        <f>Codex_calc!AK54</f>
+        <v>0</v>
+      </c>
+      <c r="AL54" s="30">
+        <f>Codex_calc!AL54</f>
+        <v>0</v>
+      </c>
+      <c r="AM54" s="30">
+        <f>Codex_calc!AM54</f>
+        <v>0</v>
+      </c>
+      <c r="AN54" s="30">
+        <f>Codex_calc!AN54</f>
+        <v>0</v>
+      </c>
       <c r="AO54" t="str">
         <f>Codex_calc!AO54</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="55" spans="3:41">
+    <row r="55" hidden="1" spans="3:41">
       <c r="C55" s="30" t="str">
         <f>Codex_calc!C55</f>
         <v>MINNiRSV2</v>
@@ -6307,7 +6527,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="56" spans="3:41">
+    <row r="56" hidden="1" spans="3:41">
       <c r="C56" s="30" t="str">
         <f>Codex_calc!C56</f>
         <v>MINNiRSV2</v>
@@ -6465,7 +6685,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="57" spans="3:41">
+    <row r="57" hidden="1" spans="3:41">
       <c r="C57" t="str">
         <f>Codex_calc!C57</f>
         <v>MINNiRSV3</v>
@@ -6478,22 +6698,13 @@
       <c r="F57"/>
       <c r="G57"/>
       <c r="H57"/>
-      <c r="I57"/>
-      <c r="J57"/>
       <c r="K57"/>
       <c r="L57"/>
       <c r="M57"/>
-      <c r="N57"/>
-      <c r="O57"/>
       <c r="P57"/>
-      <c r="Q57"/>
       <c r="R57"/>
-      <c r="S57"/>
       <c r="T57"/>
       <c r="U57"/>
-      <c r="V57"/>
-      <c r="W57"/>
-      <c r="X57"/>
       <c r="Y57"/>
       <c r="Z57"/>
       <c r="AA57"/>
@@ -6505,17 +6716,14 @@
       <c r="AG57"/>
       <c r="AH57"/>
       <c r="AI57"/>
-      <c r="AJ57"/>
       <c r="AK57"/>
-      <c r="AL57"/>
       <c r="AM57"/>
-      <c r="AN57"/>
       <c r="AO57" t="str">
         <f>Codex_calc!AO57</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="58" spans="3:41">
+    <row r="58" hidden="1" spans="3:41">
       <c r="C58" t="str">
         <f>Codex_calc!C58</f>
         <v>MINNiRSV3</v>
@@ -6670,7 +6878,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="59" spans="3:41">
+    <row r="59" hidden="1" spans="3:41">
       <c r="C59" t="str">
         <f>Codex_calc!C59</f>
         <v>MINNiRSV3</v>
@@ -6828,7 +7036,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="60" spans="3:41">
+    <row r="60" hidden="1" spans="3:41">
       <c r="C60" t="s">
         <v>63</v>
       </c>
@@ -6995,47 +7203,152 @@
         <v>BNDACT</v>
       </c>
       <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
-      <c r="H61"/>
-      <c r="I61"/>
-      <c r="J61"/>
-      <c r="K61"/>
-      <c r="L61"/>
-      <c r="M61"/>
-      <c r="N61"/>
-      <c r="O61"/>
-      <c r="P61"/>
-      <c r="Q61"/>
-      <c r="R61"/>
-      <c r="S61"/>
-      <c r="T61"/>
-      <c r="U61"/>
-      <c r="V61"/>
-      <c r="W61"/>
-      <c r="X61"/>
-      <c r="Y61"/>
-      <c r="Z61"/>
-      <c r="AA61"/>
-      <c r="AB61"/>
-      <c r="AC61"/>
-      <c r="AD61"/>
-      <c r="AE61"/>
-      <c r="AF61"/>
-      <c r="AG61"/>
-      <c r="AH61"/>
-      <c r="AI61"/>
-      <c r="AJ61"/>
-      <c r="AK61"/>
-      <c r="AL61"/>
-      <c r="AM61"/>
-      <c r="AN61"/>
+      <c r="F61" s="30">
+        <f>Codex_calc!F61</f>
+        <v>0</v>
+      </c>
+      <c r="G61" s="30">
+        <f>Codex_calc!G61</f>
+        <v>166.12332516129</v>
+      </c>
+      <c r="H61" s="30">
+        <f>Codex_calc!H61</f>
+        <v>2.62785935483871</v>
+      </c>
+      <c r="I61" s="30">
+        <f>Codex_calc!I61</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="30">
+        <f>Codex_calc!J61</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="30">
+        <f>Codex_calc!K61</f>
+        <v>0</v>
+      </c>
+      <c r="L61" s="30">
+        <f>Codex_calc!L61</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="30">
+        <f>Codex_calc!M61</f>
+        <v>1.42046451612903</v>
+      </c>
+      <c r="N61" s="30">
+        <f>Codex_calc!N61</f>
+        <v>0</v>
+      </c>
+      <c r="O61" s="30">
+        <f>Codex_calc!O61</f>
+        <v>0</v>
+      </c>
+      <c r="P61" s="30">
+        <f>Codex_calc!P61</f>
+        <v>0</v>
+      </c>
+      <c r="Q61" s="30">
+        <f>Codex_calc!Q61</f>
+        <v>0</v>
+      </c>
+      <c r="R61" s="30">
+        <f>Codex_calc!R61</f>
+        <v>0</v>
+      </c>
+      <c r="S61" s="30">
+        <f>Codex_calc!S61</f>
+        <v>0</v>
+      </c>
+      <c r="T61" s="30">
+        <f>Codex_calc!T61</f>
+        <v>0</v>
+      </c>
+      <c r="U61" s="30">
+        <f>Codex_calc!U61</f>
+        <v>0</v>
+      </c>
+      <c r="V61" s="30">
+        <f>Codex_calc!V61</f>
+        <v>0</v>
+      </c>
+      <c r="W61" s="30">
+        <f>Codex_calc!W61</f>
+        <v>0</v>
+      </c>
+      <c r="X61" s="30">
+        <f>Codex_calc!X61</f>
+        <v>0</v>
+      </c>
+      <c r="Y61" s="30">
+        <f>Codex_calc!Y61</f>
+        <v>1.42046451612903</v>
+      </c>
+      <c r="Z61" s="30">
+        <f>Codex_calc!Z61</f>
+        <v>0</v>
+      </c>
+      <c r="AA61" s="30">
+        <f>Codex_calc!AA61</f>
+        <v>2.69888258064516</v>
+      </c>
+      <c r="AB61" s="30">
+        <f>Codex_calc!AB61</f>
+        <v>0</v>
+      </c>
+      <c r="AC61" s="30">
+        <f>Codex_calc!AC61</f>
+        <v>0</v>
+      </c>
+      <c r="AD61" s="30">
+        <f>Codex_calc!AD61</f>
+        <v>42.3298425806452</v>
+      </c>
+      <c r="AE61" s="30">
+        <f>Codex_calc!AE61</f>
+        <v>5.46878838709677</v>
+      </c>
+      <c r="AF61" s="30">
+        <f>Codex_calc!AF61</f>
+        <v>0</v>
+      </c>
+      <c r="AG61" s="30">
+        <f>Codex_calc!AG61</f>
+        <v>0</v>
+      </c>
+      <c r="AH61" s="30">
+        <f>Codex_calc!AH61</f>
+        <v>0</v>
+      </c>
+      <c r="AI61" s="30">
+        <f>Codex_calc!AI61</f>
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="30">
+        <f>Codex_calc!AJ61</f>
+        <v>0</v>
+      </c>
+      <c r="AK61" s="30">
+        <f>Codex_calc!AK61</f>
+        <v>1.34944129032258</v>
+      </c>
+      <c r="AL61" s="30">
+        <f>Codex_calc!AL61</f>
+        <v>0</v>
+      </c>
+      <c r="AM61" s="30">
+        <f>Codex_calc!AM61</f>
+        <v>0</v>
+      </c>
+      <c r="AN61" s="30">
+        <f>Codex_calc!AN61</f>
+        <v>0</v>
+      </c>
       <c r="AO61" t="str">
         <f>Codex_calc!AO61</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="62" spans="3:41">
+    <row r="62" hidden="1" spans="3:41">
       <c r="C62" t="str">
         <f>Codex_calc!C62</f>
         <v>MINCoRSV1</v>
@@ -7190,7 +7503,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="63" spans="3:41">
+    <row r="63" hidden="1" spans="3:41">
       <c r="C63" t="str">
         <f>Codex_calc!C63</f>
         <v>MINCoRSV1</v>
@@ -7358,47 +7671,152 @@
         <v>BNDACT</v>
       </c>
       <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-      <c r="K64"/>
-      <c r="L64"/>
-      <c r="M64"/>
-      <c r="N64"/>
-      <c r="O64"/>
-      <c r="P64"/>
-      <c r="Q64"/>
-      <c r="R64"/>
-      <c r="S64"/>
-      <c r="T64"/>
-      <c r="U64"/>
-      <c r="V64"/>
-      <c r="W64"/>
-      <c r="X64"/>
-      <c r="Y64"/>
-      <c r="Z64"/>
-      <c r="AA64"/>
-      <c r="AB64"/>
-      <c r="AC64"/>
-      <c r="AD64"/>
-      <c r="AE64"/>
-      <c r="AF64"/>
-      <c r="AG64"/>
-      <c r="AH64"/>
-      <c r="AI64"/>
-      <c r="AJ64"/>
-      <c r="AK64"/>
-      <c r="AL64"/>
-      <c r="AM64"/>
-      <c r="AN64"/>
+      <c r="F64" s="30">
+        <f>Codex_calc!F64</f>
+        <v>0</v>
+      </c>
+      <c r="G64" s="30">
+        <f>Codex_calc!G64</f>
+        <v>332.246650322581</v>
+      </c>
+      <c r="H64" s="30">
+        <f>Codex_calc!H64</f>
+        <v>5.25571870967742</v>
+      </c>
+      <c r="I64" s="30">
+        <f>Codex_calc!I64</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="30">
+        <f>Codex_calc!J64</f>
+        <v>0</v>
+      </c>
+      <c r="K64" s="30">
+        <f>Codex_calc!K64</f>
+        <v>0</v>
+      </c>
+      <c r="L64" s="30">
+        <f>Codex_calc!L64</f>
+        <v>0</v>
+      </c>
+      <c r="M64" s="30">
+        <f>Codex_calc!M64</f>
+        <v>2.84092903225806</v>
+      </c>
+      <c r="N64" s="30">
+        <f>Codex_calc!N64</f>
+        <v>0</v>
+      </c>
+      <c r="O64" s="30">
+        <f>Codex_calc!O64</f>
+        <v>0</v>
+      </c>
+      <c r="P64" s="30">
+        <f>Codex_calc!P64</f>
+        <v>0</v>
+      </c>
+      <c r="Q64" s="30">
+        <f>Codex_calc!Q64</f>
+        <v>0</v>
+      </c>
+      <c r="R64" s="30">
+        <f>Codex_calc!R64</f>
+        <v>0</v>
+      </c>
+      <c r="S64" s="30">
+        <f>Codex_calc!S64</f>
+        <v>0</v>
+      </c>
+      <c r="T64" s="30">
+        <f>Codex_calc!T64</f>
+        <v>0</v>
+      </c>
+      <c r="U64" s="30">
+        <f>Codex_calc!U64</f>
+        <v>0</v>
+      </c>
+      <c r="V64" s="30">
+        <f>Codex_calc!V64</f>
+        <v>0</v>
+      </c>
+      <c r="W64" s="30">
+        <f>Codex_calc!W64</f>
+        <v>0</v>
+      </c>
+      <c r="X64" s="30">
+        <f>Codex_calc!X64</f>
+        <v>0</v>
+      </c>
+      <c r="Y64" s="30">
+        <f>Codex_calc!Y64</f>
+        <v>2.84092903225806</v>
+      </c>
+      <c r="Z64" s="30">
+        <f>Codex_calc!Z64</f>
+        <v>0</v>
+      </c>
+      <c r="AA64" s="30">
+        <f>Codex_calc!AA64</f>
+        <v>5.39776516129032</v>
+      </c>
+      <c r="AB64" s="30">
+        <f>Codex_calc!AB64</f>
+        <v>0</v>
+      </c>
+      <c r="AC64" s="30">
+        <f>Codex_calc!AC64</f>
+        <v>0</v>
+      </c>
+      <c r="AD64" s="30">
+        <f>Codex_calc!AD64</f>
+        <v>84.6596851612903</v>
+      </c>
+      <c r="AE64" s="30">
+        <f>Codex_calc!AE64</f>
+        <v>10.9375767741935</v>
+      </c>
+      <c r="AF64" s="30">
+        <f>Codex_calc!AF64</f>
+        <v>0</v>
+      </c>
+      <c r="AG64" s="30">
+        <f>Codex_calc!AG64</f>
+        <v>0</v>
+      </c>
+      <c r="AH64" s="30">
+        <f>Codex_calc!AH64</f>
+        <v>0</v>
+      </c>
+      <c r="AI64" s="30">
+        <f>Codex_calc!AI64</f>
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="30">
+        <f>Codex_calc!AJ64</f>
+        <v>0</v>
+      </c>
+      <c r="AK64" s="30">
+        <f>Codex_calc!AK64</f>
+        <v>2.69888258064516</v>
+      </c>
+      <c r="AL64" s="30">
+        <f>Codex_calc!AL64</f>
+        <v>0</v>
+      </c>
+      <c r="AM64" s="30">
+        <f>Codex_calc!AM64</f>
+        <v>0</v>
+      </c>
+      <c r="AN64" s="30">
+        <f>Codex_calc!AN64</f>
+        <v>0</v>
+      </c>
       <c r="AO64" t="str">
         <f>Codex_calc!AO64</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="65" spans="3:41">
+    <row r="65" hidden="1" spans="3:41">
       <c r="C65" t="str">
         <f>Codex_calc!C65</f>
         <v>MINCoRSV2</v>
@@ -7553,7 +7971,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="66" spans="3:41">
+    <row r="66" hidden="1" spans="3:41">
       <c r="C66" t="str">
         <f>Codex_calc!C66</f>
         <v>MINCoRSV2</v>
@@ -7711,7 +8129,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="67" spans="3:41">
+    <row r="67" hidden="1" spans="3:41">
       <c r="C67" t="str">
         <f>Codex_calc!C67</f>
         <v>MINCoRSV3</v>
@@ -7724,22 +8142,13 @@
       <c r="F67"/>
       <c r="G67"/>
       <c r="H67"/>
-      <c r="I67"/>
-      <c r="J67"/>
       <c r="K67"/>
       <c r="L67"/>
       <c r="M67"/>
-      <c r="N67"/>
-      <c r="O67"/>
       <c r="P67"/>
-      <c r="Q67"/>
       <c r="R67"/>
-      <c r="S67"/>
       <c r="T67"/>
       <c r="U67"/>
-      <c r="V67"/>
-      <c r="W67"/>
-      <c r="X67"/>
       <c r="Y67"/>
       <c r="Z67"/>
       <c r="AA67"/>
@@ -7751,17 +8160,14 @@
       <c r="AG67"/>
       <c r="AH67"/>
       <c r="AI67"/>
-      <c r="AJ67"/>
       <c r="AK67"/>
-      <c r="AL67"/>
       <c r="AM67"/>
-      <c r="AN67"/>
       <c r="AO67" t="str">
         <f>Codex_calc!AO67</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="68" spans="3:41">
+    <row r="68" hidden="1" spans="3:41">
       <c r="C68" t="str">
         <f>Codex_calc!C68</f>
         <v>MINCoRSV3</v>
@@ -7916,7 +8322,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="69" spans="3:41">
+    <row r="69" hidden="1" spans="3:41">
       <c r="C69" t="str">
         <f>Codex_calc!C69</f>
         <v>MINCoRSV3</v>
@@ -8074,7 +8480,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="70" spans="3:41">
+    <row r="70" hidden="1" spans="3:41">
       <c r="C70" t="s">
         <v>63</v>
       </c>
@@ -8241,47 +8647,152 @@
         <v>BNDACT</v>
       </c>
       <c r="E71"/>
-      <c r="F71"/>
-      <c r="G71"/>
-      <c r="H71"/>
-      <c r="I71"/>
-      <c r="J71"/>
-      <c r="K71"/>
-      <c r="L71"/>
-      <c r="M71"/>
-      <c r="N71"/>
-      <c r="O71"/>
-      <c r="P71"/>
-      <c r="Q71"/>
-      <c r="R71"/>
-      <c r="S71"/>
-      <c r="T71"/>
-      <c r="U71"/>
-      <c r="V71"/>
-      <c r="W71"/>
-      <c r="X71"/>
-      <c r="Y71"/>
-      <c r="Z71"/>
-      <c r="AA71"/>
-      <c r="AB71"/>
-      <c r="AC71"/>
-      <c r="AD71"/>
-      <c r="AE71"/>
-      <c r="AF71"/>
-      <c r="AG71"/>
-      <c r="AH71"/>
-      <c r="AI71"/>
-      <c r="AJ71"/>
-      <c r="AK71"/>
-      <c r="AL71"/>
-      <c r="AM71"/>
-      <c r="AN71"/>
+      <c r="F71" s="30">
+        <f>Codex_calc!F71</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="30">
+        <f>Codex_calc!G71</f>
+        <v>74.235</v>
+      </c>
+      <c r="H71" s="30">
+        <f>Codex_calc!H71</f>
+        <v>16.16</v>
+      </c>
+      <c r="I71" s="30">
+        <f>Codex_calc!I71</f>
+        <v>0</v>
+      </c>
+      <c r="J71" s="30">
+        <f>Codex_calc!J71</f>
+        <v>0</v>
+      </c>
+      <c r="K71" s="30">
+        <f>Codex_calc!K71</f>
+        <v>0</v>
+      </c>
+      <c r="L71" s="30">
+        <f>Codex_calc!L71</f>
+        <v>8.08</v>
+      </c>
+      <c r="M71" s="30">
+        <f>Codex_calc!M71</f>
+        <v>7.07</v>
+      </c>
+      <c r="N71" s="30">
+        <f>Codex_calc!N71</f>
+        <v>0</v>
+      </c>
+      <c r="O71" s="30">
+        <f>Codex_calc!O71</f>
+        <v>0</v>
+      </c>
+      <c r="P71" s="30">
+        <f>Codex_calc!P71</f>
+        <v>0</v>
+      </c>
+      <c r="Q71" s="30">
+        <f>Codex_calc!Q71</f>
+        <v>0</v>
+      </c>
+      <c r="R71" s="30">
+        <f>Codex_calc!R71</f>
+        <v>0</v>
+      </c>
+      <c r="S71" s="30">
+        <f>Codex_calc!S71</f>
+        <v>0</v>
+      </c>
+      <c r="T71" s="30">
+        <f>Codex_calc!T71</f>
+        <v>0</v>
+      </c>
+      <c r="U71" s="30">
+        <f>Codex_calc!U71</f>
+        <v>7.979</v>
+      </c>
+      <c r="V71" s="30">
+        <f>Codex_calc!V71</f>
+        <v>0</v>
+      </c>
+      <c r="W71" s="30">
+        <f>Codex_calc!W71</f>
+        <v>0</v>
+      </c>
+      <c r="X71" s="30">
+        <f>Codex_calc!X71</f>
+        <v>0</v>
+      </c>
+      <c r="Y71" s="30">
+        <f>Codex_calc!Y71</f>
+        <v>0</v>
+      </c>
+      <c r="Z71" s="30">
+        <f>Codex_calc!Z71</f>
+        <v>0</v>
+      </c>
+      <c r="AA71" s="30">
+        <f>Codex_calc!AA71</f>
+        <v>0</v>
+      </c>
+      <c r="AB71" s="30">
+        <f>Codex_calc!AB71</f>
+        <v>0</v>
+      </c>
+      <c r="AC71" s="30">
+        <f>Codex_calc!AC71</f>
+        <v>0</v>
+      </c>
+      <c r="AD71" s="30">
+        <f>Codex_calc!AD71</f>
+        <v>13.13</v>
+      </c>
+      <c r="AE71" s="30">
+        <f>Codex_calc!AE71</f>
+        <v>0</v>
+      </c>
+      <c r="AF71" s="30">
+        <f>Codex_calc!AF71</f>
+        <v>0</v>
+      </c>
+      <c r="AG71" s="30">
+        <f>Codex_calc!AG71</f>
+        <v>76.76</v>
+      </c>
+      <c r="AH71" s="30">
+        <f>Codex_calc!AH71</f>
+        <v>0</v>
+      </c>
+      <c r="AI71" s="30">
+        <f>Codex_calc!AI71</f>
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="30">
+        <f>Codex_calc!AJ71</f>
+        <v>0</v>
+      </c>
+      <c r="AK71" s="30">
+        <f>Codex_calc!AK71</f>
+        <v>0</v>
+      </c>
+      <c r="AL71" s="30">
+        <f>Codex_calc!AL71</f>
+        <v>0</v>
+      </c>
+      <c r="AM71" s="30">
+        <f>Codex_calc!AM71</f>
+        <v>0</v>
+      </c>
+      <c r="AN71" s="30">
+        <f>Codex_calc!AN71</f>
+        <v>0</v>
+      </c>
       <c r="AO71" t="str">
         <f>Codex_calc!AO71</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="72" spans="3:41">
+    <row r="72" hidden="1" spans="3:41">
       <c r="C72" t="str">
         <f>Codex_calc!C72</f>
         <v>MINMnRSV1</v>
@@ -8436,7 +8947,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="73" spans="3:41">
+    <row r="73" hidden="1" spans="3:41">
       <c r="C73" t="str">
         <f>Codex_calc!C73</f>
         <v>MINMnRSV1</v>
@@ -8604,47 +9115,152 @@
         <v>BNDACT</v>
       </c>
       <c r="E74"/>
-      <c r="F74"/>
-      <c r="G74"/>
-      <c r="H74"/>
-      <c r="I74"/>
-      <c r="J74"/>
-      <c r="K74"/>
-      <c r="L74"/>
-      <c r="M74"/>
-      <c r="N74"/>
-      <c r="O74"/>
-      <c r="P74"/>
-      <c r="Q74"/>
-      <c r="R74"/>
-      <c r="S74"/>
-      <c r="T74"/>
-      <c r="U74"/>
-      <c r="V74"/>
-      <c r="W74"/>
-      <c r="X74"/>
-      <c r="Y74"/>
-      <c r="Z74"/>
-      <c r="AA74"/>
-      <c r="AB74"/>
-      <c r="AC74"/>
-      <c r="AD74"/>
-      <c r="AE74"/>
-      <c r="AF74"/>
-      <c r="AG74"/>
-      <c r="AH74"/>
-      <c r="AI74"/>
-      <c r="AJ74"/>
-      <c r="AK74"/>
-      <c r="AL74"/>
-      <c r="AM74"/>
-      <c r="AN74"/>
+      <c r="F74" s="30">
+        <f>Codex_calc!F74</f>
+        <v>0</v>
+      </c>
+      <c r="G74" s="30">
+        <f>Codex_calc!G74</f>
+        <v>148.47</v>
+      </c>
+      <c r="H74" s="30">
+        <f>Codex_calc!H74</f>
+        <v>32.32</v>
+      </c>
+      <c r="I74" s="30">
+        <f>Codex_calc!I74</f>
+        <v>0</v>
+      </c>
+      <c r="J74" s="30">
+        <f>Codex_calc!J74</f>
+        <v>0</v>
+      </c>
+      <c r="K74" s="30">
+        <f>Codex_calc!K74</f>
+        <v>0</v>
+      </c>
+      <c r="L74" s="30">
+        <f>Codex_calc!L74</f>
+        <v>16.16</v>
+      </c>
+      <c r="M74" s="30">
+        <f>Codex_calc!M74</f>
+        <v>14.14</v>
+      </c>
+      <c r="N74" s="30">
+        <f>Codex_calc!N74</f>
+        <v>0</v>
+      </c>
+      <c r="O74" s="30">
+        <f>Codex_calc!O74</f>
+        <v>0</v>
+      </c>
+      <c r="P74" s="30">
+        <f>Codex_calc!P74</f>
+        <v>0</v>
+      </c>
+      <c r="Q74" s="30">
+        <f>Codex_calc!Q74</f>
+        <v>0</v>
+      </c>
+      <c r="R74" s="30">
+        <f>Codex_calc!R74</f>
+        <v>0</v>
+      </c>
+      <c r="S74" s="30">
+        <f>Codex_calc!S74</f>
+        <v>0</v>
+      </c>
+      <c r="T74" s="30">
+        <f>Codex_calc!T74</f>
+        <v>0</v>
+      </c>
+      <c r="U74" s="30">
+        <f>Codex_calc!U74</f>
+        <v>15.958</v>
+      </c>
+      <c r="V74" s="30">
+        <f>Codex_calc!V74</f>
+        <v>0</v>
+      </c>
+      <c r="W74" s="30">
+        <f>Codex_calc!W74</f>
+        <v>0</v>
+      </c>
+      <c r="X74" s="30">
+        <f>Codex_calc!X74</f>
+        <v>0</v>
+      </c>
+      <c r="Y74" s="30">
+        <f>Codex_calc!Y74</f>
+        <v>0</v>
+      </c>
+      <c r="Z74" s="30">
+        <f>Codex_calc!Z74</f>
+        <v>0</v>
+      </c>
+      <c r="AA74" s="30">
+        <f>Codex_calc!AA74</f>
+        <v>0</v>
+      </c>
+      <c r="AB74" s="30">
+        <f>Codex_calc!AB74</f>
+        <v>0</v>
+      </c>
+      <c r="AC74" s="30">
+        <f>Codex_calc!AC74</f>
+        <v>0</v>
+      </c>
+      <c r="AD74" s="30">
+        <f>Codex_calc!AD74</f>
+        <v>26.26</v>
+      </c>
+      <c r="AE74" s="30">
+        <f>Codex_calc!AE74</f>
+        <v>0</v>
+      </c>
+      <c r="AF74" s="30">
+        <f>Codex_calc!AF74</f>
+        <v>0</v>
+      </c>
+      <c r="AG74" s="30">
+        <f>Codex_calc!AG74</f>
+        <v>153.52</v>
+      </c>
+      <c r="AH74" s="30">
+        <f>Codex_calc!AH74</f>
+        <v>0</v>
+      </c>
+      <c r="AI74" s="30">
+        <f>Codex_calc!AI74</f>
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="30">
+        <f>Codex_calc!AJ74</f>
+        <v>0</v>
+      </c>
+      <c r="AK74" s="30">
+        <f>Codex_calc!AK74</f>
+        <v>0</v>
+      </c>
+      <c r="AL74" s="30">
+        <f>Codex_calc!AL74</f>
+        <v>0</v>
+      </c>
+      <c r="AM74" s="30">
+        <f>Codex_calc!AM74</f>
+        <v>0</v>
+      </c>
+      <c r="AN74" s="30">
+        <f>Codex_calc!AN74</f>
+        <v>0</v>
+      </c>
       <c r="AO74" t="str">
         <f>Codex_calc!AO74</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="75" spans="3:41">
+    <row r="75" hidden="1" spans="3:41">
       <c r="C75" t="str">
         <f>Codex_calc!C75</f>
         <v>MINMnRSV2</v>
@@ -8799,7 +9415,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="76" spans="3:41">
+    <row r="76" hidden="1" spans="3:41">
       <c r="C76" t="str">
         <f>Codex_calc!C76</f>
         <v>MINMnRSV2</v>
@@ -8957,7 +9573,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="77" spans="3:41">
+    <row r="77" hidden="1" spans="3:41">
       <c r="C77" t="str">
         <f>Codex_calc!C77</f>
         <v>MINMnRSV3</v>
@@ -8970,22 +9586,13 @@
       <c r="F77"/>
       <c r="G77"/>
       <c r="H77"/>
-      <c r="I77"/>
-      <c r="J77"/>
       <c r="K77"/>
       <c r="L77"/>
       <c r="M77"/>
-      <c r="N77"/>
-      <c r="O77"/>
       <c r="P77"/>
-      <c r="Q77"/>
       <c r="R77"/>
-      <c r="S77"/>
       <c r="T77"/>
       <c r="U77"/>
-      <c r="V77"/>
-      <c r="W77"/>
-      <c r="X77"/>
       <c r="Y77"/>
       <c r="Z77"/>
       <c r="AA77"/>
@@ -8997,17 +9604,14 @@
       <c r="AG77"/>
       <c r="AH77"/>
       <c r="AI77"/>
-      <c r="AJ77"/>
       <c r="AK77"/>
-      <c r="AL77"/>
       <c r="AM77"/>
-      <c r="AN77"/>
       <c r="AO77" t="str">
         <f>Codex_calc!AO77</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="78" spans="3:41">
+    <row r="78" hidden="1" spans="3:41">
       <c r="C78" t="str">
         <f>Codex_calc!C78</f>
         <v>MINMnRSV3</v>
@@ -9162,7 +9766,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="79" spans="3:41">
+    <row r="79" hidden="1" spans="3:41">
       <c r="C79" t="str">
         <f>Codex_calc!C79</f>
         <v>MINMnRSV3</v>
@@ -9320,7 +9924,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="80" spans="3:41">
+    <row r="80" hidden="1" spans="3:41">
       <c r="C80" t="s">
         <v>63</v>
       </c>
@@ -9486,12 +10090,152 @@
         <f>Codex_calc!D81</f>
         <v>BNDACT</v>
       </c>
+      <c r="F81" s="30">
+        <f>Codex_calc!F81</f>
+        <v>0</v>
+      </c>
+      <c r="G81" s="30">
+        <f>Codex_calc!G81</f>
+        <v>0</v>
+      </c>
+      <c r="H81" s="30">
+        <f>Codex_calc!H81</f>
+        <v>30.1272972972973</v>
+      </c>
+      <c r="I81" s="30">
+        <f>Codex_calc!I81</f>
+        <v>0</v>
+      </c>
+      <c r="J81" s="30">
+        <f>Codex_calc!J81</f>
+        <v>0</v>
+      </c>
+      <c r="K81" s="30">
+        <f>Codex_calc!K81</f>
+        <v>0</v>
+      </c>
+      <c r="L81" s="30">
+        <f>Codex_calc!L81</f>
+        <v>24.1018378378378</v>
+      </c>
+      <c r="M81" s="30">
+        <f>Codex_calc!M81</f>
+        <v>903.818918918919</v>
+      </c>
+      <c r="N81" s="30">
+        <f>Codex_calc!N81</f>
+        <v>0</v>
+      </c>
+      <c r="O81" s="30">
+        <f>Codex_calc!O81</f>
+        <v>0</v>
+      </c>
+      <c r="P81" s="30">
+        <f>Codex_calc!P81</f>
+        <v>0</v>
+      </c>
+      <c r="Q81" s="30">
+        <f>Codex_calc!Q81</f>
+        <v>0</v>
+      </c>
+      <c r="R81" s="30">
+        <f>Codex_calc!R81</f>
+        <v>0</v>
+      </c>
+      <c r="S81" s="30">
+        <f>Codex_calc!S81</f>
+        <v>0</v>
+      </c>
+      <c r="T81" s="30">
+        <f>Codex_calc!T81</f>
+        <v>15.0636486486486</v>
+      </c>
+      <c r="U81" s="30">
+        <f>Codex_calc!U81</f>
+        <v>84.3564324324324</v>
+      </c>
+      <c r="V81" s="30">
+        <f>Codex_calc!V81</f>
+        <v>0</v>
+      </c>
+      <c r="W81" s="30">
+        <f>Codex_calc!W81</f>
+        <v>0</v>
+      </c>
+      <c r="X81" s="30">
+        <f>Codex_calc!X81</f>
+        <v>0</v>
+      </c>
+      <c r="Y81" s="30">
+        <f>Codex_calc!Y81</f>
+        <v>0</v>
+      </c>
+      <c r="Z81" s="30">
+        <f>Codex_calc!Z81</f>
+        <v>86.3649189189189</v>
+      </c>
+      <c r="AA81" s="30">
+        <f>Codex_calc!AA81</f>
+        <v>79.5360648648649</v>
+      </c>
+      <c r="AB81" s="30">
+        <f>Codex_calc!AB81</f>
+        <v>26.1103243243243</v>
+      </c>
+      <c r="AC81" s="30">
+        <f>Codex_calc!AC81</f>
+        <v>0</v>
+      </c>
+      <c r="AD81" s="30">
+        <f>Codex_calc!AD81</f>
+        <v>162.687405405405</v>
+      </c>
+      <c r="AE81" s="30">
+        <f>Codex_calc!AE81</f>
+        <v>78.330972972973</v>
+      </c>
+      <c r="AF81" s="30">
+        <f>Codex_calc!AF81</f>
+        <v>0</v>
+      </c>
+      <c r="AG81" s="30">
+        <f>Codex_calc!AG81</f>
+        <v>0</v>
+      </c>
+      <c r="AH81" s="30">
+        <f>Codex_calc!AH81</f>
+        <v>0</v>
+      </c>
+      <c r="AI81" s="30">
+        <f>Codex_calc!AI81</f>
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="30">
+        <f>Codex_calc!AJ81</f>
+        <v>0</v>
+      </c>
+      <c r="AK81" s="30">
+        <f>Codex_calc!AK81</f>
+        <v>0</v>
+      </c>
+      <c r="AL81" s="30">
+        <f>Codex_calc!AL81</f>
+        <v>0</v>
+      </c>
+      <c r="AM81" s="30">
+        <f>Codex_calc!AM81</f>
+        <v>0</v>
+      </c>
+      <c r="AN81" s="30">
+        <f>Codex_calc!AN81</f>
+        <v>0</v>
+      </c>
       <c r="AO81" t="str">
         <f>Codex_calc!AO81</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="82" spans="3:41">
+    <row r="82" hidden="1" spans="3:41">
       <c r="C82" t="str">
         <f>Codex_calc!C82</f>
         <v>MINAlRSV1</v>
@@ -9646,7 +10390,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="83" spans="3:41">
+    <row r="83" hidden="1" spans="3:41">
       <c r="C83" t="str">
         <f>Codex_calc!C83</f>
         <v>MINAlRSV1</v>
@@ -9813,12 +10557,152 @@
         <f>Codex_calc!D84</f>
         <v>BNDACT</v>
       </c>
+      <c r="F84" s="30">
+        <f>Codex_calc!F84</f>
+        <v>0</v>
+      </c>
+      <c r="G84" s="30">
+        <f>Codex_calc!G84</f>
+        <v>0</v>
+      </c>
+      <c r="H84" s="30">
+        <f>Codex_calc!H84</f>
+        <v>60.2545945945946</v>
+      </c>
+      <c r="I84" s="30">
+        <f>Codex_calc!I84</f>
+        <v>0</v>
+      </c>
+      <c r="J84" s="30">
+        <f>Codex_calc!J84</f>
+        <v>0</v>
+      </c>
+      <c r="K84" s="30">
+        <f>Codex_calc!K84</f>
+        <v>0</v>
+      </c>
+      <c r="L84" s="30">
+        <f>Codex_calc!L84</f>
+        <v>48.2036756756757</v>
+      </c>
+      <c r="M84" s="30">
+        <f>Codex_calc!M84</f>
+        <v>1807.63783783784</v>
+      </c>
+      <c r="N84" s="30">
+        <f>Codex_calc!N84</f>
+        <v>0</v>
+      </c>
+      <c r="O84" s="30">
+        <f>Codex_calc!O84</f>
+        <v>0</v>
+      </c>
+      <c r="P84" s="30">
+        <f>Codex_calc!P84</f>
+        <v>0</v>
+      </c>
+      <c r="Q84" s="30">
+        <f>Codex_calc!Q84</f>
+        <v>0</v>
+      </c>
+      <c r="R84" s="30">
+        <f>Codex_calc!R84</f>
+        <v>0</v>
+      </c>
+      <c r="S84" s="30">
+        <f>Codex_calc!S84</f>
+        <v>0</v>
+      </c>
+      <c r="T84" s="30">
+        <f>Codex_calc!T84</f>
+        <v>30.1272972972973</v>
+      </c>
+      <c r="U84" s="30">
+        <f>Codex_calc!U84</f>
+        <v>168.712864864865</v>
+      </c>
+      <c r="V84" s="30">
+        <f>Codex_calc!V84</f>
+        <v>0</v>
+      </c>
+      <c r="W84" s="30">
+        <f>Codex_calc!W84</f>
+        <v>0</v>
+      </c>
+      <c r="X84" s="30">
+        <f>Codex_calc!X84</f>
+        <v>0</v>
+      </c>
+      <c r="Y84" s="30">
+        <f>Codex_calc!Y84</f>
+        <v>0</v>
+      </c>
+      <c r="Z84" s="30">
+        <f>Codex_calc!Z84</f>
+        <v>172.729837837838</v>
+      </c>
+      <c r="AA84" s="30">
+        <f>Codex_calc!AA84</f>
+        <v>159.07212972973</v>
+      </c>
+      <c r="AB84" s="30">
+        <f>Codex_calc!AB84</f>
+        <v>52.2206486486486</v>
+      </c>
+      <c r="AC84" s="30">
+        <f>Codex_calc!AC84</f>
+        <v>0</v>
+      </c>
+      <c r="AD84" s="30">
+        <f>Codex_calc!AD84</f>
+        <v>325.374810810811</v>
+      </c>
+      <c r="AE84" s="30">
+        <f>Codex_calc!AE84</f>
+        <v>156.661945945946</v>
+      </c>
+      <c r="AF84" s="30">
+        <f>Codex_calc!AF84</f>
+        <v>0</v>
+      </c>
+      <c r="AG84" s="30">
+        <f>Codex_calc!AG84</f>
+        <v>0</v>
+      </c>
+      <c r="AH84" s="30">
+        <f>Codex_calc!AH84</f>
+        <v>0</v>
+      </c>
+      <c r="AI84" s="30">
+        <f>Codex_calc!AI84</f>
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="30">
+        <f>Codex_calc!AJ84</f>
+        <v>0</v>
+      </c>
+      <c r="AK84" s="30">
+        <f>Codex_calc!AK84</f>
+        <v>0</v>
+      </c>
+      <c r="AL84" s="30">
+        <f>Codex_calc!AL84</f>
+        <v>0</v>
+      </c>
+      <c r="AM84" s="30">
+        <f>Codex_calc!AM84</f>
+        <v>0</v>
+      </c>
+      <c r="AN84" s="30">
+        <f>Codex_calc!AN84</f>
+        <v>0</v>
+      </c>
       <c r="AO84" t="str">
         <f>Codex_calc!AO84</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="85" spans="3:41">
+    <row r="85" hidden="1" spans="3:41">
       <c r="C85" t="str">
         <f>Codex_calc!C85</f>
         <v>MINAlRSV2</v>
@@ -9973,7 +10857,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="86" spans="3:41">
+    <row r="86" hidden="1" spans="3:41">
       <c r="C86" t="str">
         <f>Codex_calc!C86</f>
         <v>MINAlRSV2</v>
@@ -10131,7 +11015,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="87" spans="3:41">
+    <row r="87" hidden="1" spans="3:41">
       <c r="C87" t="str">
         <f>Codex_calc!C87</f>
         <v>MINAlRSV3</v>
@@ -10144,22 +11028,13 @@
       <c r="F87"/>
       <c r="G87"/>
       <c r="H87"/>
-      <c r="I87"/>
-      <c r="J87"/>
       <c r="K87"/>
       <c r="L87"/>
       <c r="M87"/>
-      <c r="N87"/>
-      <c r="O87"/>
       <c r="P87"/>
-      <c r="Q87"/>
       <c r="R87"/>
-      <c r="S87"/>
       <c r="T87"/>
       <c r="U87"/>
-      <c r="V87"/>
-      <c r="W87"/>
-      <c r="X87"/>
       <c r="Y87"/>
       <c r="Z87"/>
       <c r="AA87"/>
@@ -10171,17 +11046,14 @@
       <c r="AG87"/>
       <c r="AH87"/>
       <c r="AI87"/>
-      <c r="AJ87"/>
       <c r="AK87"/>
-      <c r="AL87"/>
       <c r="AM87"/>
-      <c r="AN87"/>
       <c r="AO87" t="str">
         <f>Codex_calc!AO87</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="88" spans="3:41">
+    <row r="88" hidden="1" spans="3:41">
       <c r="C88" t="str">
         <f>Codex_calc!C88</f>
         <v>MINAlRSV3</v>
@@ -10194,22 +11066,13 @@
       <c r="F88"/>
       <c r="G88"/>
       <c r="H88"/>
-      <c r="I88"/>
-      <c r="J88"/>
       <c r="K88"/>
       <c r="L88"/>
       <c r="M88"/>
-      <c r="N88"/>
-      <c r="O88"/>
       <c r="P88"/>
-      <c r="Q88"/>
       <c r="R88"/>
-      <c r="S88"/>
       <c r="T88"/>
       <c r="U88"/>
-      <c r="V88"/>
-      <c r="W88"/>
-      <c r="X88"/>
       <c r="Y88"/>
       <c r="Z88"/>
       <c r="AA88"/>
@@ -10221,17 +11084,14 @@
       <c r="AG88"/>
       <c r="AH88"/>
       <c r="AI88"/>
-      <c r="AJ88"/>
       <c r="AK88"/>
-      <c r="AL88"/>
       <c r="AM88"/>
-      <c r="AN88"/>
       <c r="AO88" t="str">
         <f>Codex_calc!AO88</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="89" spans="3:41">
+    <row r="89" hidden="1" spans="3:41">
       <c r="C89" t="str">
         <f>Codex_calc!C89</f>
         <v>MINAlRSV3</v>
@@ -10389,7 +11249,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="90" spans="3:41">
+    <row r="90" hidden="1" spans="3:41">
       <c r="C90" t="s">
         <v>63</v>
       </c>
@@ -10556,47 +11416,152 @@
         <v>BNDACT</v>
       </c>
       <c r="E91"/>
-      <c r="F91"/>
-      <c r="G91"/>
-      <c r="H91"/>
-      <c r="I91"/>
-      <c r="J91"/>
-      <c r="K91"/>
-      <c r="L91"/>
-      <c r="M91"/>
-      <c r="N91"/>
-      <c r="O91"/>
-      <c r="P91"/>
-      <c r="Q91"/>
-      <c r="R91"/>
-      <c r="S91"/>
-      <c r="T91"/>
-      <c r="U91"/>
-      <c r="V91"/>
-      <c r="W91"/>
-      <c r="X91"/>
-      <c r="Y91"/>
-      <c r="Z91"/>
-      <c r="AA91"/>
-      <c r="AB91"/>
-      <c r="AC91"/>
-      <c r="AD91"/>
-      <c r="AE91"/>
-      <c r="AF91"/>
-      <c r="AG91"/>
-      <c r="AH91"/>
-      <c r="AI91"/>
-      <c r="AJ91"/>
-      <c r="AK91"/>
-      <c r="AL91"/>
-      <c r="AM91"/>
-      <c r="AN91"/>
+      <c r="F91" s="30">
+        <f>Codex_calc!F91</f>
+        <v>0</v>
+      </c>
+      <c r="G91" s="30">
+        <f>Codex_calc!G91</f>
+        <v>102.6</v>
+      </c>
+      <c r="H91" s="30">
+        <f>Codex_calc!H91</f>
+        <v>18.0913043478261</v>
+      </c>
+      <c r="I91" s="30">
+        <f>Codex_calc!I91</f>
+        <v>0</v>
+      </c>
+      <c r="J91" s="30">
+        <f>Codex_calc!J91</f>
+        <v>0</v>
+      </c>
+      <c r="K91" s="30">
+        <f>Codex_calc!K91</f>
+        <v>0</v>
+      </c>
+      <c r="L91" s="30">
+        <f>Codex_calc!L91</f>
+        <v>0</v>
+      </c>
+      <c r="M91" s="30">
+        <f>Codex_calc!M91</f>
+        <v>44.6086956521739</v>
+      </c>
+      <c r="N91" s="30">
+        <f>Codex_calc!N91</f>
+        <v>0</v>
+      </c>
+      <c r="O91" s="30">
+        <f>Codex_calc!O91</f>
+        <v>0</v>
+      </c>
+      <c r="P91" s="30">
+        <f>Codex_calc!P91</f>
+        <v>0</v>
+      </c>
+      <c r="Q91" s="30">
+        <f>Codex_calc!Q91</f>
+        <v>0</v>
+      </c>
+      <c r="R91" s="30">
+        <f>Codex_calc!R91</f>
+        <v>0</v>
+      </c>
+      <c r="S91" s="30">
+        <f>Codex_calc!S91</f>
+        <v>0</v>
+      </c>
+      <c r="T91" s="30">
+        <f>Codex_calc!T91</f>
+        <v>0</v>
+      </c>
+      <c r="U91" s="30">
+        <f>Codex_calc!U91</f>
+        <v>0.57</v>
+      </c>
+      <c r="V91" s="30">
+        <f>Codex_calc!V91</f>
+        <v>0</v>
+      </c>
+      <c r="W91" s="30">
+        <f>Codex_calc!W91</f>
+        <v>0</v>
+      </c>
+      <c r="X91" s="30">
+        <f>Codex_calc!X91</f>
+        <v>0</v>
+      </c>
+      <c r="Y91" s="30">
+        <f>Codex_calc!Y91</f>
+        <v>198.260869565217</v>
+      </c>
+      <c r="Z91" s="30">
+        <f>Codex_calc!Z91</f>
+        <v>0</v>
+      </c>
+      <c r="AA91" s="30">
+        <f>Codex_calc!AA91</f>
+        <v>54.2739130434783</v>
+      </c>
+      <c r="AB91" s="30">
+        <f>Codex_calc!AB91</f>
+        <v>0</v>
+      </c>
+      <c r="AC91" s="30">
+        <f>Codex_calc!AC91</f>
+        <v>10.1608695652174</v>
+      </c>
+      <c r="AD91" s="30">
+        <f>Codex_calc!AD91</f>
+        <v>109.539130434783</v>
+      </c>
+      <c r="AE91" s="30">
+        <f>Codex_calc!AE91</f>
+        <v>32.2173913043478</v>
+      </c>
+      <c r="AF91" s="30">
+        <f>Codex_calc!AF91</f>
+        <v>0</v>
+      </c>
+      <c r="AG91" s="30">
+        <f>Codex_calc!AG91</f>
+        <v>0</v>
+      </c>
+      <c r="AH91" s="30">
+        <f>Codex_calc!AH91</f>
+        <v>0</v>
+      </c>
+      <c r="AI91" s="30">
+        <f>Codex_calc!AI91</f>
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="30">
+        <f>Codex_calc!AJ91</f>
+        <v>0</v>
+      </c>
+      <c r="AK91" s="30">
+        <f>Codex_calc!AK91</f>
+        <v>0</v>
+      </c>
+      <c r="AL91" s="30">
+        <f>Codex_calc!AL91</f>
+        <v>0</v>
+      </c>
+      <c r="AM91" s="30">
+        <f>Codex_calc!AM91</f>
+        <v>0</v>
+      </c>
+      <c r="AN91" s="30">
+        <f>Codex_calc!AN91</f>
+        <v>0</v>
+      </c>
       <c r="AO91" t="str">
         <f>Codex_calc!AO91</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="92" spans="3:41">
+    <row r="92" hidden="1" spans="3:41">
       <c r="C92" t="str">
         <f>Codex_calc!C92</f>
         <v>MINCuRSV1</v>
@@ -10751,7 +11716,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="93" spans="3:41">
+    <row r="93" hidden="1" spans="3:41">
       <c r="C93" t="str">
         <f>Codex_calc!C93</f>
         <v>MINCuRSV1</v>
@@ -10919,47 +11884,152 @@
         <v>BNDACT</v>
       </c>
       <c r="E94"/>
-      <c r="F94"/>
-      <c r="G94"/>
-      <c r="H94"/>
-      <c r="I94"/>
-      <c r="J94"/>
-      <c r="K94"/>
-      <c r="L94"/>
-      <c r="M94"/>
-      <c r="N94"/>
-      <c r="O94"/>
-      <c r="P94"/>
-      <c r="Q94"/>
-      <c r="R94"/>
-      <c r="S94"/>
-      <c r="T94"/>
-      <c r="U94"/>
-      <c r="V94"/>
-      <c r="W94"/>
-      <c r="X94"/>
-      <c r="Y94"/>
-      <c r="Z94"/>
-      <c r="AA94"/>
-      <c r="AB94"/>
-      <c r="AC94"/>
-      <c r="AD94"/>
-      <c r="AE94"/>
-      <c r="AF94"/>
-      <c r="AG94"/>
-      <c r="AH94"/>
-      <c r="AI94"/>
-      <c r="AJ94"/>
-      <c r="AK94"/>
-      <c r="AL94"/>
-      <c r="AM94"/>
-      <c r="AN94"/>
+      <c r="F94" s="30">
+        <f>Codex_calc!F94</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="30">
+        <f>Codex_calc!G94</f>
+        <v>205.2</v>
+      </c>
+      <c r="H94" s="30">
+        <f>Codex_calc!H94</f>
+        <v>36.1826086956522</v>
+      </c>
+      <c r="I94" s="30">
+        <f>Codex_calc!I94</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="30">
+        <f>Codex_calc!J94</f>
+        <v>0</v>
+      </c>
+      <c r="K94" s="30">
+        <f>Codex_calc!K94</f>
+        <v>0</v>
+      </c>
+      <c r="L94" s="30">
+        <f>Codex_calc!L94</f>
+        <v>0</v>
+      </c>
+      <c r="M94" s="30">
+        <f>Codex_calc!M94</f>
+        <v>89.2173913043478</v>
+      </c>
+      <c r="N94" s="30">
+        <f>Codex_calc!N94</f>
+        <v>0</v>
+      </c>
+      <c r="O94" s="30">
+        <f>Codex_calc!O94</f>
+        <v>0</v>
+      </c>
+      <c r="P94" s="30">
+        <f>Codex_calc!P94</f>
+        <v>0</v>
+      </c>
+      <c r="Q94" s="30">
+        <f>Codex_calc!Q94</f>
+        <v>0</v>
+      </c>
+      <c r="R94" s="30">
+        <f>Codex_calc!R94</f>
+        <v>0</v>
+      </c>
+      <c r="S94" s="30">
+        <f>Codex_calc!S94</f>
+        <v>0</v>
+      </c>
+      <c r="T94" s="30">
+        <f>Codex_calc!T94</f>
+        <v>0</v>
+      </c>
+      <c r="U94" s="30">
+        <f>Codex_calc!U94</f>
+        <v>1.14</v>
+      </c>
+      <c r="V94" s="30">
+        <f>Codex_calc!V94</f>
+        <v>0</v>
+      </c>
+      <c r="W94" s="30">
+        <f>Codex_calc!W94</f>
+        <v>0</v>
+      </c>
+      <c r="X94" s="30">
+        <f>Codex_calc!X94</f>
+        <v>0</v>
+      </c>
+      <c r="Y94" s="30">
+        <f>Codex_calc!Y94</f>
+        <v>396.521739130435</v>
+      </c>
+      <c r="Z94" s="30">
+        <f>Codex_calc!Z94</f>
+        <v>0</v>
+      </c>
+      <c r="AA94" s="30">
+        <f>Codex_calc!AA94</f>
+        <v>108.547826086957</v>
+      </c>
+      <c r="AB94" s="30">
+        <f>Codex_calc!AB94</f>
+        <v>0</v>
+      </c>
+      <c r="AC94" s="30">
+        <f>Codex_calc!AC94</f>
+        <v>20.3217391304348</v>
+      </c>
+      <c r="AD94" s="30">
+        <f>Codex_calc!AD94</f>
+        <v>219.078260869565</v>
+      </c>
+      <c r="AE94" s="30">
+        <f>Codex_calc!AE94</f>
+        <v>64.4347826086956</v>
+      </c>
+      <c r="AF94" s="30">
+        <f>Codex_calc!AF94</f>
+        <v>0</v>
+      </c>
+      <c r="AG94" s="30">
+        <f>Codex_calc!AG94</f>
+        <v>0</v>
+      </c>
+      <c r="AH94" s="30">
+        <f>Codex_calc!AH94</f>
+        <v>0</v>
+      </c>
+      <c r="AI94" s="30">
+        <f>Codex_calc!AI94</f>
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="30">
+        <f>Codex_calc!AJ94</f>
+        <v>0</v>
+      </c>
+      <c r="AK94" s="30">
+        <f>Codex_calc!AK94</f>
+        <v>0</v>
+      </c>
+      <c r="AL94" s="30">
+        <f>Codex_calc!AL94</f>
+        <v>0</v>
+      </c>
+      <c r="AM94" s="30">
+        <f>Codex_calc!AM94</f>
+        <v>0</v>
+      </c>
+      <c r="AN94" s="30">
+        <f>Codex_calc!AN94</f>
+        <v>0</v>
+      </c>
       <c r="AO94" t="str">
         <f>Codex_calc!AO94</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="95" spans="3:41">
+    <row r="95" hidden="1" spans="3:41">
       <c r="C95" t="str">
         <f>Codex_calc!C95</f>
         <v>MINCuRSV2</v>
@@ -11114,7 +12184,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="96" spans="3:41">
+    <row r="96" hidden="1" spans="3:41">
       <c r="C96" t="str">
         <f>Codex_calc!C96</f>
         <v>MINCuRSV2</v>
@@ -11272,7 +12342,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="97" spans="3:41">
+    <row r="97" hidden="1" spans="3:41">
       <c r="C97" t="str">
         <f>Codex_calc!C97</f>
         <v>MINCuRSV3</v>
@@ -11285,22 +12355,13 @@
       <c r="F97"/>
       <c r="G97"/>
       <c r="H97"/>
-      <c r="I97"/>
-      <c r="J97"/>
       <c r="K97"/>
       <c r="L97"/>
       <c r="M97"/>
-      <c r="N97"/>
-      <c r="O97"/>
       <c r="P97"/>
-      <c r="Q97"/>
       <c r="R97"/>
-      <c r="S97"/>
       <c r="T97"/>
       <c r="U97"/>
-      <c r="V97"/>
-      <c r="W97"/>
-      <c r="X97"/>
       <c r="Y97"/>
       <c r="Z97"/>
       <c r="AA97"/>
@@ -11312,17 +12373,14 @@
       <c r="AG97"/>
       <c r="AH97"/>
       <c r="AI97"/>
-      <c r="AJ97"/>
       <c r="AK97"/>
-      <c r="AL97"/>
       <c r="AM97"/>
-      <c r="AN97"/>
       <c r="AO97" t="str">
         <f>Codex_calc!AO97</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="98" spans="3:41">
+    <row r="98" hidden="1" spans="3:41">
       <c r="C98" t="str">
         <f>Codex_calc!C98</f>
         <v>MINCuRSV3</v>
@@ -11477,7 +12535,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="99" spans="3:41">
+    <row r="99" hidden="1" spans="3:41">
       <c r="C99" t="str">
         <f>Codex_calc!C99</f>
         <v>MINCuRSV3</v>
@@ -11635,7 +12693,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="100" spans="3:41">
+    <row r="100" hidden="1" spans="3:41">
       <c r="C100" t="s">
         <v>63</v>
       </c>
@@ -11802,47 +12860,152 @@
         <v>BNDACT</v>
       </c>
       <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
-      <c r="I101"/>
-      <c r="J101"/>
-      <c r="K101"/>
-      <c r="L101"/>
-      <c r="M101"/>
-      <c r="N101"/>
-      <c r="O101"/>
-      <c r="P101"/>
-      <c r="Q101"/>
-      <c r="R101"/>
-      <c r="S101"/>
-      <c r="T101"/>
-      <c r="U101"/>
-      <c r="V101"/>
-      <c r="W101"/>
-      <c r="X101"/>
-      <c r="Y101"/>
-      <c r="Z101"/>
-      <c r="AA101"/>
-      <c r="AB101"/>
-      <c r="AC101"/>
-      <c r="AD101"/>
-      <c r="AE101"/>
-      <c r="AF101"/>
-      <c r="AG101"/>
-      <c r="AH101"/>
-      <c r="AI101"/>
-      <c r="AJ101"/>
-      <c r="AK101"/>
-      <c r="AL101"/>
-      <c r="AM101"/>
-      <c r="AN101"/>
+      <c r="F101" s="30">
+        <f>Codex_calc!F101</f>
+        <v>0</v>
+      </c>
+      <c r="G101" s="30">
+        <f>Codex_calc!G101</f>
+        <v>175.30025</v>
+      </c>
+      <c r="H101" s="30">
+        <f>Codex_calc!H101</f>
+        <v>0</v>
+      </c>
+      <c r="I101" s="30">
+        <f>Codex_calc!I101</f>
+        <v>0.16307</v>
+      </c>
+      <c r="J101" s="30">
+        <f>Codex_calc!J101</f>
+        <v>0</v>
+      </c>
+      <c r="K101" s="30">
+        <f>Codex_calc!K101</f>
+        <v>0</v>
+      </c>
+      <c r="L101" s="30">
+        <f>Codex_calc!L101</f>
+        <v>52.99775</v>
+      </c>
+      <c r="M101" s="30">
+        <f>Codex_calc!M101</f>
+        <v>1141.49</v>
+      </c>
+      <c r="N101" s="30">
+        <f>Codex_calc!N101</f>
+        <v>0</v>
+      </c>
+      <c r="O101" s="30">
+        <f>Codex_calc!O101</f>
+        <v>0</v>
+      </c>
+      <c r="P101" s="30">
+        <f>Codex_calc!P101</f>
+        <v>0</v>
+      </c>
+      <c r="Q101" s="30">
+        <f>Codex_calc!Q101</f>
+        <v>0.114149</v>
+      </c>
+      <c r="R101" s="30">
+        <f>Codex_calc!R101</f>
+        <v>0</v>
+      </c>
+      <c r="S101" s="30">
+        <f>Codex_calc!S101</f>
+        <v>0</v>
+      </c>
+      <c r="T101" s="30">
+        <f>Codex_calc!T101</f>
+        <v>0</v>
+      </c>
+      <c r="U101" s="30">
+        <f>Codex_calc!U101</f>
+        <v>13.86095</v>
+      </c>
+      <c r="V101" s="30">
+        <f>Codex_calc!V101</f>
+        <v>0</v>
+      </c>
+      <c r="W101" s="30">
+        <f>Codex_calc!W101</f>
+        <v>0</v>
+      </c>
+      <c r="X101" s="30">
+        <f>Codex_calc!X101</f>
+        <v>0</v>
+      </c>
+      <c r="Y101" s="30">
+        <f>Codex_calc!Y101</f>
+        <v>0</v>
+      </c>
+      <c r="Z101" s="30">
+        <f>Codex_calc!Z101</f>
+        <v>0</v>
+      </c>
+      <c r="AA101" s="30">
+        <f>Codex_calc!AA101</f>
+        <v>7.126159</v>
+      </c>
+      <c r="AB101" s="30">
+        <f>Codex_calc!AB101</f>
+        <v>5.38131</v>
+      </c>
+      <c r="AC101" s="30">
+        <f>Codex_calc!AC101</f>
+        <v>0</v>
+      </c>
+      <c r="AD101" s="30">
+        <f>Codex_calc!AD101</f>
+        <v>9.94727</v>
+      </c>
+      <c r="AE101" s="30">
+        <f>Codex_calc!AE101</f>
+        <v>20.38375</v>
+      </c>
+      <c r="AF101" s="30">
+        <f>Codex_calc!AF101</f>
+        <v>0</v>
+      </c>
+      <c r="AG101" s="30">
+        <f>Codex_calc!AG101</f>
+        <v>0</v>
+      </c>
+      <c r="AH101" s="30">
+        <f>Codex_calc!AH101</f>
+        <v>0</v>
+      </c>
+      <c r="AI101" s="30">
+        <f>Codex_calc!AI101</f>
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="30">
+        <f>Codex_calc!AJ101</f>
+        <v>0</v>
+      </c>
+      <c r="AK101" s="30">
+        <f>Codex_calc!AK101</f>
+        <v>1.79377</v>
+      </c>
+      <c r="AL101" s="30">
+        <f>Codex_calc!AL101</f>
+        <v>0</v>
+      </c>
+      <c r="AM101" s="30">
+        <f>Codex_calc!AM101</f>
+        <v>0.65228</v>
+      </c>
+      <c r="AN101" s="30">
+        <f>Codex_calc!AN101</f>
+        <v>0</v>
+      </c>
       <c r="AO101" t="str">
         <f>Codex_calc!AO101</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="102" spans="3:41">
+    <row r="102" hidden="1" spans="3:41">
       <c r="C102" t="str">
         <f>Codex_calc!C102</f>
         <v>MINGrRSV1</v>
@@ -11997,7 +13160,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="103" spans="3:41">
+    <row r="103" hidden="1" spans="3:41">
       <c r="C103" t="str">
         <f>Codex_calc!C103</f>
         <v>MINGrRSV1</v>
@@ -12165,47 +13328,152 @@
         <v>BNDACT</v>
       </c>
       <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104"/>
-      <c r="H104"/>
-      <c r="I104"/>
-      <c r="J104"/>
-      <c r="K104"/>
-      <c r="L104"/>
-      <c r="M104"/>
-      <c r="N104"/>
-      <c r="O104"/>
-      <c r="P104"/>
-      <c r="Q104"/>
-      <c r="R104"/>
-      <c r="S104"/>
-      <c r="T104"/>
-      <c r="U104"/>
-      <c r="V104"/>
-      <c r="W104"/>
-      <c r="X104"/>
-      <c r="Y104"/>
-      <c r="Z104"/>
-      <c r="AA104"/>
-      <c r="AB104"/>
-      <c r="AC104"/>
-      <c r="AD104"/>
-      <c r="AE104"/>
-      <c r="AF104"/>
-      <c r="AG104"/>
-      <c r="AH104"/>
-      <c r="AI104"/>
-      <c r="AJ104"/>
-      <c r="AK104"/>
-      <c r="AL104"/>
-      <c r="AM104"/>
-      <c r="AN104"/>
+      <c r="F104" s="30">
+        <f>Codex_calc!F104</f>
+        <v>0</v>
+      </c>
+      <c r="G104" s="30">
+        <f>Codex_calc!G104</f>
+        <v>350.6005</v>
+      </c>
+      <c r="H104" s="30">
+        <f>Codex_calc!H104</f>
+        <v>0</v>
+      </c>
+      <c r="I104" s="30">
+        <f>Codex_calc!I104</f>
+        <v>0.32614</v>
+      </c>
+      <c r="J104" s="30">
+        <f>Codex_calc!J104</f>
+        <v>0</v>
+      </c>
+      <c r="K104" s="30">
+        <f>Codex_calc!K104</f>
+        <v>0</v>
+      </c>
+      <c r="L104" s="30">
+        <f>Codex_calc!L104</f>
+        <v>105.9955</v>
+      </c>
+      <c r="M104" s="30">
+        <f>Codex_calc!M104</f>
+        <v>2282.98</v>
+      </c>
+      <c r="N104" s="30">
+        <f>Codex_calc!N104</f>
+        <v>0</v>
+      </c>
+      <c r="O104" s="30">
+        <f>Codex_calc!O104</f>
+        <v>0</v>
+      </c>
+      <c r="P104" s="30">
+        <f>Codex_calc!P104</f>
+        <v>0</v>
+      </c>
+      <c r="Q104" s="30">
+        <f>Codex_calc!Q104</f>
+        <v>0.228298</v>
+      </c>
+      <c r="R104" s="30">
+        <f>Codex_calc!R104</f>
+        <v>0</v>
+      </c>
+      <c r="S104" s="30">
+        <f>Codex_calc!S104</f>
+        <v>0</v>
+      </c>
+      <c r="T104" s="30">
+        <f>Codex_calc!T104</f>
+        <v>0</v>
+      </c>
+      <c r="U104" s="30">
+        <f>Codex_calc!U104</f>
+        <v>27.7219</v>
+      </c>
+      <c r="V104" s="30">
+        <f>Codex_calc!V104</f>
+        <v>0</v>
+      </c>
+      <c r="W104" s="30">
+        <f>Codex_calc!W104</f>
+        <v>0</v>
+      </c>
+      <c r="X104" s="30">
+        <f>Codex_calc!X104</f>
+        <v>0</v>
+      </c>
+      <c r="Y104" s="30">
+        <f>Codex_calc!Y104</f>
+        <v>0</v>
+      </c>
+      <c r="Z104" s="30">
+        <f>Codex_calc!Z104</f>
+        <v>0</v>
+      </c>
+      <c r="AA104" s="30">
+        <f>Codex_calc!AA104</f>
+        <v>14.252318</v>
+      </c>
+      <c r="AB104" s="30">
+        <f>Codex_calc!AB104</f>
+        <v>10.76262</v>
+      </c>
+      <c r="AC104" s="30">
+        <f>Codex_calc!AC104</f>
+        <v>0</v>
+      </c>
+      <c r="AD104" s="30">
+        <f>Codex_calc!AD104</f>
+        <v>19.89454</v>
+      </c>
+      <c r="AE104" s="30">
+        <f>Codex_calc!AE104</f>
+        <v>40.7675</v>
+      </c>
+      <c r="AF104" s="30">
+        <f>Codex_calc!AF104</f>
+        <v>0</v>
+      </c>
+      <c r="AG104" s="30">
+        <f>Codex_calc!AG104</f>
+        <v>0</v>
+      </c>
+      <c r="AH104" s="30">
+        <f>Codex_calc!AH104</f>
+        <v>0</v>
+      </c>
+      <c r="AI104" s="30">
+        <f>Codex_calc!AI104</f>
+        <v>0</v>
+      </c>
+      <c r="AJ104" s="30">
+        <f>Codex_calc!AJ104</f>
+        <v>0</v>
+      </c>
+      <c r="AK104" s="30">
+        <f>Codex_calc!AK104</f>
+        <v>3.58754</v>
+      </c>
+      <c r="AL104" s="30">
+        <f>Codex_calc!AL104</f>
+        <v>0</v>
+      </c>
+      <c r="AM104" s="30">
+        <f>Codex_calc!AM104</f>
+        <v>1.30456</v>
+      </c>
+      <c r="AN104" s="30">
+        <f>Codex_calc!AN104</f>
+        <v>0</v>
+      </c>
       <c r="AO104" t="str">
         <f>Codex_calc!AO104</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="105" spans="3:41">
+    <row r="105" hidden="1" spans="3:41">
       <c r="C105" t="str">
         <f>Codex_calc!C105</f>
         <v>MINGrRSV2</v>
@@ -12360,7 +13628,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="106" spans="3:41">
+    <row r="106" hidden="1" spans="3:41">
       <c r="C106" t="str">
         <f>Codex_calc!C106</f>
         <v>MINGrRSV2</v>
@@ -12518,7 +13786,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="107" spans="3:41">
+    <row r="107" hidden="1" spans="3:41">
       <c r="C107" t="str">
         <f>Codex_calc!C107</f>
         <v>MINGrRSV3</v>
@@ -12531,22 +13799,13 @@
       <c r="F107"/>
       <c r="G107"/>
       <c r="H107"/>
-      <c r="I107"/>
-      <c r="J107"/>
       <c r="K107"/>
       <c r="L107"/>
       <c r="M107"/>
-      <c r="N107"/>
-      <c r="O107"/>
       <c r="P107"/>
-      <c r="Q107"/>
       <c r="R107"/>
-      <c r="S107"/>
       <c r="T107"/>
       <c r="U107"/>
-      <c r="V107"/>
-      <c r="W107"/>
-      <c r="X107"/>
       <c r="Y107"/>
       <c r="Z107"/>
       <c r="AA107"/>
@@ -12558,17 +13817,14 @@
       <c r="AG107"/>
       <c r="AH107"/>
       <c r="AI107"/>
-      <c r="AJ107"/>
       <c r="AK107"/>
-      <c r="AL107"/>
       <c r="AM107"/>
-      <c r="AN107"/>
       <c r="AO107" t="str">
         <f>Codex_calc!AO107</f>
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="108" spans="3:41">
+    <row r="108" hidden="1" spans="3:41">
       <c r="C108" t="str">
         <f>Codex_calc!C108</f>
         <v>MINGrRSV3</v>
@@ -12723,7 +13979,7 @@
         <v>2019, 2130</v>
       </c>
     </row>
-    <row r="109" spans="3:41">
+    <row r="109" hidden="1" spans="3:41">
       <c r="C109" t="str">
         <f>Codex_calc!C109</f>
         <v>MINGrRSV3</v>
@@ -13314,17 +14570,17 @@
         <f>F102/F101</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G116" s="1" t="e">
+      <c r="G116" s="1">
         <f t="shared" ref="G116:AN116" si="4">G102/G101</f>
-        <v>#DIV/0!</v>
+        <v>325.581395348837</v>
       </c>
       <c r="H116" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I116" s="1" t="e">
+      <c r="I116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="J116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -13334,13 +14590,13 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L116" s="1" t="e">
+      <c r="L116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M116" s="1" t="e">
+        <v>1138.46153846154</v>
+      </c>
+      <c r="M116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>71.4285714285714</v>
       </c>
       <c r="N116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -13354,9 +14610,9 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q116" s="1" t="e">
+      <c r="Q116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="R116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -13370,9 +14626,9 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U116" s="1" t="e">
+      <c r="U116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>505.882352941176</v>
       </c>
       <c r="V116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -13394,25 +14650,25 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA116" s="1" t="e">
+      <c r="AA116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB116" s="1" t="e">
+        <v>1029.74828375286</v>
+      </c>
+      <c r="AB116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>90.9090909090909</v>
       </c>
       <c r="AC116" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD116" s="1" t="e">
+      <c r="AD116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE116" s="1" t="e">
+        <v>1229.50819672131</v>
+      </c>
+      <c r="AE116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>560</v>
       </c>
       <c r="AF116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -13434,17 +14690,17 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK116" s="1" t="e">
+      <c r="AK116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>3136.36363636364</v>
       </c>
       <c r="AL116" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AM116" s="1" t="e">
+      <c r="AM116" s="1">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="AN116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -15217,6 +16473,34 @@
       <c r="AO172" s="38"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C39:AO109" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="MINAlRSV1"/>
+        <filter val="MINCoRSV1"/>
+        <filter val="MINCuRSV1"/>
+        <filter val="MINGrRSV1"/>
+        <filter val="MINLiRSV1"/>
+        <filter val="MINMnRSV1"/>
+        <filter val="MINNiRSV1"/>
+        <filter val="MINAlRSV2"/>
+        <filter val="MINCoRSV2"/>
+        <filter val="MINCuRSV2"/>
+        <filter val="MINGrRSV2"/>
+        <filter val="MINLiRSV2"/>
+        <filter val="MINMnRSV2"/>
+        <filter val="MINNiRSV2"/>
+        <filter val="pset_pn"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="BNDACT"/>
+        <filter val="Attribute"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -22113,7 +23397,9 @@
   <dimension ref="A1:G94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="7" width="20" style="1" customWidth="1"/>
+    <col min="1" max="5" width="20" style="1" customWidth="1"/>
+    <col min="6" max="6" width="71" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">

--- a/SuppXLS/Scen_usingStepMining_n_mute_original_Min2.xlsx
+++ b/SuppXLS/Scen_usingStepMining_n_mute_original_Min2.xlsx
@@ -4459,146 +4459,41 @@
         <v>CUM</v>
       </c>
       <c r="E42" s="32"/>
-      <c r="F42" s="32">
-        <f>Codex_calc!F42</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="32">
-        <f>Codex_calc!G42</f>
-        <v>1255.49969906292</v>
-      </c>
-      <c r="H42" s="33">
-        <f>Codex_calc!H42</f>
-        <v>4287.65214468541</v>
-      </c>
-      <c r="I42" s="32">
-        <f>Codex_calc!I42</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="32">
-        <f>Codex_calc!J42</f>
-        <v>0</v>
-      </c>
-      <c r="K42" s="32">
-        <f>Codex_calc!K42</f>
-        <v>0</v>
-      </c>
-      <c r="L42" s="32">
-        <f>Codex_calc!L42</f>
-        <v>195.317977260422</v>
-      </c>
-      <c r="M42" s="33">
-        <f>Codex_calc!M42</f>
-        <v>141.234113860241</v>
-      </c>
-      <c r="N42" s="32">
-        <f>Codex_calc!N42</f>
-        <v>0</v>
-      </c>
-      <c r="O42" s="32">
-        <f>Codex_calc!O42</f>
-        <v>0</v>
-      </c>
-      <c r="P42" s="32">
-        <f>Codex_calc!P42</f>
-        <v>0</v>
-      </c>
-      <c r="Q42" s="32">
-        <f>Codex_calc!Q42</f>
-        <v>94.0713806172166</v>
-      </c>
-      <c r="R42" s="32">
-        <f>Codex_calc!R42</f>
-        <v>0</v>
-      </c>
-      <c r="S42" s="32">
-        <f>Codex_calc!S42</f>
-        <v>0</v>
-      </c>
-      <c r="T42" s="32">
-        <f>Codex_calc!T42</f>
-        <v>0</v>
-      </c>
-      <c r="U42" s="32">
-        <f>Codex_calc!U42</f>
-        <v>0</v>
-      </c>
-      <c r="V42" s="32">
-        <f>Codex_calc!V42</f>
-        <v>0</v>
-      </c>
-      <c r="W42" s="32">
-        <f>Codex_calc!W42</f>
-        <v>0</v>
-      </c>
-      <c r="X42" s="32">
-        <f>Codex_calc!X42</f>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="32">
-        <f>Codex_calc!Y42</f>
-        <v>10711.7730997293</v>
-      </c>
-      <c r="Z42" s="32">
-        <f>Codex_calc!Z42</f>
-        <v>0</v>
-      </c>
-      <c r="AA42" s="32">
-        <f>Codex_calc!AA42</f>
-        <v>2108.04312881084</v>
-      </c>
-      <c r="AB42" s="32">
-        <f>Codex_calc!AB42</f>
-        <v>0</v>
-      </c>
-      <c r="AC42" s="32">
-        <f>Codex_calc!AC42</f>
-        <v>0</v>
-      </c>
-      <c r="AD42" s="32">
-        <f>Codex_calc!AD42</f>
-        <v>0</v>
-      </c>
-      <c r="AE42" s="32">
-        <f>Codex_calc!AE42</f>
-        <v>0</v>
-      </c>
-      <c r="AF42" s="32">
-        <f>Codex_calc!AF42</f>
-        <v>0</v>
-      </c>
-      <c r="AG42" s="32">
-        <f>Codex_calc!AG42</f>
-        <v>0</v>
-      </c>
-      <c r="AH42" s="32">
-        <f>Codex_calc!AH42</f>
-        <v>124.694798393575</v>
-      </c>
-      <c r="AI42" s="32">
-        <f>Codex_calc!AI42</f>
-        <v>32.0074152680022</v>
-      </c>
-      <c r="AJ42" s="32">
-        <f>Codex_calc!AJ42</f>
-        <v>0</v>
-      </c>
-      <c r="AK42" s="32">
-        <f>Codex_calc!AK42</f>
-        <v>0</v>
-      </c>
-      <c r="AL42" s="32">
-        <f>Codex_calc!AL42</f>
-        <v>0</v>
-      </c>
-      <c r="AM42" s="32">
-        <f>Codex_calc!AM42</f>
-        <v>0</v>
-      </c>
-      <c r="AN42" s="32">
-        <f>Codex_calc!AN42</f>
-        <v>122.822577777778</v>
-      </c>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="33"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="32"/>
+      <c r="X42" s="32"/>
+      <c r="Y42" s="32"/>
+      <c r="Z42" s="32"/>
+      <c r="AA42" s="32"/>
+      <c r="AB42" s="32"/>
+      <c r="AC42" s="32"/>
+      <c r="AD42" s="32"/>
+      <c r="AE42" s="32"/>
+      <c r="AF42" s="32"/>
+      <c r="AG42" s="32"/>
+      <c r="AH42" s="32"/>
+      <c r="AI42" s="32"/>
+      <c r="AJ42" s="32"/>
+      <c r="AK42" s="32"/>
+      <c r="AL42" s="32"/>
+      <c r="AM42" s="32"/>
+      <c r="AN42" s="32"/>
       <c r="AO42" t="str">
         <f>Codex_calc!AO42</f>
         <v>2019, 2130</v>
@@ -4927,146 +4822,41 @@
         <v>CUM</v>
       </c>
       <c r="E45" s="32"/>
-      <c r="F45" s="32">
-        <f>Codex_calc!F45</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="32">
-        <f>Codex_calc!G45</f>
-        <v>1525.9653935711</v>
-      </c>
-      <c r="H45" s="33">
-        <f>Codex_calc!H45</f>
-        <v>2609.34575023318</v>
-      </c>
-      <c r="I45" s="32">
-        <f>Codex_calc!I45</f>
-        <v>32.7025435073628</v>
-      </c>
-      <c r="J45" s="32">
-        <f>Codex_calc!J45</f>
-        <v>0</v>
-      </c>
-      <c r="K45" s="32">
-        <f>Codex_calc!K45</f>
-        <v>0</v>
-      </c>
-      <c r="L45" s="32">
-        <f>Codex_calc!L45</f>
-        <v>332.113163822226</v>
-      </c>
-      <c r="M45" s="33">
-        <f>Codex_calc!M45</f>
-        <v>733.619844112292</v>
-      </c>
-      <c r="N45" s="32">
-        <f>Codex_calc!N45</f>
-        <v>0</v>
-      </c>
-      <c r="O45" s="32">
-        <f>Codex_calc!O45</f>
-        <v>748.933838657282</v>
-      </c>
-      <c r="P45" s="32">
-        <f>Codex_calc!P45</f>
-        <v>0</v>
-      </c>
-      <c r="Q45" s="32">
-        <f>Codex_calc!Q45</f>
-        <v>2143.2183216026</v>
-      </c>
-      <c r="R45" s="32">
-        <f>Codex_calc!R45</f>
-        <v>0</v>
-      </c>
-      <c r="S45" s="32">
-        <f>Codex_calc!S45</f>
-        <v>0</v>
-      </c>
-      <c r="T45" s="32">
-        <f>Codex_calc!T45</f>
-        <v>0</v>
-      </c>
-      <c r="U45" s="32">
-        <f>Codex_calc!U45</f>
-        <v>0</v>
-      </c>
-      <c r="V45" s="32">
-        <f>Codex_calc!V45</f>
-        <v>0</v>
-      </c>
-      <c r="W45" s="32">
-        <f>Codex_calc!W45</f>
-        <v>0</v>
-      </c>
-      <c r="X45" s="32">
-        <f>Codex_calc!X45</f>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="32">
-        <f>Codex_calc!Y45</f>
-        <v>24639.9614434218</v>
-      </c>
-      <c r="Z45" s="32">
-        <f>Codex_calc!Z45</f>
-        <v>0</v>
-      </c>
-      <c r="AA45" s="32">
-        <f>Codex_calc!AA45</f>
-        <v>10676.420788286</v>
-      </c>
-      <c r="AB45" s="32">
-        <f>Codex_calc!AB45</f>
-        <v>0</v>
-      </c>
-      <c r="AC45" s="32">
-        <f>Codex_calc!AC45</f>
-        <v>0</v>
-      </c>
-      <c r="AD45" s="32">
-        <f>Codex_calc!AD45</f>
-        <v>0</v>
-      </c>
-      <c r="AE45" s="32">
-        <f>Codex_calc!AE45</f>
-        <v>0</v>
-      </c>
-      <c r="AF45" s="32">
-        <f>Codex_calc!AF45</f>
-        <v>0</v>
-      </c>
-      <c r="AG45" s="32">
-        <f>Codex_calc!AG45</f>
-        <v>0</v>
-      </c>
-      <c r="AH45" s="32">
-        <f>Codex_calc!AH45</f>
-        <v>103.146036947791</v>
-      </c>
-      <c r="AI45" s="32">
-        <f>Codex_calc!AI45</f>
-        <v>16.4666247969681</v>
-      </c>
-      <c r="AJ45" s="32">
-        <f>Codex_calc!AJ45</f>
-        <v>0</v>
-      </c>
-      <c r="AK45" s="32">
-        <f>Codex_calc!AK45</f>
-        <v>0</v>
-      </c>
-      <c r="AL45" s="32">
-        <f>Codex_calc!AL45</f>
-        <v>49.0538152610442</v>
-      </c>
-      <c r="AM45" s="32">
-        <f>Codex_calc!AM45</f>
-        <v>0</v>
-      </c>
-      <c r="AN45" s="32">
-        <f>Codex_calc!AN45</f>
-        <v>505.556795716198</v>
-      </c>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="33"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="33"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="32"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
+      <c r="V45" s="32"/>
+      <c r="W45" s="32"/>
+      <c r="X45" s="32"/>
+      <c r="Y45" s="32"/>
+      <c r="Z45" s="32"/>
+      <c r="AA45" s="32"/>
+      <c r="AB45" s="32"/>
+      <c r="AC45" s="32"/>
+      <c r="AD45" s="32"/>
+      <c r="AE45" s="32"/>
+      <c r="AF45" s="32"/>
+      <c r="AG45" s="32"/>
+      <c r="AH45" s="32"/>
+      <c r="AI45" s="32"/>
+      <c r="AJ45" s="32"/>
+      <c r="AK45" s="32"/>
+      <c r="AL45" s="32"/>
+      <c r="AM45" s="32"/>
+      <c r="AN45" s="32"/>
       <c r="AO45" t="str">
         <f>Codex_calc!AO45</f>
         <v>2019, 2130</v>
@@ -5810,146 +5600,41 @@
         <v>CUM</v>
       </c>
       <c r="E52" s="32"/>
-      <c r="F52" s="32">
-        <f>Codex_calc!F52</f>
-        <v>0</v>
-      </c>
-      <c r="G52" s="32">
-        <f>Codex_calc!G52</f>
-        <v>0</v>
-      </c>
-      <c r="H52" s="33">
-        <f>Codex_calc!H52</f>
-        <v>3557.69230769231</v>
-      </c>
-      <c r="I52" s="32">
-        <f>Codex_calc!I52</f>
-        <v>0</v>
-      </c>
-      <c r="J52" s="32">
-        <f>Codex_calc!J52</f>
-        <v>0</v>
-      </c>
-      <c r="K52" s="32">
-        <f>Codex_calc!K52</f>
-        <v>0</v>
-      </c>
-      <c r="L52" s="32">
-        <f>Codex_calc!L52</f>
-        <v>2276.92307692308</v>
-      </c>
-      <c r="M52" s="33">
-        <f>Codex_calc!M52</f>
-        <v>626.153846153846</v>
-      </c>
-      <c r="N52" s="32">
-        <f>Codex_calc!N52</f>
-        <v>0</v>
-      </c>
-      <c r="O52" s="32">
-        <f>Codex_calc!O52</f>
-        <v>0</v>
-      </c>
-      <c r="P52" s="32">
-        <f>Codex_calc!P52</f>
-        <v>0</v>
-      </c>
-      <c r="Q52" s="32">
-        <f>Codex_calc!Q52</f>
-        <v>0</v>
-      </c>
-      <c r="R52" s="32">
-        <f>Codex_calc!R52</f>
-        <v>0</v>
-      </c>
-      <c r="S52" s="32">
-        <f>Codex_calc!S52</f>
-        <v>0</v>
-      </c>
-      <c r="T52" s="32">
-        <f>Codex_calc!T52</f>
-        <v>0</v>
-      </c>
-      <c r="U52" s="32">
-        <f>Codex_calc!U52</f>
-        <v>0</v>
-      </c>
-      <c r="V52" s="32">
-        <f>Codex_calc!V52</f>
-        <v>0</v>
-      </c>
-      <c r="W52" s="32">
-        <f>Codex_calc!W52</f>
-        <v>0</v>
-      </c>
-      <c r="X52" s="32">
-        <f>Codex_calc!X52</f>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="32">
-        <f>Codex_calc!Y52</f>
-        <v>0</v>
-      </c>
-      <c r="Z52" s="32">
-        <f>Codex_calc!Z52</f>
-        <v>0</v>
-      </c>
-      <c r="AA52" s="32">
-        <f>Codex_calc!AA52</f>
-        <v>361.461538461538</v>
-      </c>
-      <c r="AB52" s="32">
-        <f>Codex_calc!AB52</f>
-        <v>0</v>
-      </c>
-      <c r="AC52" s="32">
-        <f>Codex_calc!AC52</f>
-        <v>0</v>
-      </c>
-      <c r="AD52" s="32">
-        <f>Codex_calc!AD52</f>
-        <v>11811.5384615385</v>
-      </c>
-      <c r="AE52" s="32">
-        <f>Codex_calc!AE52</f>
-        <v>1181.15384615385</v>
-      </c>
-      <c r="AF52" s="32">
-        <f>Codex_calc!AF52</f>
-        <v>0</v>
-      </c>
-      <c r="AG52" s="32">
-        <f>Codex_calc!AG52</f>
-        <v>0</v>
-      </c>
-      <c r="AH52" s="32">
-        <f>Codex_calc!AH52</f>
-        <v>0</v>
-      </c>
-      <c r="AI52" s="32">
-        <f>Codex_calc!AI52</f>
-        <v>0</v>
-      </c>
-      <c r="AJ52" s="32">
-        <f>Codex_calc!AJ52</f>
-        <v>0</v>
-      </c>
-      <c r="AK52" s="32">
-        <f>Codex_calc!AK52</f>
-        <v>0</v>
-      </c>
-      <c r="AL52" s="32">
-        <f>Codex_calc!AL52</f>
-        <v>0</v>
-      </c>
-      <c r="AM52" s="32">
-        <f>Codex_calc!AM52</f>
-        <v>0</v>
-      </c>
-      <c r="AN52" s="32">
-        <f>Codex_calc!AN52</f>
-        <v>0</v>
-      </c>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="33"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="33"/>
+      <c r="N52" s="32"/>
+      <c r="O52" s="32"/>
+      <c r="P52" s="32"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="32"/>
+      <c r="S52" s="32"/>
+      <c r="T52" s="32"/>
+      <c r="U52" s="32"/>
+      <c r="V52" s="32"/>
+      <c r="W52" s="32"/>
+      <c r="X52" s="32"/>
+      <c r="Y52" s="32"/>
+      <c r="Z52" s="32"/>
+      <c r="AA52" s="32"/>
+      <c r="AB52" s="32"/>
+      <c r="AC52" s="32"/>
+      <c r="AD52" s="32"/>
+      <c r="AE52" s="32"/>
+      <c r="AF52" s="32"/>
+      <c r="AG52" s="32"/>
+      <c r="AH52" s="32"/>
+      <c r="AI52" s="32"/>
+      <c r="AJ52" s="32"/>
+      <c r="AK52" s="32"/>
+      <c r="AL52" s="32"/>
+      <c r="AM52" s="32"/>
+      <c r="AN52" s="32"/>
       <c r="AO52" t="str">
         <f>Codex_calc!AO52</f>
         <v>2019, 2130</v>
@@ -6278,146 +5963,41 @@
         <v>CUM</v>
       </c>
       <c r="E55" s="32"/>
-      <c r="F55" s="32">
-        <f>Codex_calc!F55</f>
-        <v>0</v>
-      </c>
-      <c r="G55" s="32">
-        <f>Codex_calc!G55</f>
-        <v>0</v>
-      </c>
-      <c r="H55" s="33">
-        <f>Codex_calc!H55</f>
-        <v>2668.26923076923</v>
-      </c>
-      <c r="I55" s="32">
-        <f>Codex_calc!I55</f>
-        <v>0</v>
-      </c>
-      <c r="J55" s="32">
-        <f>Codex_calc!J55</f>
-        <v>0</v>
-      </c>
-      <c r="K55" s="32">
-        <f>Codex_calc!K55</f>
-        <v>0</v>
-      </c>
-      <c r="L55" s="32">
-        <f>Codex_calc!L55</f>
-        <v>1707.69230769231</v>
-      </c>
-      <c r="M55" s="33">
-        <f>Codex_calc!M55</f>
-        <v>469.615384615385</v>
-      </c>
-      <c r="N55" s="32">
-        <f>Codex_calc!N55</f>
-        <v>0</v>
-      </c>
-      <c r="O55" s="32">
-        <f>Codex_calc!O55</f>
-        <v>0</v>
-      </c>
-      <c r="P55" s="32">
-        <f>Codex_calc!P55</f>
-        <v>0</v>
-      </c>
-      <c r="Q55" s="32">
-        <f>Codex_calc!Q55</f>
-        <v>0</v>
-      </c>
-      <c r="R55" s="32">
-        <f>Codex_calc!R55</f>
-        <v>0</v>
-      </c>
-      <c r="S55" s="32">
-        <f>Codex_calc!S55</f>
-        <v>0</v>
-      </c>
-      <c r="T55" s="32">
-        <f>Codex_calc!T55</f>
-        <v>0</v>
-      </c>
-      <c r="U55" s="32">
-        <f>Codex_calc!U55</f>
-        <v>0</v>
-      </c>
-      <c r="V55" s="32">
-        <f>Codex_calc!V55</f>
-        <v>0</v>
-      </c>
-      <c r="W55" s="32">
-        <f>Codex_calc!W55</f>
-        <v>0</v>
-      </c>
-      <c r="X55" s="32">
-        <f>Codex_calc!X55</f>
-        <v>0</v>
-      </c>
-      <c r="Y55" s="32">
-        <f>Codex_calc!Y55</f>
-        <v>0</v>
-      </c>
-      <c r="Z55" s="32">
-        <f>Codex_calc!Z55</f>
-        <v>0</v>
-      </c>
-      <c r="AA55" s="32">
-        <f>Codex_calc!AA55</f>
-        <v>271.096153846154</v>
-      </c>
-      <c r="AB55" s="32">
-        <f>Codex_calc!AB55</f>
-        <v>0</v>
-      </c>
-      <c r="AC55" s="32">
-        <f>Codex_calc!AC55</f>
-        <v>0</v>
-      </c>
-      <c r="AD55" s="32">
-        <f>Codex_calc!AD55</f>
-        <v>8858.65384615385</v>
-      </c>
-      <c r="AE55" s="32">
-        <f>Codex_calc!AE55</f>
-        <v>885.865384615385</v>
-      </c>
-      <c r="AF55" s="32">
-        <f>Codex_calc!AF55</f>
-        <v>0</v>
-      </c>
-      <c r="AG55" s="32">
-        <f>Codex_calc!AG55</f>
-        <v>0</v>
-      </c>
-      <c r="AH55" s="32">
-        <f>Codex_calc!AH55</f>
-        <v>0</v>
-      </c>
-      <c r="AI55" s="32">
-        <f>Codex_calc!AI55</f>
-        <v>0</v>
-      </c>
-      <c r="AJ55" s="32">
-        <f>Codex_calc!AJ55</f>
-        <v>0</v>
-      </c>
-      <c r="AK55" s="32">
-        <f>Codex_calc!AK55</f>
-        <v>0</v>
-      </c>
-      <c r="AL55" s="32">
-        <f>Codex_calc!AL55</f>
-        <v>0</v>
-      </c>
-      <c r="AM55" s="32">
-        <f>Codex_calc!AM55</f>
-        <v>0</v>
-      </c>
-      <c r="AN55" s="32">
-        <f>Codex_calc!AN55</f>
-        <v>0</v>
-      </c>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="33"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="33"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="32"/>
+      <c r="T55" s="32"/>
+      <c r="U55" s="32"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="32"/>
+      <c r="X55" s="32"/>
+      <c r="Y55" s="32"/>
+      <c r="Z55" s="32"/>
+      <c r="AA55" s="32"/>
+      <c r="AB55" s="32"/>
+      <c r="AC55" s="32"/>
+      <c r="AD55" s="32"/>
+      <c r="AE55" s="32"/>
+      <c r="AF55" s="32"/>
+      <c r="AG55" s="32"/>
+      <c r="AH55" s="32"/>
+      <c r="AI55" s="32"/>
+      <c r="AJ55" s="32"/>
+      <c r="AK55" s="32"/>
+      <c r="AL55" s="32"/>
+      <c r="AM55" s="32"/>
+      <c r="AN55" s="32"/>
       <c r="AO55" t="str">
         <f>Codex_calc!AO55</f>
         <v>2019, 2130</v>
@@ -6632,22 +6212,13 @@
       <c r="F58"/>
       <c r="G58"/>
       <c r="H58" s="29"/>
-      <c r="I58"/>
-      <c r="J58"/>
       <c r="K58"/>
       <c r="L58"/>
       <c r="M58" s="29"/>
-      <c r="N58"/>
-      <c r="O58"/>
       <c r="P58"/>
-      <c r="Q58"/>
       <c r="R58"/>
-      <c r="S58"/>
       <c r="T58"/>
       <c r="U58"/>
-      <c r="V58"/>
-      <c r="W58"/>
-      <c r="X58"/>
       <c r="Y58"/>
       <c r="Z58"/>
       <c r="AA58"/>
@@ -6659,11 +6230,8 @@
       <c r="AG58"/>
       <c r="AH58"/>
       <c r="AI58"/>
-      <c r="AJ58"/>
       <c r="AK58"/>
-      <c r="AL58"/>
       <c r="AM58"/>
-      <c r="AN58"/>
       <c r="AO58" t="str">
         <f>Codex_calc!AO58</f>
         <v>2019, 2130</v>
@@ -7149,146 +6717,41 @@
         <v>CUM</v>
       </c>
       <c r="E62"/>
-      <c r="F62">
-        <f>Codex_calc!F62</f>
-        <v>0</v>
-      </c>
-      <c r="G62">
-        <f>Codex_calc!G62</f>
-        <v>4332.41677419355</v>
-      </c>
-      <c r="H62" s="29">
-        <f>Codex_calc!H62</f>
-        <v>1207.39483870968</v>
-      </c>
-      <c r="I62">
-        <f>Codex_calc!I62</f>
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <f>Codex_calc!J62</f>
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <f>Codex_calc!K62</f>
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <f>Codex_calc!L62</f>
-        <v>0</v>
-      </c>
-      <c r="M62" s="29">
-        <f>Codex_calc!M62</f>
-        <v>113.637161290323</v>
-      </c>
-      <c r="N62">
-        <f>Codex_calc!N62</f>
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <f>Codex_calc!O62</f>
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <f>Codex_calc!P62</f>
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <f>Codex_calc!Q62</f>
-        <v>0</v>
-      </c>
-      <c r="R62">
-        <f>Codex_calc!R62</f>
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <f>Codex_calc!S62</f>
-        <v>0</v>
-      </c>
-      <c r="T62">
-        <f>Codex_calc!T62</f>
-        <v>0</v>
-      </c>
-      <c r="U62">
-        <f>Codex_calc!U62</f>
-        <v>0</v>
-      </c>
-      <c r="V62">
-        <f>Codex_calc!V62</f>
-        <v>0</v>
-      </c>
-      <c r="W62">
-        <f>Codex_calc!W62</f>
-        <v>0</v>
-      </c>
-      <c r="X62">
-        <f>Codex_calc!X62</f>
-        <v>0</v>
-      </c>
-      <c r="Y62">
-        <f>Codex_calc!Y62</f>
-        <v>355.116129032258</v>
-      </c>
-      <c r="Z62">
-        <f>Codex_calc!Z62</f>
-        <v>0</v>
-      </c>
-      <c r="AA62">
-        <f>Codex_calc!AA62</f>
-        <v>205.96735483871</v>
-      </c>
-      <c r="AB62">
-        <f>Codex_calc!AB62</f>
-        <v>0</v>
-      </c>
-      <c r="AC62">
-        <f>Codex_calc!AC62</f>
-        <v>0</v>
-      </c>
-      <c r="AD62">
-        <f>Codex_calc!AD62</f>
-        <v>1338.07757419355</v>
-      </c>
-      <c r="AE62">
-        <f>Codex_calc!AE62</f>
-        <v>568.185806451613</v>
-      </c>
-      <c r="AF62">
-        <f>Codex_calc!AF62</f>
-        <v>0</v>
-      </c>
-      <c r="AG62">
-        <f>Codex_calc!AG62</f>
-        <v>0</v>
-      </c>
-      <c r="AH62">
-        <f>Codex_calc!AH62</f>
-        <v>0</v>
-      </c>
-      <c r="AI62">
-        <f>Codex_calc!AI62</f>
-        <v>0</v>
-      </c>
-      <c r="AJ62">
-        <f>Codex_calc!AJ62</f>
-        <v>0</v>
-      </c>
-      <c r="AK62">
-        <f>Codex_calc!AK62</f>
-        <v>64.631135483871</v>
-      </c>
-      <c r="AL62">
-        <f>Codex_calc!AL62</f>
-        <v>0</v>
-      </c>
-      <c r="AM62">
-        <f>Codex_calc!AM62</f>
-        <v>0</v>
-      </c>
-      <c r="AN62">
-        <f>Codex_calc!AN62</f>
-        <v>0</v>
-      </c>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62" s="29"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
+      <c r="L62"/>
+      <c r="M62" s="29"/>
+      <c r="N62"/>
+      <c r="O62"/>
+      <c r="P62"/>
+      <c r="Q62"/>
+      <c r="R62"/>
+      <c r="S62"/>
+      <c r="T62"/>
+      <c r="U62"/>
+      <c r="V62"/>
+      <c r="W62"/>
+      <c r="X62"/>
+      <c r="Y62"/>
+      <c r="Z62"/>
+      <c r="AA62"/>
+      <c r="AB62"/>
+      <c r="AC62"/>
+      <c r="AD62"/>
+      <c r="AE62"/>
+      <c r="AF62"/>
+      <c r="AG62"/>
+      <c r="AH62"/>
+      <c r="AI62"/>
+      <c r="AJ62"/>
+      <c r="AK62"/>
+      <c r="AL62"/>
+      <c r="AM62"/>
+      <c r="AN62"/>
       <c r="AO62" t="str">
         <f>Codex_calc!AO62</f>
         <v>2019, 2130</v>
@@ -7617,146 +7080,41 @@
         <v>CUM</v>
       </c>
       <c r="E65"/>
-      <c r="F65">
-        <f>Codex_calc!F65</f>
-        <v>0</v>
-      </c>
-      <c r="G65">
-        <f>Codex_calc!G65</f>
-        <v>2346.72575268817</v>
-      </c>
-      <c r="H65" s="29">
-        <f>Codex_calc!H65</f>
-        <v>654.005537634409</v>
-      </c>
-      <c r="I65">
-        <f>Codex_calc!I65</f>
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <f>Codex_calc!J65</f>
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <f>Codex_calc!K65</f>
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <f>Codex_calc!L65</f>
-        <v>0</v>
-      </c>
-      <c r="M65" s="29">
-        <f>Codex_calc!M65</f>
-        <v>61.5534623655914</v>
-      </c>
-      <c r="N65">
-        <f>Codex_calc!N65</f>
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <f>Codex_calc!O65</f>
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <f>Codex_calc!P65</f>
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <f>Codex_calc!Q65</f>
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <f>Codex_calc!R65</f>
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <f>Codex_calc!S65</f>
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <f>Codex_calc!T65</f>
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <f>Codex_calc!U65</f>
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <f>Codex_calc!V65</f>
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <f>Codex_calc!W65</f>
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <f>Codex_calc!X65</f>
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <f>Codex_calc!Y65</f>
-        <v>192.354569892473</v>
-      </c>
-      <c r="Z65">
-        <f>Codex_calc!Z65</f>
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <f>Codex_calc!AA65</f>
-        <v>111.565650537634</v>
-      </c>
-      <c r="AB65">
-        <f>Codex_calc!AB65</f>
-        <v>0</v>
-      </c>
-      <c r="AC65">
-        <f>Codex_calc!AC65</f>
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <f>Codex_calc!AD65</f>
-        <v>724.792019354839</v>
-      </c>
-      <c r="AE65">
-        <f>Codex_calc!AE65</f>
-        <v>307.767311827957</v>
-      </c>
-      <c r="AF65">
-        <f>Codex_calc!AF65</f>
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <f>Codex_calc!AG65</f>
-        <v>0</v>
-      </c>
-      <c r="AH65">
-        <f>Codex_calc!AH65</f>
-        <v>0</v>
-      </c>
-      <c r="AI65">
-        <f>Codex_calc!AI65</f>
-        <v>0</v>
-      </c>
-      <c r="AJ65">
-        <f>Codex_calc!AJ65</f>
-        <v>0</v>
-      </c>
-      <c r="AK65">
-        <f>Codex_calc!AK65</f>
-        <v>35.0085317204301</v>
-      </c>
-      <c r="AL65">
-        <f>Codex_calc!AL65</f>
-        <v>0</v>
-      </c>
-      <c r="AM65">
-        <f>Codex_calc!AM65</f>
-        <v>0</v>
-      </c>
-      <c r="AN65">
-        <f>Codex_calc!AN65</f>
-        <v>0</v>
-      </c>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65" s="29"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="M65" s="29"/>
+      <c r="N65"/>
+      <c r="O65"/>
+      <c r="P65"/>
+      <c r="Q65"/>
+      <c r="R65"/>
+      <c r="S65"/>
+      <c r="T65"/>
+      <c r="U65"/>
+      <c r="V65"/>
+      <c r="W65"/>
+      <c r="X65"/>
+      <c r="Y65"/>
+      <c r="Z65"/>
+      <c r="AA65"/>
+      <c r="AB65"/>
+      <c r="AC65"/>
+      <c r="AD65"/>
+      <c r="AE65"/>
+      <c r="AF65"/>
+      <c r="AG65"/>
+      <c r="AH65"/>
+      <c r="AI65"/>
+      <c r="AJ65"/>
+      <c r="AK65"/>
+      <c r="AL65"/>
+      <c r="AM65"/>
+      <c r="AN65"/>
       <c r="AO65" t="str">
         <f>Codex_calc!AO65</f>
         <v>2019, 2130</v>
@@ -7971,22 +7329,13 @@
       <c r="F68"/>
       <c r="G68"/>
       <c r="H68" s="29"/>
-      <c r="I68"/>
-      <c r="J68"/>
       <c r="K68"/>
       <c r="L68"/>
       <c r="M68" s="29"/>
-      <c r="N68"/>
-      <c r="O68"/>
       <c r="P68"/>
-      <c r="Q68"/>
       <c r="R68"/>
-      <c r="S68"/>
       <c r="T68"/>
       <c r="U68"/>
-      <c r="V68"/>
-      <c r="W68"/>
-      <c r="X68"/>
       <c r="Y68"/>
       <c r="Z68"/>
       <c r="AA68"/>
@@ -7998,11 +7347,8 @@
       <c r="AG68"/>
       <c r="AH68"/>
       <c r="AI68"/>
-      <c r="AJ68"/>
       <c r="AK68"/>
-      <c r="AL68"/>
       <c r="AM68"/>
-      <c r="AN68"/>
       <c r="AO68" t="str">
         <f>Codex_calc!AO68</f>
         <v>2019, 2130</v>
@@ -8488,146 +7834,41 @@
         <v>CUM</v>
       </c>
       <c r="E72"/>
-      <c r="F72">
-        <f>Codex_calc!F72</f>
-        <v>0</v>
-      </c>
-      <c r="G72">
-        <f>Codex_calc!G72</f>
-        <v>747.4</v>
-      </c>
-      <c r="H72" s="29">
-        <f>Codex_calc!H72</f>
-        <v>5858</v>
-      </c>
-      <c r="I72">
-        <f>Codex_calc!I72</f>
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <f>Codex_calc!J72</f>
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <f>Codex_calc!K72</f>
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <f>Codex_calc!L72</f>
-        <v>3030</v>
-      </c>
-      <c r="M72" s="29">
-        <f>Codex_calc!M72</f>
-        <v>2626</v>
-      </c>
-      <c r="N72">
-        <f>Codex_calc!N72</f>
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <f>Codex_calc!O72</f>
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <f>Codex_calc!P72</f>
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <f>Codex_calc!Q72</f>
-        <v>0</v>
-      </c>
-      <c r="R72">
-        <f>Codex_calc!R72</f>
-        <v>0</v>
-      </c>
-      <c r="S72">
-        <f>Codex_calc!S72</f>
-        <v>0</v>
-      </c>
-      <c r="T72">
-        <f>Codex_calc!T72</f>
-        <v>0</v>
-      </c>
-      <c r="U72">
-        <f>Codex_calc!U72</f>
-        <v>343.4</v>
-      </c>
-      <c r="V72">
-        <f>Codex_calc!V72</f>
-        <v>0</v>
-      </c>
-      <c r="W72">
-        <f>Codex_calc!W72</f>
-        <v>0</v>
-      </c>
-      <c r="X72">
-        <f>Codex_calc!X72</f>
-        <v>0</v>
-      </c>
-      <c r="Y72">
-        <f>Codex_calc!Y72</f>
-        <v>0</v>
-      </c>
-      <c r="Z72">
-        <f>Codex_calc!Z72</f>
-        <v>0</v>
-      </c>
-      <c r="AA72">
-        <f>Codex_calc!AA72</f>
-        <v>0</v>
-      </c>
-      <c r="AB72">
-        <f>Codex_calc!AB72</f>
-        <v>0</v>
-      </c>
-      <c r="AC72">
-        <f>Codex_calc!AC72</f>
-        <v>0</v>
-      </c>
-      <c r="AD72">
-        <f>Codex_calc!AD72</f>
-        <v>20.2</v>
-      </c>
-      <c r="AE72">
-        <f>Codex_calc!AE72</f>
-        <v>0</v>
-      </c>
-      <c r="AF72">
-        <f>Codex_calc!AF72</f>
-        <v>0</v>
-      </c>
-      <c r="AG72">
-        <f>Codex_calc!AG72</f>
-        <v>5555</v>
-      </c>
-      <c r="AH72">
-        <f>Codex_calc!AH72</f>
-        <v>0</v>
-      </c>
-      <c r="AI72">
-        <f>Codex_calc!AI72</f>
-        <v>0</v>
-      </c>
-      <c r="AJ72">
-        <f>Codex_calc!AJ72</f>
-        <v>0</v>
-      </c>
-      <c r="AK72">
-        <f>Codex_calc!AK72</f>
-        <v>0</v>
-      </c>
-      <c r="AL72">
-        <f>Codex_calc!AL72</f>
-        <v>0</v>
-      </c>
-      <c r="AM72">
-        <f>Codex_calc!AM72</f>
-        <v>0</v>
-      </c>
-      <c r="AN72">
-        <f>Codex_calc!AN72</f>
-        <v>0</v>
-      </c>
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="H72" s="29"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="M72" s="29"/>
+      <c r="N72"/>
+      <c r="O72"/>
+      <c r="P72"/>
+      <c r="Q72"/>
+      <c r="R72"/>
+      <c r="S72"/>
+      <c r="T72"/>
+      <c r="U72"/>
+      <c r="V72"/>
+      <c r="W72"/>
+      <c r="X72"/>
+      <c r="Y72"/>
+      <c r="Z72"/>
+      <c r="AA72"/>
+      <c r="AB72"/>
+      <c r="AC72"/>
+      <c r="AD72"/>
+      <c r="AE72"/>
+      <c r="AF72"/>
+      <c r="AG72"/>
+      <c r="AH72"/>
+      <c r="AI72"/>
+      <c r="AJ72"/>
+      <c r="AK72"/>
+      <c r="AL72"/>
+      <c r="AM72"/>
+      <c r="AN72"/>
       <c r="AO72" t="str">
         <f>Codex_calc!AO72</f>
         <v>2019, 2130</v>
@@ -8956,146 +8197,41 @@
         <v>CUM</v>
       </c>
       <c r="E75"/>
-      <c r="F75">
-        <f>Codex_calc!F75</f>
-        <v>0</v>
-      </c>
-      <c r="G75">
-        <f>Codex_calc!G75</f>
-        <v>3155.68888888889</v>
-      </c>
-      <c r="H75" s="29">
-        <f>Codex_calc!H75</f>
-        <v>24733.7777777778</v>
-      </c>
-      <c r="I75">
-        <f>Codex_calc!I75</f>
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <f>Codex_calc!J75</f>
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <f>Codex_calc!K75</f>
-        <v>0</v>
-      </c>
-      <c r="L75">
-        <f>Codex_calc!L75</f>
-        <v>12793.3333333333</v>
-      </c>
-      <c r="M75" s="29">
-        <f>Codex_calc!M75</f>
-        <v>11087.5555555555</v>
-      </c>
-      <c r="N75">
-        <f>Codex_calc!N75</f>
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <f>Codex_calc!O75</f>
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <f>Codex_calc!P75</f>
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <f>Codex_calc!Q75</f>
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <f>Codex_calc!R75</f>
-        <v>0</v>
-      </c>
-      <c r="S75">
-        <f>Codex_calc!S75</f>
-        <v>0</v>
-      </c>
-      <c r="T75">
-        <f>Codex_calc!T75</f>
-        <v>0</v>
-      </c>
-      <c r="U75">
-        <f>Codex_calc!U75</f>
-        <v>1449.91111111111</v>
-      </c>
-      <c r="V75">
-        <f>Codex_calc!V75</f>
-        <v>0</v>
-      </c>
-      <c r="W75">
-        <f>Codex_calc!W75</f>
-        <v>0</v>
-      </c>
-      <c r="X75">
-        <f>Codex_calc!X75</f>
-        <v>0</v>
-      </c>
-      <c r="Y75">
-        <f>Codex_calc!Y75</f>
-        <v>0</v>
-      </c>
-      <c r="Z75">
-        <f>Codex_calc!Z75</f>
-        <v>0</v>
-      </c>
-      <c r="AA75">
-        <f>Codex_calc!AA75</f>
-        <v>0</v>
-      </c>
-      <c r="AB75">
-        <f>Codex_calc!AB75</f>
-        <v>0</v>
-      </c>
-      <c r="AC75">
-        <f>Codex_calc!AC75</f>
-        <v>0</v>
-      </c>
-      <c r="AD75">
-        <f>Codex_calc!AD75</f>
-        <v>85.2888888888888</v>
-      </c>
-      <c r="AE75">
-        <f>Codex_calc!AE75</f>
-        <v>0</v>
-      </c>
-      <c r="AF75">
-        <f>Codex_calc!AF75</f>
-        <v>0</v>
-      </c>
-      <c r="AG75">
-        <f>Codex_calc!AG75</f>
-        <v>23454.4444444444</v>
-      </c>
-      <c r="AH75">
-        <f>Codex_calc!AH75</f>
-        <v>0</v>
-      </c>
-      <c r="AI75">
-        <f>Codex_calc!AI75</f>
-        <v>0</v>
-      </c>
-      <c r="AJ75">
-        <f>Codex_calc!AJ75</f>
-        <v>0</v>
-      </c>
-      <c r="AK75">
-        <f>Codex_calc!AK75</f>
-        <v>0</v>
-      </c>
-      <c r="AL75">
-        <f>Codex_calc!AL75</f>
-        <v>0</v>
-      </c>
-      <c r="AM75">
-        <f>Codex_calc!AM75</f>
-        <v>0</v>
-      </c>
-      <c r="AN75">
-        <f>Codex_calc!AN75</f>
-        <v>0</v>
-      </c>
+      <c r="F75"/>
+      <c r="G75"/>
+      <c r="H75" s="29"/>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75"/>
+      <c r="L75"/>
+      <c r="M75" s="29"/>
+      <c r="N75"/>
+      <c r="O75"/>
+      <c r="P75"/>
+      <c r="Q75"/>
+      <c r="R75"/>
+      <c r="S75"/>
+      <c r="T75"/>
+      <c r="U75"/>
+      <c r="V75"/>
+      <c r="W75"/>
+      <c r="X75"/>
+      <c r="Y75"/>
+      <c r="Z75"/>
+      <c r="AA75"/>
+      <c r="AB75"/>
+      <c r="AC75"/>
+      <c r="AD75"/>
+      <c r="AE75"/>
+      <c r="AF75"/>
+      <c r="AG75"/>
+      <c r="AH75"/>
+      <c r="AI75"/>
+      <c r="AJ75"/>
+      <c r="AK75"/>
+      <c r="AL75"/>
+      <c r="AM75"/>
+      <c r="AN75"/>
       <c r="AO75" t="str">
         <f>Codex_calc!AO75</f>
         <v>2019, 2130</v>
@@ -9310,22 +8446,13 @@
       <c r="F78"/>
       <c r="G78"/>
       <c r="H78" s="29"/>
-      <c r="I78"/>
-      <c r="J78"/>
       <c r="K78"/>
       <c r="L78"/>
       <c r="M78" s="29"/>
-      <c r="N78"/>
-      <c r="O78"/>
       <c r="P78"/>
-      <c r="Q78"/>
       <c r="R78"/>
-      <c r="S78"/>
       <c r="T78"/>
       <c r="U78"/>
-      <c r="V78"/>
-      <c r="W78"/>
-      <c r="X78"/>
       <c r="Y78"/>
       <c r="Z78"/>
       <c r="AA78"/>
@@ -9337,11 +8464,8 @@
       <c r="AG78"/>
       <c r="AH78"/>
       <c r="AI78"/>
-      <c r="AJ78"/>
       <c r="AK78"/>
-      <c r="AL78"/>
       <c r="AM78"/>
-      <c r="AN78"/>
       <c r="AO78" t="str">
         <f>Codex_calc!AO78</f>
         <v>2019, 2130</v>
@@ -9825,146 +8949,6 @@
         <f>Codex_calc!D82</f>
         <v>CUM</v>
       </c>
-      <c r="F82" s="29">
-        <f>Codex_calc!F82</f>
-        <v>0</v>
-      </c>
-      <c r="G82" s="29">
-        <f>Codex_calc!G82</f>
-        <v>37157</v>
-      </c>
-      <c r="H82" s="29">
-        <f>Codex_calc!H82</f>
-        <v>18578.5</v>
-      </c>
-      <c r="I82" s="29">
-        <f>Codex_calc!I82</f>
-        <v>0</v>
-      </c>
-      <c r="J82" s="29">
-        <f>Codex_calc!J82</f>
-        <v>0</v>
-      </c>
-      <c r="K82" s="29">
-        <f>Codex_calc!K82</f>
-        <v>0</v>
-      </c>
-      <c r="L82" s="29">
-        <f>Codex_calc!L82</f>
-        <v>8536.06756756757</v>
-      </c>
-      <c r="M82" s="29">
-        <f>Codex_calc!M82</f>
-        <v>3565.06351351351</v>
-      </c>
-      <c r="N82" s="29">
-        <f>Codex_calc!N82</f>
-        <v>0</v>
-      </c>
-      <c r="O82" s="29">
-        <f>Codex_calc!O82</f>
-        <v>0</v>
-      </c>
-      <c r="P82" s="29">
-        <f>Codex_calc!P82</f>
-        <v>0</v>
-      </c>
-      <c r="Q82" s="29">
-        <f>Codex_calc!Q82</f>
-        <v>0</v>
-      </c>
-      <c r="R82" s="29">
-        <f>Codex_calc!R82</f>
-        <v>0</v>
-      </c>
-      <c r="S82" s="29">
-        <f>Codex_calc!S82</f>
-        <v>0</v>
-      </c>
-      <c r="T82" s="29">
-        <f>Codex_calc!T82</f>
-        <v>0</v>
-      </c>
-      <c r="U82" s="29">
-        <f>Codex_calc!U82</f>
-        <v>3263.79054054054</v>
-      </c>
-      <c r="V82" s="29">
-        <f>Codex_calc!V82</f>
-        <v>0</v>
-      </c>
-      <c r="W82" s="29">
-        <f>Codex_calc!W82</f>
-        <v>0</v>
-      </c>
-      <c r="X82" s="29">
-        <f>Codex_calc!X82</f>
-        <v>0</v>
-      </c>
-      <c r="Y82" s="29">
-        <f>Codex_calc!Y82</f>
-        <v>10042.4324324324</v>
-      </c>
-      <c r="Z82" s="29">
-        <f>Codex_calc!Z82</f>
-        <v>0</v>
-      </c>
-      <c r="AA82" s="29">
-        <f>Codex_calc!AA82</f>
-        <v>100.424324324324</v>
-      </c>
-      <c r="AB82" s="29">
-        <f>Codex_calc!AB82</f>
-        <v>0</v>
-      </c>
-      <c r="AC82" s="29">
-        <f>Codex_calc!AC82</f>
-        <v>0</v>
-      </c>
-      <c r="AD82" s="29">
-        <f>Codex_calc!AD82</f>
-        <v>57543.1378378378</v>
-      </c>
-      <c r="AE82" s="29">
-        <f>Codex_calc!AE82</f>
-        <v>3263.79054054054</v>
-      </c>
-      <c r="AF82" s="29">
-        <f>Codex_calc!AF82</f>
-        <v>903.818918918919</v>
-      </c>
-      <c r="AG82" s="29">
-        <f>Codex_calc!AG82</f>
-        <v>0</v>
-      </c>
-      <c r="AH82" s="29">
-        <f>Codex_calc!AH82</f>
-        <v>0</v>
-      </c>
-      <c r="AI82" s="29">
-        <f>Codex_calc!AI82</f>
-        <v>0</v>
-      </c>
-      <c r="AJ82" s="29">
-        <f>Codex_calc!AJ82</f>
-        <v>0</v>
-      </c>
-      <c r="AK82" s="29">
-        <f>Codex_calc!AK82</f>
-        <v>346.463918918919</v>
-      </c>
-      <c r="AL82" s="29">
-        <f>Codex_calc!AL82</f>
-        <v>0</v>
-      </c>
-      <c r="AM82" s="29">
-        <f>Codex_calc!AM82</f>
-        <v>0</v>
-      </c>
-      <c r="AN82" s="29">
-        <f>Codex_calc!AN82</f>
-        <v>0</v>
-      </c>
       <c r="AO82" s="29" t="str">
         <f>Codex_calc!AO82</f>
         <v>2019, 2130</v>
@@ -10292,146 +9276,41 @@
         <v>CUM</v>
       </c>
       <c r="E85"/>
-      <c r="F85">
-        <f>Codex_calc!F85</f>
-        <v>0</v>
-      </c>
-      <c r="G85">
-        <f>Codex_calc!G85</f>
-        <v>46125.9310344828</v>
-      </c>
-      <c r="H85" s="29">
-        <f>Codex_calc!H85</f>
-        <v>23062.9655172414</v>
-      </c>
-      <c r="I85">
-        <f>Codex_calc!I85</f>
-        <v>0</v>
-      </c>
-      <c r="J85">
-        <f>Codex_calc!J85</f>
-        <v>0</v>
-      </c>
-      <c r="K85">
-        <f>Codex_calc!K85</f>
-        <v>0</v>
-      </c>
-      <c r="L85">
-        <f>Codex_calc!L85</f>
-        <v>10596.4976700839</v>
-      </c>
-      <c r="M85" s="29">
-        <f>Codex_calc!M85</f>
-        <v>4425.59608574091</v>
-      </c>
-      <c r="N85">
-        <f>Codex_calc!N85</f>
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <f>Codex_calc!O85</f>
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <f>Codex_calc!P85</f>
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <f>Codex_calc!Q85</f>
-        <v>0</v>
-      </c>
-      <c r="R85">
-        <f>Codex_calc!R85</f>
-        <v>0</v>
-      </c>
-      <c r="S85">
-        <f>Codex_calc!S85</f>
-        <v>0</v>
-      </c>
-      <c r="T85">
-        <f>Codex_calc!T85</f>
-        <v>0</v>
-      </c>
-      <c r="U85">
-        <f>Codex_calc!U85</f>
-        <v>4051.60205032619</v>
-      </c>
-      <c r="V85">
-        <f>Codex_calc!V85</f>
-        <v>0</v>
-      </c>
-      <c r="W85">
-        <f>Codex_calc!W85</f>
-        <v>0</v>
-      </c>
-      <c r="X85">
-        <f>Codex_calc!X85</f>
-        <v>0</v>
-      </c>
-      <c r="Y85">
-        <f>Codex_calc!Y85</f>
-        <v>12466.4678471575</v>
-      </c>
-      <c r="Z85">
-        <f>Codex_calc!Z85</f>
-        <v>0</v>
-      </c>
-      <c r="AA85">
-        <f>Codex_calc!AA85</f>
-        <v>124.664678471575</v>
-      </c>
-      <c r="AB85">
-        <f>Codex_calc!AB85</f>
-        <v>0</v>
-      </c>
-      <c r="AC85">
-        <f>Codex_calc!AC85</f>
-        <v>0</v>
-      </c>
-      <c r="AD85">
-        <f>Codex_calc!AD85</f>
-        <v>71432.8607642125</v>
-      </c>
-      <c r="AE85">
-        <f>Codex_calc!AE85</f>
-        <v>4051.60205032619</v>
-      </c>
-      <c r="AF85">
-        <f>Codex_calc!AF85</f>
-        <v>1121.98210624418</v>
-      </c>
-      <c r="AG85">
-        <f>Codex_calc!AG85</f>
-        <v>0</v>
-      </c>
-      <c r="AH85">
-        <f>Codex_calc!AH85</f>
-        <v>0</v>
-      </c>
-      <c r="AI85">
-        <f>Codex_calc!AI85</f>
-        <v>0</v>
-      </c>
-      <c r="AJ85">
-        <f>Codex_calc!AJ85</f>
-        <v>0</v>
-      </c>
-      <c r="AK85">
-        <f>Codex_calc!AK85</f>
-        <v>430.093140726934</v>
-      </c>
-      <c r="AL85">
-        <f>Codex_calc!AL85</f>
-        <v>0</v>
-      </c>
-      <c r="AM85">
-        <f>Codex_calc!AM85</f>
-        <v>0</v>
-      </c>
-      <c r="AN85">
-        <f>Codex_calc!AN85</f>
-        <v>0</v>
-      </c>
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="H85" s="29"/>
+      <c r="I85"/>
+      <c r="J85"/>
+      <c r="K85"/>
+      <c r="L85"/>
+      <c r="M85" s="29"/>
+      <c r="N85"/>
+      <c r="O85"/>
+      <c r="P85"/>
+      <c r="Q85"/>
+      <c r="R85"/>
+      <c r="S85"/>
+      <c r="T85"/>
+      <c r="U85"/>
+      <c r="V85"/>
+      <c r="W85"/>
+      <c r="X85"/>
+      <c r="Y85"/>
+      <c r="Z85"/>
+      <c r="AA85"/>
+      <c r="AB85"/>
+      <c r="AC85"/>
+      <c r="AD85"/>
+      <c r="AE85"/>
+      <c r="AF85"/>
+      <c r="AG85"/>
+      <c r="AH85"/>
+      <c r="AI85"/>
+      <c r="AJ85"/>
+      <c r="AK85"/>
+      <c r="AL85"/>
+      <c r="AM85"/>
+      <c r="AN85"/>
       <c r="AO85" t="str">
         <f>Codex_calc!AO85</f>
         <v>2019, 2130</v>
@@ -11150,146 +10029,6 @@
         <f>Codex_calc!D92</f>
         <v>CUM</v>
       </c>
-      <c r="F92" s="29">
-        <f>Codex_calc!F92</f>
-        <v>0</v>
-      </c>
-      <c r="G92" s="29">
-        <f>Codex_calc!G92</f>
-        <v>2503.04347826087</v>
-      </c>
-      <c r="H92" s="29">
-        <f>Codex_calc!H92</f>
-        <v>2478.26086956522</v>
-      </c>
-      <c r="I92" s="29">
-        <f>Codex_calc!I92</f>
-        <v>0</v>
-      </c>
-      <c r="J92" s="29">
-        <f>Codex_calc!J92</f>
-        <v>0</v>
-      </c>
-      <c r="K92" s="29">
-        <f>Codex_calc!K92</f>
-        <v>0</v>
-      </c>
-      <c r="L92" s="29">
-        <f>Codex_calc!L92</f>
-        <v>0</v>
-      </c>
-      <c r="M92" s="29">
-        <f>Codex_calc!M92</f>
-        <v>1016.08695652174</v>
-      </c>
-      <c r="N92" s="29">
-        <f>Codex_calc!N92</f>
-        <v>0</v>
-      </c>
-      <c r="O92" s="29">
-        <f>Codex_calc!O92</f>
-        <v>0</v>
-      </c>
-      <c r="P92" s="29">
-        <f>Codex_calc!P92</f>
-        <v>0</v>
-      </c>
-      <c r="Q92" s="29">
-        <f>Codex_calc!Q92</f>
-        <v>0</v>
-      </c>
-      <c r="R92" s="29">
-        <f>Codex_calc!R92</f>
-        <v>0</v>
-      </c>
-      <c r="S92" s="29">
-        <f>Codex_calc!S92</f>
-        <v>0</v>
-      </c>
-      <c r="T92" s="29">
-        <f>Codex_calc!T92</f>
-        <v>0</v>
-      </c>
-      <c r="U92" s="29">
-        <f>Codex_calc!U92</f>
-        <v>54.5217391304348</v>
-      </c>
-      <c r="V92" s="29">
-        <f>Codex_calc!V92</f>
-        <v>0</v>
-      </c>
-      <c r="W92" s="29">
-        <f>Codex_calc!W92</f>
-        <v>0</v>
-      </c>
-      <c r="X92" s="29">
-        <f>Codex_calc!X92</f>
-        <v>0</v>
-      </c>
-      <c r="Y92" s="29">
-        <f>Codex_calc!Y92</f>
-        <v>6567.39130434783</v>
-      </c>
-      <c r="Z92" s="29">
-        <f>Codex_calc!Z92</f>
-        <v>0</v>
-      </c>
-      <c r="AA92" s="29">
-        <f>Codex_calc!AA92</f>
-        <v>2651.73913043478</v>
-      </c>
-      <c r="AB92" s="29">
-        <f>Codex_calc!AB92</f>
-        <v>0</v>
-      </c>
-      <c r="AC92" s="29">
-        <f>Codex_calc!AC92</f>
-        <v>817.826086956522</v>
-      </c>
-      <c r="AD92" s="29">
-        <f>Codex_calc!AD92</f>
-        <v>6220.4347826087</v>
-      </c>
-      <c r="AE92" s="29">
-        <f>Codex_calc!AE92</f>
-        <v>1982.60869565217</v>
-      </c>
-      <c r="AF92" s="29">
-        <f>Codex_calc!AF92</f>
-        <v>0</v>
-      </c>
-      <c r="AG92" s="29">
-        <f>Codex_calc!AG92</f>
-        <v>0</v>
-      </c>
-      <c r="AH92" s="29">
-        <f>Codex_calc!AH92</f>
-        <v>0</v>
-      </c>
-      <c r="AI92" s="29">
-        <f>Codex_calc!AI92</f>
-        <v>0</v>
-      </c>
-      <c r="AJ92" s="29">
-        <f>Codex_calc!AJ92</f>
-        <v>0</v>
-      </c>
-      <c r="AK92" s="29">
-        <f>Codex_calc!AK92</f>
-        <v>0</v>
-      </c>
-      <c r="AL92" s="29">
-        <f>Codex_calc!AL92</f>
-        <v>0</v>
-      </c>
-      <c r="AM92" s="29">
-        <f>Codex_calc!AM92</f>
-        <v>0</v>
-      </c>
-      <c r="AN92" s="29">
-        <f>Codex_calc!AN92</f>
-        <v>0</v>
-      </c>
       <c r="AO92" s="29" t="str">
         <f>Codex_calc!AO92</f>
         <v>2019, 2130</v>
@@ -11618,146 +10357,41 @@
         <v>CUM</v>
       </c>
       <c r="E95"/>
-      <c r="F95">
-        <f>Codex_calc!F95</f>
-        <v>0</v>
-      </c>
-      <c r="G95">
-        <f>Codex_calc!G95</f>
-        <v>1328.1455190772</v>
-      </c>
-      <c r="H95" s="29">
-        <f>Codex_calc!H95</f>
-        <v>1314.99556344277</v>
-      </c>
-      <c r="I95">
-        <f>Codex_calc!I95</f>
-        <v>0</v>
-      </c>
-      <c r="J95">
-        <f>Codex_calc!J95</f>
-        <v>0</v>
-      </c>
-      <c r="K95">
-        <f>Codex_calc!K95</f>
-        <v>0</v>
-      </c>
-      <c r="L95">
-        <f>Codex_calc!L95</f>
-        <v>0</v>
-      </c>
-      <c r="M95" s="29">
-        <f>Codex_calc!M95</f>
-        <v>539.148181011535</v>
-      </c>
-      <c r="N95">
-        <f>Codex_calc!N95</f>
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <f>Codex_calc!O95</f>
-        <v>0</v>
-      </c>
-      <c r="P95">
-        <f>Codex_calc!P95</f>
-        <v>0</v>
-      </c>
-      <c r="Q95">
-        <f>Codex_calc!Q95</f>
-        <v>0</v>
-      </c>
-      <c r="R95">
-        <f>Codex_calc!R95</f>
-        <v>0</v>
-      </c>
-      <c r="S95">
-        <f>Codex_calc!S95</f>
-        <v>0</v>
-      </c>
-      <c r="T95">
-        <f>Codex_calc!T95</f>
-        <v>0</v>
-      </c>
-      <c r="U95">
-        <f>Codex_calc!U95</f>
-        <v>28.9299023957409</v>
-      </c>
-      <c r="V95">
-        <f>Codex_calc!V95</f>
-        <v>0</v>
-      </c>
-      <c r="W95">
-        <f>Codex_calc!W95</f>
-        <v>0</v>
-      </c>
-      <c r="X95">
-        <f>Codex_calc!X95</f>
-        <v>0</v>
-      </c>
-      <c r="Y95">
-        <f>Codex_calc!Y95</f>
-        <v>3484.73824312334</v>
-      </c>
-      <c r="Z95">
-        <f>Codex_calc!Z95</f>
-        <v>0</v>
-      </c>
-      <c r="AA95">
-        <f>Codex_calc!AA95</f>
-        <v>1407.04525288376</v>
-      </c>
-      <c r="AB95">
-        <f>Codex_calc!AB95</f>
-        <v>0</v>
-      </c>
-      <c r="AC95">
-        <f>Codex_calc!AC95</f>
-        <v>433.948535936114</v>
-      </c>
-      <c r="AD95">
-        <f>Codex_calc!AD95</f>
-        <v>3300.63886424135</v>
-      </c>
-      <c r="AE95">
-        <f>Codex_calc!AE95</f>
-        <v>1051.99645075421</v>
-      </c>
-      <c r="AF95">
-        <f>Codex_calc!AF95</f>
-        <v>0</v>
-      </c>
-      <c r="AG95">
-        <f>Codex_calc!AG95</f>
-        <v>0</v>
-      </c>
-      <c r="AH95">
-        <f>Codex_calc!AH95</f>
-        <v>0</v>
-      </c>
-      <c r="AI95">
-        <f>Codex_calc!AI95</f>
-        <v>0</v>
-      </c>
-      <c r="AJ95">
-        <f>Codex_calc!AJ95</f>
-        <v>0</v>
-      </c>
-      <c r="AK95">
-        <f>Codex_calc!AK95</f>
-        <v>0</v>
-      </c>
-      <c r="AL95">
-        <f>Codex_calc!AL95</f>
-        <v>0</v>
-      </c>
-      <c r="AM95">
-        <f>Codex_calc!AM95</f>
-        <v>0</v>
-      </c>
-      <c r="AN95">
-        <f>Codex_calc!AN95</f>
-        <v>0</v>
-      </c>
+      <c r="F95"/>
+      <c r="G95"/>
+      <c r="H95" s="29"/>
+      <c r="I95"/>
+      <c r="J95"/>
+      <c r="K95"/>
+      <c r="L95"/>
+      <c r="M95" s="29"/>
+      <c r="N95"/>
+      <c r="O95"/>
+      <c r="P95"/>
+      <c r="Q95"/>
+      <c r="R95"/>
+      <c r="S95"/>
+      <c r="T95"/>
+      <c r="U95"/>
+      <c r="V95"/>
+      <c r="W95"/>
+      <c r="X95"/>
+      <c r="Y95"/>
+      <c r="Z95"/>
+      <c r="AA95"/>
+      <c r="AB95"/>
+      <c r="AC95"/>
+      <c r="AD95"/>
+      <c r="AE95"/>
+      <c r="AF95"/>
+      <c r="AG95"/>
+      <c r="AH95"/>
+      <c r="AI95"/>
+      <c r="AJ95"/>
+      <c r="AK95"/>
+      <c r="AL95"/>
+      <c r="AM95"/>
+      <c r="AN95"/>
       <c r="AO95" t="str">
         <f>Codex_calc!AO95</f>
         <v>2019, 2130</v>
@@ -11972,22 +10606,13 @@
       <c r="F98"/>
       <c r="G98"/>
       <c r="H98" s="29"/>
-      <c r="I98"/>
-      <c r="J98"/>
       <c r="K98"/>
       <c r="L98"/>
       <c r="M98" s="29"/>
-      <c r="N98"/>
-      <c r="O98"/>
       <c r="P98"/>
-      <c r="Q98"/>
       <c r="R98"/>
-      <c r="S98"/>
       <c r="T98"/>
       <c r="U98"/>
-      <c r="V98"/>
-      <c r="W98"/>
-      <c r="X98"/>
       <c r="Y98"/>
       <c r="Z98"/>
       <c r="AA98"/>
@@ -11999,11 +10624,8 @@
       <c r="AG98"/>
       <c r="AH98"/>
       <c r="AI98"/>
-      <c r="AJ98"/>
       <c r="AK98"/>
-      <c r="AL98"/>
       <c r="AM98"/>
-      <c r="AN98"/>
       <c r="AO98" t="str">
         <f>Codex_calc!AO98</f>
         <v>2019, 2130</v>
@@ -12489,146 +11111,41 @@
         <v>CUM</v>
       </c>
       <c r="E102"/>
-      <c r="F102">
-        <f>Codex_calc!F102</f>
-        <v>0</v>
-      </c>
-      <c r="G102">
-        <f>Codex_calc!G102</f>
-        <v>57074.5</v>
-      </c>
-      <c r="H102" s="29">
-        <f>Codex_calc!H102</f>
-        <v>0</v>
-      </c>
-      <c r="I102">
-        <f>Codex_calc!I102</f>
-        <v>0</v>
-      </c>
-      <c r="J102">
-        <f>Codex_calc!J102</f>
-        <v>0</v>
-      </c>
-      <c r="K102">
-        <f>Codex_calc!K102</f>
-        <v>0</v>
-      </c>
-      <c r="L102">
-        <f>Codex_calc!L102</f>
-        <v>60335.9</v>
-      </c>
-      <c r="M102" s="29">
-        <f>Codex_calc!M102</f>
-        <v>81535</v>
-      </c>
-      <c r="N102">
-        <f>Codex_calc!N102</f>
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <f>Codex_calc!O102</f>
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <f>Codex_calc!P102</f>
-        <v>0</v>
-      </c>
-      <c r="Q102">
-        <f>Codex_calc!Q102</f>
-        <v>0</v>
-      </c>
-      <c r="R102">
-        <f>Codex_calc!R102</f>
-        <v>0</v>
-      </c>
-      <c r="S102">
-        <f>Codex_calc!S102</f>
-        <v>0</v>
-      </c>
-      <c r="T102">
-        <f>Codex_calc!T102</f>
-        <v>0</v>
-      </c>
-      <c r="U102">
-        <f>Codex_calc!U102</f>
-        <v>7012.01</v>
-      </c>
-      <c r="V102">
-        <f>Codex_calc!V102</f>
-        <v>0</v>
-      </c>
-      <c r="W102">
-        <f>Codex_calc!W102</f>
-        <v>0</v>
-      </c>
-      <c r="X102">
-        <f>Codex_calc!X102</f>
-        <v>0</v>
-      </c>
-      <c r="Y102">
-        <f>Codex_calc!Y102</f>
-        <v>0</v>
-      </c>
-      <c r="Z102">
-        <f>Codex_calc!Z102</f>
-        <v>0</v>
-      </c>
-      <c r="AA102">
-        <f>Codex_calc!AA102</f>
-        <v>7338.15</v>
-      </c>
-      <c r="AB102">
-        <f>Codex_calc!AB102</f>
-        <v>489.21</v>
-      </c>
-      <c r="AC102">
-        <f>Codex_calc!AC102</f>
-        <v>0</v>
-      </c>
-      <c r="AD102">
-        <f>Codex_calc!AD102</f>
-        <v>12230.25</v>
-      </c>
-      <c r="AE102">
-        <f>Codex_calc!AE102</f>
-        <v>11414.9</v>
-      </c>
-      <c r="AF102">
-        <f>Codex_calc!AF102</f>
-        <v>0</v>
-      </c>
-      <c r="AG102">
-        <f>Codex_calc!AG102</f>
-        <v>0</v>
-      </c>
-      <c r="AH102">
-        <f>Codex_calc!AH102</f>
-        <v>0</v>
-      </c>
-      <c r="AI102">
-        <f>Codex_calc!AI102</f>
-        <v>0</v>
-      </c>
-      <c r="AJ102">
-        <f>Codex_calc!AJ102</f>
-        <v>0</v>
-      </c>
-      <c r="AK102">
-        <f>Codex_calc!AK102</f>
-        <v>5625.915</v>
-      </c>
-      <c r="AL102">
-        <f>Codex_calc!AL102</f>
-        <v>0</v>
-      </c>
-      <c r="AM102">
-        <f>Codex_calc!AM102</f>
-        <v>0</v>
-      </c>
-      <c r="AN102">
-        <f>Codex_calc!AN102</f>
-        <v>0</v>
-      </c>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102" s="29"/>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102"/>
+      <c r="L102"/>
+      <c r="M102" s="29"/>
+      <c r="N102"/>
+      <c r="O102"/>
+      <c r="P102"/>
+      <c r="Q102"/>
+      <c r="R102"/>
+      <c r="S102"/>
+      <c r="T102"/>
+      <c r="U102"/>
+      <c r="V102"/>
+      <c r="W102"/>
+      <c r="X102"/>
+      <c r="Y102"/>
+      <c r="Z102"/>
+      <c r="AA102"/>
+      <c r="AB102"/>
+      <c r="AC102"/>
+      <c r="AD102"/>
+      <c r="AE102"/>
+      <c r="AF102"/>
+      <c r="AG102"/>
+      <c r="AH102"/>
+      <c r="AI102"/>
+      <c r="AJ102"/>
+      <c r="AK102"/>
+      <c r="AL102"/>
+      <c r="AM102"/>
+      <c r="AN102"/>
       <c r="AO102" t="str">
         <f>Codex_calc!AO102</f>
         <v>2019, 2130</v>
@@ -12957,146 +11474,41 @@
         <v>CUM</v>
       </c>
       <c r="E105"/>
-      <c r="F105">
-        <f>Codex_calc!F105</f>
-        <v>0</v>
-      </c>
-      <c r="G105">
-        <f>Codex_calc!G105</f>
-        <v>45107.2661290323</v>
-      </c>
-      <c r="H105" s="29">
-        <f>Codex_calc!H105</f>
-        <v>0</v>
-      </c>
-      <c r="I105">
-        <f>Codex_calc!I105</f>
-        <v>0</v>
-      </c>
-      <c r="J105">
-        <f>Codex_calc!J105</f>
-        <v>0</v>
-      </c>
-      <c r="K105">
-        <f>Codex_calc!K105</f>
-        <v>0</v>
-      </c>
-      <c r="L105">
-        <f>Codex_calc!L105</f>
-        <v>47684.8241935484</v>
-      </c>
-      <c r="M105" s="29">
-        <f>Codex_calc!M105</f>
-        <v>64438.9516129032</v>
-      </c>
-      <c r="N105">
-        <f>Codex_calc!N105</f>
-        <v>0</v>
-      </c>
-      <c r="O105">
-        <f>Codex_calc!O105</f>
-        <v>0</v>
-      </c>
-      <c r="P105">
-        <f>Codex_calc!P105</f>
-        <v>0</v>
-      </c>
-      <c r="Q105">
-        <f>Codex_calc!Q105</f>
-        <v>0</v>
-      </c>
-      <c r="R105">
-        <f>Codex_calc!R105</f>
-        <v>0</v>
-      </c>
-      <c r="S105">
-        <f>Codex_calc!S105</f>
-        <v>0</v>
-      </c>
-      <c r="T105">
-        <f>Codex_calc!T105</f>
-        <v>0</v>
-      </c>
-      <c r="U105">
-        <f>Codex_calc!U105</f>
-        <v>5541.74983870968</v>
-      </c>
-      <c r="V105">
-        <f>Codex_calc!V105</f>
-        <v>0</v>
-      </c>
-      <c r="W105">
-        <f>Codex_calc!W105</f>
-        <v>0</v>
-      </c>
-      <c r="X105">
-        <f>Codex_calc!X105</f>
-        <v>0</v>
-      </c>
-      <c r="Y105">
-        <f>Codex_calc!Y105</f>
-        <v>0</v>
-      </c>
-      <c r="Z105">
-        <f>Codex_calc!Z105</f>
-        <v>0</v>
-      </c>
-      <c r="AA105">
-        <f>Codex_calc!AA105</f>
-        <v>5799.50564516129</v>
-      </c>
-      <c r="AB105">
-        <f>Codex_calc!AB105</f>
-        <v>386.633709677419</v>
-      </c>
-      <c r="AC105">
-        <f>Codex_calc!AC105</f>
-        <v>0</v>
-      </c>
-      <c r="AD105">
-        <f>Codex_calc!AD105</f>
-        <v>9665.84274193548</v>
-      </c>
-      <c r="AE105">
-        <f>Codex_calc!AE105</f>
-        <v>9021.45322580645</v>
-      </c>
-      <c r="AF105">
-        <f>Codex_calc!AF105</f>
-        <v>0</v>
-      </c>
-      <c r="AG105">
-        <f>Codex_calc!AG105</f>
-        <v>0</v>
-      </c>
-      <c r="AH105">
-        <f>Codex_calc!AH105</f>
-        <v>0</v>
-      </c>
-      <c r="AI105">
-        <f>Codex_calc!AI105</f>
-        <v>0</v>
-      </c>
-      <c r="AJ105">
-        <f>Codex_calc!AJ105</f>
-        <v>0</v>
-      </c>
-      <c r="AK105">
-        <f>Codex_calc!AK105</f>
-        <v>4446.28766129032</v>
-      </c>
-      <c r="AL105">
-        <f>Codex_calc!AL105</f>
-        <v>0</v>
-      </c>
-      <c r="AM105">
-        <f>Codex_calc!AM105</f>
-        <v>0</v>
-      </c>
-      <c r="AN105">
-        <f>Codex_calc!AN105</f>
-        <v>0</v>
-      </c>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105" s="29"/>
+      <c r="I105"/>
+      <c r="J105"/>
+      <c r="K105"/>
+      <c r="L105"/>
+      <c r="M105" s="29"/>
+      <c r="N105"/>
+      <c r="O105"/>
+      <c r="P105"/>
+      <c r="Q105"/>
+      <c r="R105"/>
+      <c r="S105"/>
+      <c r="T105"/>
+      <c r="U105"/>
+      <c r="V105"/>
+      <c r="W105"/>
+      <c r="X105"/>
+      <c r="Y105"/>
+      <c r="Z105"/>
+      <c r="AA105"/>
+      <c r="AB105"/>
+      <c r="AC105"/>
+      <c r="AD105"/>
+      <c r="AE105"/>
+      <c r="AF105"/>
+      <c r="AG105"/>
+      <c r="AH105"/>
+      <c r="AI105"/>
+      <c r="AJ105"/>
+      <c r="AK105"/>
+      <c r="AL105"/>
+      <c r="AM105"/>
+      <c r="AN105"/>
       <c r="AO105" t="str">
         <f>Codex_calc!AO105</f>
         <v>2019, 2130</v>
@@ -13311,22 +11723,13 @@
       <c r="F108"/>
       <c r="G108"/>
       <c r="H108" s="29"/>
-      <c r="I108"/>
-      <c r="J108"/>
       <c r="K108"/>
       <c r="L108"/>
       <c r="M108" s="29"/>
-      <c r="N108"/>
-      <c r="O108"/>
       <c r="P108"/>
-      <c r="Q108"/>
       <c r="R108"/>
-      <c r="S108"/>
       <c r="T108"/>
       <c r="U108"/>
-      <c r="V108"/>
-      <c r="W108"/>
-      <c r="X108"/>
       <c r="Y108"/>
       <c r="Z108"/>
       <c r="AA108"/>
@@ -13338,11 +11741,8 @@
       <c r="AG108"/>
       <c r="AH108"/>
       <c r="AI108"/>
-      <c r="AJ108"/>
       <c r="AK108"/>
-      <c r="AL108"/>
       <c r="AM108"/>
-      <c r="AN108"/>
       <c r="AO108" t="str">
         <f>Codex_calc!AO108</f>
         <v>2019, 2130</v>
@@ -13803,7 +12203,7 @@
       </c>
       <c r="H115" s="30">
         <f t="shared" si="3"/>
-        <v>616.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I115" s="1" t="e">
         <f t="shared" si="3"/>
@@ -13819,11 +12219,11 @@
       </c>
       <c r="L115" s="1">
         <f t="shared" si="3"/>
-        <v>354.166666666667</v>
+        <v>0</v>
       </c>
       <c r="M115" s="30">
         <f t="shared" si="3"/>
-        <v>3.94444444444444</v>
+        <v>0</v>
       </c>
       <c r="N115" s="1" t="e">
         <f t="shared" si="3"/>
@@ -13855,7 +12255,7 @@
       </c>
       <c r="U115" s="1">
         <f t="shared" si="3"/>
-        <v>38.6904761904762</v>
+        <v>0</v>
       </c>
       <c r="V115" s="1" t="e">
         <f t="shared" si="3"/>
@@ -13879,7 +12279,7 @@
       </c>
       <c r="AA115" s="1">
         <f t="shared" si="3"/>
-        <v>1.26262626262626</v>
+        <v>0</v>
       </c>
       <c r="AB115" s="1">
         <f t="shared" si="3"/>
@@ -13891,11 +12291,11 @@
       </c>
       <c r="AD115" s="1">
         <f t="shared" si="3"/>
-        <v>353.703703703704</v>
+        <v>0</v>
       </c>
       <c r="AE115" s="1">
         <f t="shared" si="3"/>
-        <v>41.6666666666666</v>
+        <v>0</v>
       </c>
       <c r="AF115" s="1" t="e">
         <f t="shared" si="3"/>
@@ -13941,7 +12341,7 @@
       </c>
       <c r="G116" s="1">
         <f t="shared" ref="G116:AN116" si="4">G102/G101</f>
-        <v>325.581395348837</v>
+        <v>0</v>
       </c>
       <c r="H116" s="30" t="e">
         <f t="shared" si="4"/>
@@ -13961,11 +12361,11 @@
       </c>
       <c r="L116" s="1">
         <f t="shared" si="4"/>
-        <v>1138.46153846154</v>
+        <v>0</v>
       </c>
       <c r="M116" s="30">
         <f t="shared" si="4"/>
-        <v>71.4285714285714</v>
+        <v>0</v>
       </c>
       <c r="N116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -13997,7 +12397,7 @@
       </c>
       <c r="U116" s="1">
         <f t="shared" si="4"/>
-        <v>505.882352941176</v>
+        <v>0</v>
       </c>
       <c r="V116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -14021,11 +12421,11 @@
       </c>
       <c r="AA116" s="1">
         <f t="shared" si="4"/>
-        <v>1029.74828375286</v>
+        <v>0</v>
       </c>
       <c r="AB116" s="1">
         <f t="shared" si="4"/>
-        <v>90.9090909090909</v>
+        <v>0</v>
       </c>
       <c r="AC116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -14033,11 +12433,11 @@
       </c>
       <c r="AD116" s="1">
         <f t="shared" si="4"/>
-        <v>1229.50819672131</v>
+        <v>0</v>
       </c>
       <c r="AE116" s="1">
         <f t="shared" si="4"/>
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="AF116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -14061,7 +12461,7 @@
       </c>
       <c r="AK116" s="1">
         <f t="shared" si="4"/>
-        <v>3136.36363636364</v>
+        <v>0</v>
       </c>
       <c r="AL116" s="1" t="e">
         <f t="shared" si="4"/>
@@ -14986,12 +13386,10 @@
       <c r="E152" s="30"/>
       <c r="F152" s="30"/>
       <c r="G152" s="30"/>
-      <c r="H152" s="30"/>
       <c r="I152" s="29"/>
       <c r="J152" s="29"/>
       <c r="K152" s="30"/>
       <c r="L152" s="30"/>
-      <c r="M152" s="30"/>
       <c r="N152" s="29"/>
       <c r="O152" s="29"/>
       <c r="P152" s="30"/>
@@ -15027,12 +13425,10 @@
       <c r="E153" s="30"/>
       <c r="F153" s="30"/>
       <c r="G153" s="30"/>
-      <c r="H153" s="30"/>
       <c r="I153" s="29"/>
       <c r="J153" s="29"/>
       <c r="K153" s="30"/>
       <c r="L153" s="30"/>
-      <c r="M153" s="30"/>
       <c r="N153" s="29"/>
       <c r="O153" s="29"/>
       <c r="P153" s="30"/>
@@ -15068,12 +13464,10 @@
       <c r="E154" s="30"/>
       <c r="F154" s="30"/>
       <c r="G154" s="30"/>
-      <c r="H154" s="30"/>
       <c r="I154" s="29"/>
       <c r="J154" s="29"/>
       <c r="K154" s="30"/>
       <c r="L154" s="30"/>
-      <c r="M154" s="30"/>
       <c r="N154" s="29"/>
       <c r="O154" s="29"/>
       <c r="P154" s="30"/>
@@ -15109,12 +13503,10 @@
       <c r="E155" s="30"/>
       <c r="F155" s="30"/>
       <c r="G155" s="30"/>
-      <c r="H155" s="30"/>
       <c r="I155" s="29"/>
       <c r="J155" s="29"/>
       <c r="K155" s="30"/>
       <c r="L155" s="30"/>
-      <c r="M155" s="30"/>
       <c r="N155" s="29"/>
       <c r="O155" s="29"/>
       <c r="P155" s="30"/>
@@ -15150,12 +13542,10 @@
       <c r="E156" s="30"/>
       <c r="F156" s="30"/>
       <c r="G156" s="30"/>
-      <c r="H156" s="30"/>
       <c r="I156" s="29"/>
       <c r="J156" s="29"/>
       <c r="K156" s="30"/>
       <c r="L156" s="30"/>
-      <c r="M156" s="30"/>
       <c r="N156" s="29"/>
       <c r="O156" s="29"/>
       <c r="P156" s="30"/>
@@ -15191,12 +13581,10 @@
       <c r="E157" s="30"/>
       <c r="F157" s="30"/>
       <c r="G157" s="30"/>
-      <c r="H157" s="30"/>
       <c r="I157" s="29"/>
       <c r="J157" s="29"/>
       <c r="K157" s="30"/>
       <c r="L157" s="30"/>
-      <c r="M157" s="30"/>
       <c r="N157" s="29"/>
       <c r="O157" s="29"/>
       <c r="P157" s="30"/>
@@ -15232,12 +13620,10 @@
       <c r="E158" s="30"/>
       <c r="F158" s="30"/>
       <c r="G158" s="30"/>
-      <c r="H158" s="30"/>
       <c r="I158" s="29"/>
       <c r="J158" s="29"/>
       <c r="K158" s="30"/>
       <c r="L158" s="30"/>
-      <c r="M158" s="30"/>
       <c r="N158" s="29"/>
       <c r="O158" s="29"/>
       <c r="P158" s="30"/>
@@ -15273,12 +13659,10 @@
       <c r="E159" s="30"/>
       <c r="F159" s="30"/>
       <c r="G159" s="30"/>
-      <c r="H159" s="30"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="30"/>
       <c r="L159" s="30"/>
-      <c r="M159" s="30"/>
       <c r="N159" s="29"/>
       <c r="O159" s="29"/>
       <c r="P159" s="30"/>
@@ -15314,12 +13698,10 @@
       <c r="E160" s="30"/>
       <c r="F160" s="30"/>
       <c r="G160" s="30"/>
-      <c r="H160" s="30"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="30"/>
       <c r="L160" s="30"/>
-      <c r="M160" s="30"/>
       <c r="N160" s="29"/>
       <c r="O160" s="29"/>
       <c r="P160" s="30"/>
@@ -15355,12 +13737,10 @@
       <c r="E161" s="30"/>
       <c r="F161" s="30"/>
       <c r="G161" s="30"/>
-      <c r="H161" s="30"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="30"/>
       <c r="L161" s="30"/>
-      <c r="M161" s="30"/>
       <c r="N161" s="29"/>
       <c r="O161" s="29"/>
       <c r="P161" s="30"/>
@@ -15396,7 +13776,6 @@
       <c r="E162" s="33"/>
       <c r="F162" s="33"/>
       <c r="G162" s="30"/>
-      <c r="H162" s="30"/>
       <c r="I162" s="33"/>
       <c r="J162" s="33"/>
       <c r="K162" s="33"/>
